--- a/research/traditional_assets/database/data/germany/germany_retail_general.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_retail_general.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.194</v>
+        <v>-0.142</v>
       </c>
       <c r="E2">
-        <v>-0.171</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.01765704584040747</v>
+        <v>0.06593567251461988</v>
       </c>
       <c r="H2">
-        <v>-0.01765704584040747</v>
+        <v>0.06593567251461988</v>
       </c>
       <c r="I2">
-        <v>-0.03837011884550084</v>
+        <v>-0.005950292397660818</v>
       </c>
       <c r="J2">
-        <v>-0.03837011884550084</v>
+        <v>-0.005049043290958319</v>
       </c>
       <c r="K2">
-        <v>1.35</v>
+        <v>4.93</v>
       </c>
       <c r="L2">
-        <v>0.02292020373514431</v>
+        <v>0.07207602339181285</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.004139161462979483</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.02011922503725783</v>
+        <v>0.07347242921013412</v>
       </c>
       <c r="X2">
-        <v>0.07857309762631068</v>
+        <v>0.1046711563557526</v>
       </c>
       <c r="Y2">
-        <v>-0.05845387258905285</v>
+        <v>-0.03119872714561851</v>
       </c>
       <c r="Z2">
-        <v>0.2786253222640082</v>
+        <v>0.3436564239635041</v>
       </c>
       <c r="AA2">
-        <v>-0.01069088672863597</v>
+        <v>-0.001735136161807658</v>
       </c>
       <c r="AB2">
-        <v>0.04487428208001871</v>
+        <v>0.0779139886650953</v>
       </c>
       <c r="AC2">
-        <v>-0.05556516880865468</v>
+        <v>-0.07964912482690296</v>
       </c>
       <c r="AD2">
-        <v>132.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>132.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>131.936</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5415132924335379</v>
+        <v>0.4212987012987013</v>
       </c>
       <c r="AI2">
-        <v>0.6636591478696742</v>
+        <v>0.5687237026647967</v>
       </c>
       <c r="AJ2">
-        <v>0.5406415446901277</v>
+        <v>0.4212987012987013</v>
       </c>
       <c r="AK2">
-        <v>0.6628750577784923</v>
+        <v>0.5687237026647967</v>
       </c>
       <c r="AL2">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="AM2">
-        <v>2.81</v>
+        <v>2.129</v>
       </c>
       <c r="AN2">
-        <v>30.22831050228311</v>
+        <v>15.24436090225564</v>
       </c>
       <c r="AO2">
-        <v>-0.8042704626334519</v>
+        <v>-0.1910798122065728</v>
       </c>
       <c r="AP2">
-        <v>30.12237442922375</v>
+        <v>15.24436090225564</v>
       </c>
       <c r="AQ2">
-        <v>-0.8042704626334519</v>
+        <v>-0.1911695631751996</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.194</v>
+        <v>-0.142</v>
       </c>
       <c r="E3">
-        <v>-0.171</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.01765704584040747</v>
+        <v>0.06593567251461988</v>
       </c>
       <c r="H3">
-        <v>-0.01765704584040747</v>
+        <v>0.06593567251461988</v>
       </c>
       <c r="I3">
-        <v>-0.03837011884550084</v>
+        <v>-0.005950292397660818</v>
       </c>
       <c r="J3">
-        <v>-0.03837011884550084</v>
+        <v>-0.005049043290958319</v>
       </c>
       <c r="K3">
-        <v>1.35</v>
+        <v>4.93</v>
       </c>
       <c r="L3">
-        <v>0.02292020373514431</v>
+        <v>0.07207602339181285</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.004139161462979483</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.02011922503725783</v>
+        <v>0.07347242921013412</v>
       </c>
       <c r="X3">
-        <v>0.07857309762631068</v>
+        <v>0.1046711563557526</v>
       </c>
       <c r="Y3">
-        <v>-0.05845387258905285</v>
+        <v>-0.03119872714561851</v>
       </c>
       <c r="Z3">
-        <v>0.2786253222640082</v>
+        <v>0.3436564239635041</v>
       </c>
       <c r="AA3">
-        <v>-0.01069088672863597</v>
+        <v>-0.001735136161807658</v>
       </c>
       <c r="AB3">
-        <v>0.04487428208001871</v>
+        <v>0.0779139886650953</v>
       </c>
       <c r="AC3">
-        <v>-0.05556516880865468</v>
+        <v>-0.07964912482690296</v>
       </c>
       <c r="AD3">
-        <v>132.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>132.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>131.936</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5415132924335379</v>
+        <v>0.4212987012987013</v>
       </c>
       <c r="AI3">
-        <v>0.6636591478696742</v>
+        <v>0.5687237026647967</v>
       </c>
       <c r="AJ3">
-        <v>0.5406415446901277</v>
+        <v>0.4212987012987013</v>
       </c>
       <c r="AK3">
-        <v>0.6628750577784923</v>
+        <v>0.5687237026647967</v>
       </c>
       <c r="AL3">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="AM3">
-        <v>2.81</v>
+        <v>2.129</v>
       </c>
       <c r="AN3">
-        <v>30.22831050228311</v>
+        <v>15.24436090225564</v>
       </c>
       <c r="AO3">
-        <v>-0.8042704626334519</v>
+        <v>-0.1910798122065728</v>
       </c>
       <c r="AP3">
-        <v>30.12237442922375</v>
+        <v>15.24436090225564</v>
       </c>
       <c r="AQ3">
-        <v>-0.8042704626334519</v>
+        <v>-0.1911695631751996</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_retail_general.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_retail_general.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="xtra_eck" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.142</v>
+        <v>-0.121</v>
       </c>
       <c r="E2">
-        <v>0.04269999999999999</v>
+        <v>-0.106</v>
       </c>
       <c r="G2">
-        <v>0.06593567251461988</v>
+        <v>0.1368286445012788</v>
       </c>
       <c r="H2">
-        <v>0.06593567251461988</v>
+        <v>0.1368286445012788</v>
       </c>
       <c r="I2">
-        <v>-0.005950292397660818</v>
+        <v>0.04398976982097186</v>
       </c>
       <c r="J2">
-        <v>-0.005049043290958319</v>
+        <v>0.03565630410954552</v>
       </c>
       <c r="K2">
-        <v>4.93</v>
+        <v>1.31</v>
       </c>
       <c r="L2">
-        <v>0.07207602339181285</v>
+        <v>0.01675191815856777</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.005314070351758795</v>
       </c>
       <c r="W2">
-        <v>0.07347242921013412</v>
+        <v>0.02130081300813008</v>
       </c>
       <c r="X2">
-        <v>0.1046711563557526</v>
+        <v>0.1266628206004837</v>
       </c>
       <c r="Y2">
-        <v>-0.03119872714561851</v>
+        <v>-0.1053620075923536</v>
       </c>
       <c r="Z2">
-        <v>0.3436564239635041</v>
+        <v>0.5483870967741936</v>
       </c>
       <c r="AA2">
-        <v>-0.001735136161807658</v>
+        <v>0.01955345709233141</v>
       </c>
       <c r="AB2">
-        <v>0.0779139886650953</v>
+        <v>0.07444598354061718</v>
       </c>
       <c r="AC2">
-        <v>-0.07964912482690296</v>
+        <v>-0.05489252644828577</v>
       </c>
       <c r="AD2">
-        <v>81.09999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>81.09999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="AG2">
-        <v>81.09999999999999</v>
+        <v>111.977</v>
       </c>
       <c r="AH2">
-        <v>0.4212987012987013</v>
+        <v>0.5854166666666667</v>
       </c>
       <c r="AI2">
-        <v>0.5687237026647967</v>
+        <v>0.6240977234869517</v>
       </c>
       <c r="AJ2">
-        <v>0.4212987012987013</v>
+        <v>0.5845012710294033</v>
       </c>
       <c r="AK2">
-        <v>0.5687237026647967</v>
+        <v>0.6232127651285362</v>
       </c>
       <c r="AL2">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="AM2">
-        <v>2.129</v>
+        <v>2.438</v>
       </c>
       <c r="AN2">
-        <v>15.24436090225564</v>
+        <v>11.79433368310598</v>
       </c>
       <c r="AO2">
-        <v>-0.1910798122065728</v>
+        <v>1.409836065573771</v>
       </c>
       <c r="AP2">
-        <v>15.24436090225564</v>
+        <v>11.74994753410283</v>
       </c>
       <c r="AQ2">
-        <v>-0.1911695631751996</v>
+        <v>1.410992616899098</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.142</v>
+        <v>-0.121</v>
       </c>
       <c r="E3">
-        <v>0.04269999999999999</v>
+        <v>-0.106</v>
       </c>
       <c r="G3">
-        <v>0.06593567251461988</v>
+        <v>0.1368286445012788</v>
       </c>
       <c r="H3">
-        <v>0.06593567251461988</v>
+        <v>0.1368286445012788</v>
       </c>
       <c r="I3">
-        <v>-0.005950292397660818</v>
+        <v>0.04398976982097186</v>
       </c>
       <c r="J3">
-        <v>-0.005049043290958319</v>
+        <v>0.03565630410954552</v>
       </c>
       <c r="K3">
-        <v>4.93</v>
+        <v>1.31</v>
       </c>
       <c r="L3">
-        <v>0.07207602339181285</v>
+        <v>0.01675191815856777</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +766,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.005314070351758795</v>
       </c>
       <c r="W3">
-        <v>0.07347242921013412</v>
+        <v>0.02130081300813008</v>
       </c>
       <c r="X3">
-        <v>0.1046711563557526</v>
+        <v>0.1266628206004837</v>
       </c>
       <c r="Y3">
-        <v>-0.03119872714561851</v>
+        <v>-0.1053620075923536</v>
       </c>
       <c r="Z3">
-        <v>0.3436564239635041</v>
+        <v>0.5483870967741936</v>
       </c>
       <c r="AA3">
-        <v>-0.001735136161807658</v>
+        <v>0.01955345709233141</v>
       </c>
       <c r="AB3">
-        <v>0.0779139886650953</v>
+        <v>0.07444598354061718</v>
       </c>
       <c r="AC3">
-        <v>-0.07964912482690296</v>
+        <v>-0.05489252644828577</v>
       </c>
       <c r="AD3">
-        <v>81.09999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>81.09999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="AG3">
-        <v>81.09999999999999</v>
+        <v>111.977</v>
       </c>
       <c r="AH3">
-        <v>0.4212987012987013</v>
+        <v>0.5854166666666667</v>
       </c>
       <c r="AI3">
-        <v>0.5687237026647967</v>
+        <v>0.6240977234869517</v>
       </c>
       <c r="AJ3">
-        <v>0.4212987012987013</v>
+        <v>0.5845012710294033</v>
       </c>
       <c r="AK3">
-        <v>0.5687237026647967</v>
+        <v>0.6232127651285362</v>
       </c>
       <c r="AL3">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="AM3">
-        <v>2.129</v>
+        <v>2.438</v>
       </c>
       <c r="AN3">
-        <v>15.24436090225564</v>
+        <v>11.79433368310598</v>
       </c>
       <c r="AO3">
-        <v>-0.1910798122065728</v>
+        <v>1.409836065573771</v>
       </c>
       <c r="AP3">
-        <v>15.24436090225564</v>
+        <v>11.74994753410283</v>
       </c>
       <c r="AQ3">
-        <v>-0.1911695631751996</v>
+        <v>1.410992616899098</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LUDWIG BECK am Rathauseck - Textilhaus Feldmeier AG (XTRA:ECK)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>XTRA:ECK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (General)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.10245901639344</v>
+      </c>
+      <c r="F2">
+        <v>4.62678727352106</v>
+      </c>
+      <c r="G2">
+        <v>11.794333683106</v>
+      </c>
+      <c r="H2">
+        <v>4.02938090241343</v>
+      </c>
+      <c r="I2">
+        <v>0.585416666666667</v>
+      </c>
+      <c r="J2">
+        <v>0.2</v>
+      </c>
+      <c r="K2">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="L2">
+        <v>128.983658174986</v>
+      </c>
+      <c r="M2">
+        <v>191.577</v>
+      </c>
+      <c r="N2">
+        <v>166.960658174986</v>
+      </c>
+      <c r="O2">
+        <v>112.4</v>
+      </c>
+      <c r="P2">
+        <v>38.4</v>
+      </c>
+      <c r="Q2">
+        <v>0.0744459835406172</v>
+      </c>
+      <c r="R2">
+        <v>0.07970155527300091</v>
+      </c>
+      <c r="S2">
+        <v>0.0374668</v>
+      </c>
+      <c r="T2">
+        <v>0.03563</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.126662820600484</v>
+      </c>
+      <c r="X2">
+        <v>0.0907194440912512</v>
+      </c>
+      <c r="Y2">
+        <v>1.91006131740182</v>
+      </c>
+      <c r="Z2">
+        <v>1.12868356720111</v>
+      </c>
+      <c r="AA2">
+        <v>112.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.053524</v>
+      </c>
+      <c r="AC2">
+        <v>1.102459016393442</v>
+      </c>
+      <c r="AD2">
+        <v>112.4</v>
+      </c>
+      <c r="AE2">
+        <v>2.44</v>
+      </c>
+      <c r="AF2">
+        <v>6.84</v>
+      </c>
+      <c r="AG2">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2.53</v>
+      </c>
+      <c r="AR2">
+        <v>2.44</v>
+      </c>
+      <c r="AS2">
+        <v>112.4</v>
+      </c>
+      <c r="AT2">
+        <v>0.423</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08298676092872442</v>
+      </c>
+      <c r="C2">
+        <v>154.9704355944822</v>
+      </c>
+      <c r="D2">
+        <v>154.5474355944822</v>
+      </c>
+      <c r="E2">
+        <v>-112.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.423</v>
+      </c>
+      <c r="H2">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K2">
+        <v>6.84</v>
+      </c>
+      <c r="L2">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="O2">
+        <v>2.713</v>
+      </c>
+      <c r="P2">
+        <v>6.330333333333334</v>
+      </c>
+      <c r="Q2">
+        <v>13.17033333333333</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08298676092872442</v>
+      </c>
+      <c r="T2">
+        <v>0.960581759320096</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03129</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08277910064593824</v>
+      </c>
+      <c r="C3">
+        <v>153.7801768513078</v>
+      </c>
+      <c r="D3">
+        <v>155.2771768513078</v>
+      </c>
+      <c r="E3">
+        <v>-110.48</v>
+      </c>
+      <c r="F3">
+        <v>1.92</v>
+      </c>
+      <c r="G3">
+        <v>0.423</v>
+      </c>
+      <c r="H3">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K3">
+        <v>6.84</v>
+      </c>
+      <c r="L3">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M3">
+        <v>0.085824</v>
+      </c>
+      <c r="N3">
+        <v>8.957509333333332</v>
+      </c>
+      <c r="O3">
+        <v>2.6872528</v>
+      </c>
+      <c r="P3">
+        <v>6.270256533333333</v>
+      </c>
+      <c r="Q3">
+        <v>13.11025653333333</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08329919257165479</v>
+      </c>
+      <c r="T3">
+        <v>0.9673737515577128</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03129</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>105.3706810837683</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08257144036315206</v>
+      </c>
+      <c r="C4">
+        <v>152.5968421789201</v>
+      </c>
+      <c r="D4">
+        <v>156.0138421789201</v>
+      </c>
+      <c r="E4">
+        <v>-108.56</v>
+      </c>
+      <c r="F4">
+        <v>3.84</v>
+      </c>
+      <c r="G4">
+        <v>0.423</v>
+      </c>
+      <c r="H4">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K4">
+        <v>6.84</v>
+      </c>
+      <c r="L4">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M4">
+        <v>0.171648</v>
+      </c>
+      <c r="N4">
+        <v>8.871685333333334</v>
+      </c>
+      <c r="O4">
+        <v>2.6615056</v>
+      </c>
+      <c r="P4">
+        <v>6.210179733333334</v>
+      </c>
+      <c r="Q4">
+        <v>13.05017973333333</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08361800037056333</v>
+      </c>
+      <c r="T4">
+        <v>0.9743043558818116</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03129</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>52.68534054188417</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08236378008036589</v>
+      </c>
+      <c r="C5">
+        <v>151.4205305945182</v>
+      </c>
+      <c r="D5">
+        <v>156.7575305945182</v>
+      </c>
+      <c r="E5">
+        <v>-106.64</v>
+      </c>
+      <c r="F5">
+        <v>5.76</v>
+      </c>
+      <c r="G5">
+        <v>0.423</v>
+      </c>
+      <c r="H5">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K5">
+        <v>6.84</v>
+      </c>
+      <c r="L5">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M5">
+        <v>0.257472</v>
+      </c>
+      <c r="N5">
+        <v>8.785861333333333</v>
+      </c>
+      <c r="O5">
+        <v>2.6357584</v>
+      </c>
+      <c r="P5">
+        <v>6.150102933333333</v>
+      </c>
+      <c r="Q5">
+        <v>12.99010293333333</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08394338152615041</v>
+      </c>
+      <c r="T5">
+        <v>0.9813778592641392</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03129</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>35.1235603612561</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08215611979757972</v>
+      </c>
+      <c r="C6">
+        <v>150.251343012329</v>
+      </c>
+      <c r="D6">
+        <v>157.508343012329</v>
+      </c>
+      <c r="E6">
+        <v>-104.72</v>
+      </c>
+      <c r="F6">
+        <v>7.68</v>
+      </c>
+      <c r="G6">
+        <v>0.423</v>
+      </c>
+      <c r="H6">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K6">
+        <v>6.84</v>
+      </c>
+      <c r="L6">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M6">
+        <v>0.343296</v>
+      </c>
+      <c r="N6">
+        <v>8.700037333333333</v>
+      </c>
+      <c r="O6">
+        <v>2.6100112</v>
+      </c>
+      <c r="P6">
+        <v>6.090026133333333</v>
+      </c>
+      <c r="Q6">
+        <v>12.93002613333333</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0842755414558122</v>
+      </c>
+      <c r="T6">
+        <v>0.9885987273002654</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03129</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>26.34267027094208</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08194845951479353</v>
+      </c>
+      <c r="C7">
+        <v>149.0893822892565</v>
+      </c>
+      <c r="D7">
+        <v>158.2663822892565</v>
+      </c>
+      <c r="E7">
+        <v>-102.8</v>
+      </c>
+      <c r="F7">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.423</v>
+      </c>
+      <c r="H7">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K7">
+        <v>6.84</v>
+      </c>
+      <c r="L7">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M7">
+        <v>0.4291200000000001</v>
+      </c>
+      <c r="N7">
+        <v>8.614213333333334</v>
+      </c>
+      <c r="O7">
+        <v>2.584264</v>
+      </c>
+      <c r="P7">
+        <v>6.029949333333334</v>
+      </c>
+      <c r="Q7">
+        <v>12.86994933333333</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08461469422609846</v>
+      </c>
+      <c r="T7">
+        <v>0.9959716136108363</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03129</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>21.07413621675366</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08174079923200737</v>
+      </c>
+      <c r="C8">
+        <v>147.9347532718541</v>
+      </c>
+      <c r="D8">
+        <v>159.0317532718541</v>
+      </c>
+      <c r="E8">
+        <v>-100.88</v>
+      </c>
+      <c r="F8">
+        <v>11.52</v>
+      </c>
+      <c r="G8">
+        <v>0.423</v>
+      </c>
+      <c r="H8">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K8">
+        <v>6.84</v>
+      </c>
+      <c r="L8">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M8">
+        <v>0.5149440000000001</v>
+      </c>
+      <c r="N8">
+        <v>8.528389333333333</v>
+      </c>
+      <c r="O8">
+        <v>2.5585168</v>
+      </c>
+      <c r="P8">
+        <v>5.969872533333334</v>
+      </c>
+      <c r="Q8">
+        <v>12.80987253333333</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0849610630127738</v>
+      </c>
+      <c r="T8">
+        <v>1.003501369842909</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03129</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>17.56178018062805</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08153313894922121</v>
+      </c>
+      <c r="C9">
+        <v>146.7875628446696</v>
+      </c>
+      <c r="D9">
+        <v>159.8045628446696</v>
+      </c>
+      <c r="E9">
+        <v>-98.96000000000001</v>
+      </c>
+      <c r="F9">
+        <v>13.44</v>
+      </c>
+      <c r="G9">
+        <v>0.423</v>
+      </c>
+      <c r="H9">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K9">
+        <v>6.84</v>
+      </c>
+      <c r="L9">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M9">
+        <v>0.6007680000000001</v>
+      </c>
+      <c r="N9">
+        <v>8.442565333333333</v>
+      </c>
+      <c r="O9">
+        <v>2.5327696</v>
+      </c>
+      <c r="P9">
+        <v>5.909795733333333</v>
+      </c>
+      <c r="Q9">
+        <v>12.74979573333333</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08531488059056044</v>
+      </c>
+      <c r="T9">
+        <v>1.011193056316531</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03129</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>15.05295444053833</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08132547866643504</v>
+      </c>
+      <c r="C10">
+        <v>145.6479199800035</v>
+      </c>
+      <c r="D10">
+        <v>160.5849199800035</v>
+      </c>
+      <c r="E10">
+        <v>-97.04000000000001</v>
+      </c>
+      <c r="F10">
+        <v>15.36</v>
+      </c>
+      <c r="G10">
+        <v>0.423</v>
+      </c>
+      <c r="H10">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K10">
+        <v>6.84</v>
+      </c>
+      <c r="L10">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M10">
+        <v>0.686592</v>
+      </c>
+      <c r="N10">
+        <v>8.356741333333334</v>
+      </c>
+      <c r="O10">
+        <v>2.5070224</v>
+      </c>
+      <c r="P10">
+        <v>5.849718933333333</v>
+      </c>
+      <c r="Q10">
+        <v>12.68971893333333</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08567638985482069</v>
+      </c>
+      <c r="T10">
+        <v>1.019051953365667</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03129</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>13.17133513547104</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08118711838364887</v>
+      </c>
+      <c r="C11">
+        <v>144.2521022265655</v>
+      </c>
+      <c r="D11">
+        <v>161.1091022265655</v>
+      </c>
+      <c r="E11">
+        <v>-95.12</v>
+      </c>
+      <c r="F11">
+        <v>17.28</v>
+      </c>
+      <c r="G11">
+        <v>0.423</v>
+      </c>
+      <c r="H11">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K11">
+        <v>6.84</v>
+      </c>
+      <c r="L11">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M11">
+        <v>0.791424</v>
+      </c>
+      <c r="N11">
+        <v>8.251909333333334</v>
+      </c>
+      <c r="O11">
+        <v>2.4755728</v>
+      </c>
+      <c r="P11">
+        <v>5.776336533333334</v>
+      </c>
+      <c r="Q11">
+        <v>12.61633653333333</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08604584437763611</v>
+      </c>
+      <c r="T11">
+        <v>1.027083573426872</v>
+      </c>
+      <c r="U11">
+        <v>0.0458</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03206</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>11.42666046687153</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08098715810086268</v>
+      </c>
+      <c r="C12">
+        <v>143.0957332245016</v>
+      </c>
+      <c r="D12">
+        <v>161.8727332245016</v>
+      </c>
+      <c r="E12">
+        <v>-93.2</v>
+      </c>
+      <c r="F12">
+        <v>19.2</v>
+      </c>
+      <c r="G12">
+        <v>0.423</v>
+      </c>
+      <c r="H12">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K12">
+        <v>6.84</v>
+      </c>
+      <c r="L12">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M12">
+        <v>0.8793600000000001</v>
+      </c>
+      <c r="N12">
+        <v>8.163973333333333</v>
+      </c>
+      <c r="O12">
+        <v>2.449192</v>
+      </c>
+      <c r="P12">
+        <v>5.714781333333333</v>
+      </c>
+      <c r="Q12">
+        <v>12.55478133333333</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08642350900095853</v>
+      </c>
+      <c r="T12">
+        <v>1.035293673933881</v>
+      </c>
+      <c r="U12">
+        <v>0.0458</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03206</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>10.28399442018437</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08095659781807651</v>
+      </c>
+      <c r="C13">
+        <v>141.2930784743261</v>
+      </c>
+      <c r="D13">
+        <v>161.9900784743261</v>
+      </c>
+      <c r="E13">
+        <v>-91.28</v>
+      </c>
+      <c r="F13">
+        <v>21.12</v>
+      </c>
+      <c r="G13">
+        <v>0.423</v>
+      </c>
+      <c r="H13">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K13">
+        <v>6.84</v>
+      </c>
+      <c r="L13">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M13">
+        <v>1.01376</v>
+      </c>
+      <c r="N13">
+        <v>8.029573333333333</v>
+      </c>
+      <c r="O13">
+        <v>2.408872</v>
+      </c>
+      <c r="P13">
+        <v>5.620701333333333</v>
+      </c>
+      <c r="Q13">
+        <v>12.46070133333333</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08680966046974889</v>
+      </c>
+      <c r="T13">
+        <v>1.043688271081498</v>
+      </c>
+      <c r="U13">
+        <v>0.048</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.0336</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.920586069023569</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08077203753529033</v>
+      </c>
+      <c r="C14">
+        <v>140.0853844867907</v>
+      </c>
+      <c r="D14">
+        <v>162.7023844867907</v>
+      </c>
+      <c r="E14">
+        <v>-89.36000000000001</v>
+      </c>
+      <c r="F14">
+        <v>23.04</v>
+      </c>
+      <c r="G14">
+        <v>0.423</v>
+      </c>
+      <c r="H14">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K14">
+        <v>6.84</v>
+      </c>
+      <c r="L14">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M14">
+        <v>1.10592</v>
+      </c>
+      <c r="N14">
+        <v>7.937413333333333</v>
+      </c>
+      <c r="O14">
+        <v>2.381224</v>
+      </c>
+      <c r="P14">
+        <v>5.556189333333333</v>
+      </c>
+      <c r="Q14">
+        <v>12.39618933333333</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08720458810828448</v>
+      </c>
+      <c r="T14">
+        <v>1.052273654527923</v>
+      </c>
+      <c r="U14">
+        <v>0.048</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.0336</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.177203896604937</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08072397725250416</v>
+      </c>
+      <c r="C15">
+        <v>138.3519012039743</v>
+      </c>
+      <c r="D15">
+        <v>162.8889012039743</v>
+      </c>
+      <c r="E15">
+        <v>-87.44</v>
+      </c>
+      <c r="F15">
+        <v>24.96</v>
+      </c>
+      <c r="G15">
+        <v>0.423</v>
+      </c>
+      <c r="H15">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K15">
+        <v>6.84</v>
+      </c>
+      <c r="L15">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M15">
+        <v>1.23552</v>
+      </c>
+      <c r="N15">
+        <v>7.807813333333333</v>
+      </c>
+      <c r="O15">
+        <v>2.342344</v>
+      </c>
+      <c r="P15">
+        <v>5.465469333333333</v>
+      </c>
+      <c r="Q15">
+        <v>12.30546933333333</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08760859454310824</v>
+      </c>
+      <c r="T15">
+        <v>1.061056403111049</v>
+      </c>
+      <c r="U15">
+        <v>0.0495</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03465</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.319455236121901</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08054991696971799</v>
+      </c>
+      <c r="C16">
+        <v>137.1110040684629</v>
+      </c>
+      <c r="D16">
+        <v>163.5680040684629</v>
+      </c>
+      <c r="E16">
+        <v>-85.52000000000001</v>
+      </c>
+      <c r="F16">
+        <v>26.88</v>
+      </c>
+      <c r="G16">
+        <v>0.423</v>
+      </c>
+      <c r="H16">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K16">
+        <v>6.84</v>
+      </c>
+      <c r="L16">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M16">
+        <v>1.33056</v>
+      </c>
+      <c r="N16">
+        <v>7.712773333333333</v>
+      </c>
+      <c r="O16">
+        <v>2.313832</v>
+      </c>
+      <c r="P16">
+        <v>5.398941333333333</v>
+      </c>
+      <c r="Q16">
+        <v>12.23894133333333</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08802199647641627</v>
+      </c>
+      <c r="T16">
+        <v>1.070043401661223</v>
+      </c>
+      <c r="U16">
+        <v>0.0495</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.03465</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>6.796637004970338</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08037585668693181</v>
+      </c>
+      <c r="C17">
+        <v>135.8757931578931</v>
+      </c>
+      <c r="D17">
+        <v>164.2527931578931</v>
+      </c>
+      <c r="E17">
+        <v>-83.60000000000001</v>
+      </c>
+      <c r="F17">
+        <v>28.8</v>
+      </c>
+      <c r="G17">
+        <v>0.423</v>
+      </c>
+      <c r="H17">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K17">
+        <v>6.84</v>
+      </c>
+      <c r="L17">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M17">
+        <v>1.4256</v>
+      </c>
+      <c r="N17">
+        <v>7.617733333333333</v>
+      </c>
+      <c r="O17">
+        <v>2.28532</v>
+      </c>
+      <c r="P17">
+        <v>5.332413333333333</v>
+      </c>
+      <c r="Q17">
+        <v>12.17241333333333</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08844512551403744</v>
+      </c>
+      <c r="T17">
+        <v>1.079241859000814</v>
+      </c>
+      <c r="U17">
+        <v>0.0495</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.03465</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.343527871305649</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08035859640414564</v>
+      </c>
+      <c r="C18">
+        <v>134.0240112861175</v>
+      </c>
+      <c r="D18">
+        <v>164.3210112861175</v>
+      </c>
+      <c r="E18">
+        <v>-81.68000000000001</v>
+      </c>
+      <c r="F18">
+        <v>30.72</v>
+      </c>
+      <c r="G18">
+        <v>0.423</v>
+      </c>
+      <c r="H18">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K18">
+        <v>6.84</v>
+      </c>
+      <c r="L18">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M18">
+        <v>1.563648</v>
+      </c>
+      <c r="N18">
+        <v>7.479685333333333</v>
+      </c>
+      <c r="O18">
+        <v>2.2439056</v>
+      </c>
+      <c r="P18">
+        <v>5.235779733333334</v>
+      </c>
+      <c r="Q18">
+        <v>12.07577973333333</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08887832905255434</v>
+      </c>
+      <c r="T18">
+        <v>1.088659327229442</v>
+      </c>
+      <c r="U18">
+        <v>0.0509</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.03563</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.783484091901332</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08019433612135946</v>
+      </c>
+      <c r="C19">
+        <v>132.7560670577679</v>
+      </c>
+      <c r="D19">
+        <v>164.9730670577679</v>
+      </c>
+      <c r="E19">
+        <v>-79.76000000000001</v>
+      </c>
+      <c r="F19">
+        <v>32.64</v>
+      </c>
+      <c r="G19">
+        <v>0.423</v>
+      </c>
+      <c r="H19">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K19">
+        <v>6.84</v>
+      </c>
+      <c r="L19">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M19">
+        <v>1.661376</v>
+      </c>
+      <c r="N19">
+        <v>7.381957333333333</v>
+      </c>
+      <c r="O19">
+        <v>2.2145872</v>
+      </c>
+      <c r="P19">
+        <v>5.167370133333334</v>
+      </c>
+      <c r="Q19">
+        <v>12.00737013333333</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08932197123055358</v>
+      </c>
+      <c r="T19">
+        <v>1.098303722403339</v>
+      </c>
+      <c r="U19">
+        <v>0.0509</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03563</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.4432791453189</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.0800300758385733</v>
+      </c>
+      <c r="C20">
+        <v>131.4933183990729</v>
+      </c>
+      <c r="D20">
+        <v>165.6303183990729</v>
+      </c>
+      <c r="E20">
+        <v>-77.84</v>
+      </c>
+      <c r="F20">
+        <v>34.56</v>
+      </c>
+      <c r="G20">
+        <v>0.423</v>
+      </c>
+      <c r="H20">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K20">
+        <v>6.84</v>
+      </c>
+      <c r="L20">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M20">
+        <v>1.759104</v>
+      </c>
+      <c r="N20">
+        <v>7.284229333333332</v>
+      </c>
+      <c r="O20">
+        <v>2.1852688</v>
+      </c>
+      <c r="P20">
+        <v>5.098960533333333</v>
+      </c>
+      <c r="Q20">
+        <v>11.93896053333333</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08977643394947962</v>
+      </c>
+      <c r="T20">
+        <v>1.108183346727818</v>
+      </c>
+      <c r="U20">
+        <v>0.0509</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03563</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.140874748356739</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.07986581555578713</v>
+      </c>
+      <c r="C21">
+        <v>130.2358276557376</v>
+      </c>
+      <c r="D21">
+        <v>166.2928276557376</v>
+      </c>
+      <c r="E21">
+        <v>-75.92</v>
+      </c>
+      <c r="F21">
+        <v>36.48</v>
+      </c>
+      <c r="G21">
+        <v>0.423</v>
+      </c>
+      <c r="H21">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K21">
+        <v>6.84</v>
+      </c>
+      <c r="L21">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M21">
+        <v>1.856832</v>
+      </c>
+      <c r="N21">
+        <v>7.186501333333332</v>
+      </c>
+      <c r="O21">
+        <v>2.1559504</v>
+      </c>
+      <c r="P21">
+        <v>5.030550933333332</v>
+      </c>
+      <c r="Q21">
+        <v>11.87055093333333</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09024211797010756</v>
+      </c>
+      <c r="T21">
+        <v>1.118306912393643</v>
+      </c>
+      <c r="U21">
+        <v>0.0509</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.03563</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.870302393180068</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.07970155527300095</v>
+      </c>
+      <c r="C22">
+        <v>128.9836581749863</v>
+      </c>
+      <c r="D22">
+        <v>166.9606581749863</v>
+      </c>
+      <c r="E22">
+        <v>-74</v>
+      </c>
+      <c r="F22">
+        <v>38.40000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.423</v>
+      </c>
+      <c r="H22">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K22">
+        <v>6.84</v>
+      </c>
+      <c r="L22">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M22">
+        <v>1.95456</v>
+      </c>
+      <c r="N22">
+        <v>7.088773333333332</v>
+      </c>
+      <c r="O22">
+        <v>2.126631999999999</v>
+      </c>
+      <c r="P22">
+        <v>4.962141333333333</v>
+      </c>
+      <c r="Q22">
+        <v>11.80214133333333</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09071944409125118</v>
+      </c>
+      <c r="T22">
+        <v>1.128683567201113</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.03563</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.626787273521064</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.07991949499021476</v>
+      </c>
+      <c r="C23">
+        <v>126.1787407255587</v>
+      </c>
+      <c r="D23">
+        <v>166.0757407255587</v>
+      </c>
+      <c r="E23">
+        <v>-72.08000000000001</v>
+      </c>
+      <c r="F23">
+        <v>40.32</v>
+      </c>
+      <c r="G23">
+        <v>0.423</v>
+      </c>
+      <c r="H23">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K23">
+        <v>6.84</v>
+      </c>
+      <c r="L23">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M23">
+        <v>2.15712</v>
+      </c>
+      <c r="N23">
+        <v>6.886213333333333</v>
+      </c>
+      <c r="O23">
+        <v>2.065864</v>
+      </c>
+      <c r="P23">
+        <v>4.820349333333333</v>
+      </c>
+      <c r="Q23">
+        <v>11.66034933333333</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09120885441799338</v>
+      </c>
+      <c r="T23">
+        <v>1.139322922130291</v>
+      </c>
+      <c r="U23">
+        <v>0.0535</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.03745</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.192318152598526</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07977343470742861</v>
+      </c>
+      <c r="C24">
+        <v>124.8507601602852</v>
+      </c>
+      <c r="D24">
+        <v>166.6677601602852</v>
+      </c>
+      <c r="E24">
+        <v>-70.16</v>
+      </c>
+      <c r="F24">
+        <v>42.24</v>
+      </c>
+      <c r="G24">
+        <v>0.423</v>
+      </c>
+      <c r="H24">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K24">
+        <v>6.84</v>
+      </c>
+      <c r="L24">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M24">
+        <v>2.25984</v>
+      </c>
+      <c r="N24">
+        <v>6.783493333333332</v>
+      </c>
+      <c r="O24">
+        <v>2.035048</v>
+      </c>
+      <c r="P24">
+        <v>4.748445333333333</v>
+      </c>
+      <c r="Q24">
+        <v>11.58844533333333</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09171081372747257</v>
+      </c>
+      <c r="T24">
+        <v>1.150235081032012</v>
+      </c>
+      <c r="U24">
+        <v>0.0535</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.03745</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.00175823657132</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08006207442464243</v>
+      </c>
+      <c r="C25">
+        <v>121.7648726998963</v>
+      </c>
+      <c r="D25">
+        <v>165.5018726998963</v>
+      </c>
+      <c r="E25">
+        <v>-68.24000000000001</v>
+      </c>
+      <c r="F25">
+        <v>44.16</v>
+      </c>
+      <c r="G25">
+        <v>0.423</v>
+      </c>
+      <c r="H25">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K25">
+        <v>6.84</v>
+      </c>
+      <c r="L25">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M25">
+        <v>2.481792</v>
+      </c>
+      <c r="N25">
+        <v>6.561541333333333</v>
+      </c>
+      <c r="O25">
+        <v>1.9684624</v>
+      </c>
+      <c r="P25">
+        <v>4.593078933333333</v>
+      </c>
+      <c r="Q25">
+        <v>11.43307893333333</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09222581094109406</v>
+      </c>
+      <c r="T25">
+        <v>1.16143067263248</v>
+      </c>
+      <c r="U25">
+        <v>0.0562</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.03934</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.643872384685474</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08072451414185626</v>
+      </c>
+      <c r="C26">
+        <v>117.2298152330711</v>
+      </c>
+      <c r="D26">
+        <v>162.8868152330711</v>
+      </c>
+      <c r="E26">
+        <v>-66.32000000000001</v>
+      </c>
+      <c r="F26">
+        <v>46.08</v>
+      </c>
+      <c r="G26">
+        <v>0.423</v>
+      </c>
+      <c r="H26">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K26">
+        <v>6.84</v>
+      </c>
+      <c r="L26">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M26">
+        <v>2.806272</v>
+      </c>
+      <c r="N26">
+        <v>6.237061333333333</v>
+      </c>
+      <c r="O26">
+        <v>1.8711184</v>
+      </c>
+      <c r="P26">
+        <v>4.365942933333333</v>
+      </c>
+      <c r="Q26">
+        <v>11.20594293333333</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09275436071296876</v>
+      </c>
+      <c r="T26">
+        <v>1.172920885064538</v>
+      </c>
+      <c r="U26">
+        <v>0.0609</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.04263</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.22254340752904</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08063025385907009</v>
+      </c>
+      <c r="C27">
+        <v>115.6768643386715</v>
+      </c>
+      <c r="D27">
+        <v>163.2538643386715</v>
+      </c>
+      <c r="E27">
+        <v>-64.40000000000001</v>
+      </c>
+      <c r="F27">
+        <v>48</v>
+      </c>
+      <c r="G27">
+        <v>0.423</v>
+      </c>
+      <c r="H27">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K27">
+        <v>6.84</v>
+      </c>
+      <c r="L27">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M27">
+        <v>2.9232</v>
+      </c>
+      <c r="N27">
+        <v>6.120133333333333</v>
+      </c>
+      <c r="O27">
+        <v>1.83604</v>
+      </c>
+      <c r="P27">
+        <v>4.284093333333334</v>
+      </c>
+      <c r="Q27">
+        <v>11.12409333333333</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09329700514542678</v>
+      </c>
+      <c r="T27">
+        <v>1.184717503161452</v>
+      </c>
+      <c r="U27">
+        <v>0.0609</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.04263</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>3.093641671227878</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08222859357628393</v>
+      </c>
+      <c r="C28">
+        <v>107.7484925754276</v>
+      </c>
+      <c r="D28">
+        <v>157.2454925754276</v>
+      </c>
+      <c r="E28">
+        <v>-62.48</v>
+      </c>
+      <c r="F28">
+        <v>49.92</v>
+      </c>
+      <c r="G28">
+        <v>0.423</v>
+      </c>
+      <c r="H28">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K28">
+        <v>6.84</v>
+      </c>
+      <c r="L28">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M28">
+        <v>3.504384</v>
+      </c>
+      <c r="N28">
+        <v>5.538949333333333</v>
+      </c>
+      <c r="O28">
+        <v>1.6616848</v>
+      </c>
+      <c r="P28">
+        <v>3.877264533333333</v>
+      </c>
+      <c r="Q28">
+        <v>10.71726453333333</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09385431564362691</v>
+      </c>
+      <c r="T28">
+        <v>1.196832948774498</v>
+      </c>
+      <c r="U28">
+        <v>0.0702</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.04914</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.58057716658144</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08308773329349775</v>
+      </c>
+      <c r="C29">
+        <v>102.7780802382436</v>
+      </c>
+      <c r="D29">
+        <v>154.1950802382436</v>
+      </c>
+      <c r="E29">
+        <v>-60.56</v>
+      </c>
+      <c r="F29">
+        <v>51.84</v>
+      </c>
+      <c r="G29">
+        <v>0.423</v>
+      </c>
+      <c r="H29">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K29">
+        <v>6.84</v>
+      </c>
+      <c r="L29">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M29">
+        <v>3.882816</v>
+      </c>
+      <c r="N29">
+        <v>5.160517333333333</v>
+      </c>
+      <c r="O29">
+        <v>1.5481552</v>
+      </c>
+      <c r="P29">
+        <v>3.612362133333333</v>
+      </c>
+      <c r="Q29">
+        <v>10.45236213333333</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09442689492259965</v>
+      </c>
+      <c r="T29">
+        <v>1.20928032440434</v>
+      </c>
+      <c r="U29">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.329065640332515</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08309147301071157</v>
+      </c>
+      <c r="C30">
+        <v>100.8450608926076</v>
+      </c>
+      <c r="D30">
+        <v>154.1820608926076</v>
+      </c>
+      <c r="E30">
+        <v>-58.64</v>
+      </c>
+      <c r="F30">
+        <v>53.76000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.423</v>
+      </c>
+      <c r="H30">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K30">
+        <v>6.84</v>
+      </c>
+      <c r="L30">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M30">
+        <v>4.026624</v>
+      </c>
+      <c r="N30">
+        <v>5.016709333333333</v>
+      </c>
+      <c r="O30">
+        <v>1.5050128</v>
+      </c>
+      <c r="P30">
+        <v>3.511696533333333</v>
+      </c>
+      <c r="Q30">
+        <v>10.35169653333333</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09501537918154385</v>
+      </c>
+      <c r="T30">
+        <v>1.222073460468344</v>
+      </c>
+      <c r="U30">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.245884724606353</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08309521272792539</v>
+      </c>
+      <c r="C31">
+        <v>98.91204374534335</v>
+      </c>
+      <c r="D31">
+        <v>154.1690437453433</v>
+      </c>
+      <c r="E31">
+        <v>-56.72000000000001</v>
+      </c>
+      <c r="F31">
+        <v>55.67999999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.423</v>
+      </c>
+      <c r="H31">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K31">
+        <v>6.84</v>
+      </c>
+      <c r="L31">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M31">
+        <v>4.170431999999999</v>
+      </c>
+      <c r="N31">
+        <v>4.872901333333334</v>
+      </c>
+      <c r="O31">
+        <v>1.4618704</v>
+      </c>
+      <c r="P31">
+        <v>3.411030933333334</v>
+      </c>
+      <c r="Q31">
+        <v>10.25103093333333</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09562044046186675</v>
+      </c>
+      <c r="T31">
+        <v>1.235226966562321</v>
+      </c>
+      <c r="U31">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.168440423757859</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08309895244513921</v>
+      </c>
+      <c r="C32">
+        <v>96.97902879589401</v>
+      </c>
+      <c r="D32">
+        <v>154.156028795894</v>
+      </c>
+      <c r="E32">
+        <v>-54.80000000000001</v>
+      </c>
+      <c r="F32">
+        <v>57.59999999999999</v>
+      </c>
+      <c r="G32">
+        <v>0.423</v>
+      </c>
+      <c r="H32">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K32">
+        <v>6.84</v>
+      </c>
+      <c r="L32">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M32">
+        <v>4.314239999999999</v>
+      </c>
+      <c r="N32">
+        <v>4.729093333333334</v>
+      </c>
+      <c r="O32">
+        <v>1.418728</v>
+      </c>
+      <c r="P32">
+        <v>3.310365333333334</v>
+      </c>
+      <c r="Q32">
+        <v>10.15036533333333</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09624278920734175</v>
+      </c>
+      <c r="T32">
+        <v>1.248756287116125</v>
+      </c>
+      <c r="U32">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.096159076299264</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08310269216235304</v>
+      </c>
+      <c r="C33">
+        <v>95.04601604370298</v>
+      </c>
+      <c r="D33">
+        <v>154.143016043703</v>
+      </c>
+      <c r="E33">
+        <v>-52.88000000000001</v>
+      </c>
+      <c r="F33">
+        <v>59.52</v>
+      </c>
+      <c r="G33">
+        <v>0.423</v>
+      </c>
+      <c r="H33">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K33">
+        <v>6.84</v>
+      </c>
+      <c r="L33">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M33">
+        <v>4.458048</v>
+      </c>
+      <c r="N33">
+        <v>4.585285333333333</v>
+      </c>
+      <c r="O33">
+        <v>1.3755856</v>
+      </c>
+      <c r="P33">
+        <v>3.209699733333333</v>
+      </c>
+      <c r="Q33">
+        <v>10.04969973333333</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09688317704688848</v>
+      </c>
+      <c r="T33">
+        <v>1.26267776188888</v>
+      </c>
+      <c r="U33">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V33">
+        <v>0.3</v>
+      </c>
+      <c r="W33">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.028541041579932</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08675763187956687</v>
+      </c>
+      <c r="C34">
+        <v>81.37849204410162</v>
+      </c>
+      <c r="D34">
+        <v>142.3954920441016</v>
+      </c>
+      <c r="E34">
+        <v>-50.96000000000001</v>
+      </c>
+      <c r="F34">
+        <v>61.44</v>
+      </c>
+      <c r="G34">
+        <v>0.423</v>
+      </c>
+      <c r="H34">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K34">
+        <v>6.84</v>
+      </c>
+      <c r="L34">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M34">
+        <v>5.603328</v>
+      </c>
+      <c r="N34">
+        <v>3.440005333333333</v>
+      </c>
+      <c r="O34">
+        <v>1.0320016</v>
+      </c>
+      <c r="P34">
+        <v>2.408003733333333</v>
+      </c>
+      <c r="Q34">
+        <v>9.248003733333332</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09754239982289246</v>
+      </c>
+      <c r="T34">
+        <v>1.27700869180201</v>
+      </c>
+      <c r="U34">
+        <v>0.0912</v>
+      </c>
+      <c r="V34">
+        <v>0.3</v>
+      </c>
+      <c r="W34">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>1.613921821698343</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08687547159678069</v>
+      </c>
+      <c r="C35">
+        <v>79.10946074065988</v>
+      </c>
+      <c r="D35">
+        <v>142.0464607406599</v>
+      </c>
+      <c r="E35">
+        <v>-49.04000000000001</v>
+      </c>
+      <c r="F35">
+        <v>63.36</v>
+      </c>
+      <c r="G35">
+        <v>0.423</v>
+      </c>
+      <c r="H35">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K35">
+        <v>6.84</v>
+      </c>
+      <c r="L35">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M35">
+        <v>5.778432</v>
+      </c>
+      <c r="N35">
+        <v>3.264901333333333</v>
+      </c>
+      <c r="O35">
+        <v>0.9794703999999997</v>
+      </c>
+      <c r="P35">
+        <v>2.285430933333333</v>
+      </c>
+      <c r="Q35">
+        <v>9.125430933333332</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09822130089071747</v>
+      </c>
+      <c r="T35">
+        <v>1.291767410667771</v>
+      </c>
+      <c r="U35">
+        <v>0.0912</v>
+      </c>
+      <c r="V35">
+        <v>0.3</v>
+      </c>
+      <c r="W35">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>1.565015099828696</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08699331131399451</v>
+      </c>
+      <c r="C36">
+        <v>76.84213630271361</v>
+      </c>
+      <c r="D36">
+        <v>141.6991363027136</v>
+      </c>
+      <c r="E36">
+        <v>-47.12</v>
+      </c>
+      <c r="F36">
+        <v>65.28</v>
+      </c>
+      <c r="G36">
+        <v>0.423</v>
+      </c>
+      <c r="H36">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K36">
+        <v>6.84</v>
+      </c>
+      <c r="L36">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M36">
+        <v>5.953536000000001</v>
+      </c>
+      <c r="N36">
+        <v>3.089797333333332</v>
+      </c>
+      <c r="O36">
+        <v>0.9269391999999996</v>
+      </c>
+      <c r="P36">
+        <v>2.162858133333333</v>
+      </c>
+      <c r="Q36">
+        <v>9.002858133333334</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09892077471817354</v>
+      </c>
+      <c r="T36">
+        <v>1.306973363438555</v>
+      </c>
+      <c r="U36">
+        <v>0.0912</v>
+      </c>
+      <c r="V36">
+        <v>0.3</v>
+      </c>
+      <c r="W36">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>1.518985243951382</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1060995274517253</v>
+      </c>
+      <c r="C37">
+        <v>34.69400354693134</v>
+      </c>
+      <c r="D37">
+        <v>101.4710035469313</v>
+      </c>
+      <c r="E37">
+        <v>-45.2</v>
+      </c>
+      <c r="F37">
+        <v>67.2</v>
+      </c>
+      <c r="G37">
+        <v>0.423</v>
+      </c>
+      <c r="H37">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K37">
+        <v>6.84</v>
+      </c>
+      <c r="L37">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M37">
+        <v>10.52352</v>
+      </c>
+      <c r="N37">
+        <v>-1.480186666666668</v>
+      </c>
+      <c r="O37">
+        <v>-0.4440560000000005</v>
+      </c>
+      <c r="P37">
+        <v>-1.036130666666668</v>
+      </c>
+      <c r="Q37">
+        <v>5.803869333333332</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1006457473616286</v>
+      </c>
+      <c r="T37">
+        <v>1.344472768731056</v>
+      </c>
+      <c r="U37">
+        <v>0.1566</v>
+      </c>
+      <c r="V37">
+        <v>0.2578034726023231</v>
+      </c>
+      <c r="W37">
+        <v>0.1162279761904762</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.8593449086744105</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1072775274517253</v>
+      </c>
+      <c r="C38">
+        <v>31.02842588625207</v>
+      </c>
+      <c r="D38">
+        <v>99.72542588625207</v>
+      </c>
+      <c r="E38">
+        <v>-43.28</v>
+      </c>
+      <c r="F38">
+        <v>69.12</v>
+      </c>
+      <c r="G38">
+        <v>0.423</v>
+      </c>
+      <c r="H38">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K38">
+        <v>6.84</v>
+      </c>
+      <c r="L38">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M38">
+        <v>10.824192</v>
+      </c>
+      <c r="N38">
+        <v>-1.780858666666669</v>
+      </c>
+      <c r="O38">
+        <v>-0.5342576000000007</v>
+      </c>
+      <c r="P38">
+        <v>-1.246601066666668</v>
+      </c>
+      <c r="Q38">
+        <v>5.593398933333331</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.101612087164154</v>
+      </c>
+      <c r="T38">
+        <v>1.365480155742479</v>
+      </c>
+      <c r="U38">
+        <v>0.1566</v>
+      </c>
+      <c r="V38">
+        <v>0.2506422650300363</v>
+      </c>
+      <c r="W38">
+        <v>0.1173494212962963</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.8354742167667879</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1084555274517253</v>
+      </c>
+      <c r="C39">
+        <v>27.42188992863659</v>
+      </c>
+      <c r="D39">
+        <v>98.03888992863658</v>
+      </c>
+      <c r="E39">
+        <v>-41.36000000000001</v>
+      </c>
+      <c r="F39">
+        <v>71.03999999999999</v>
+      </c>
+      <c r="G39">
+        <v>0.423</v>
+      </c>
+      <c r="H39">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K39">
+        <v>6.84</v>
+      </c>
+      <c r="L39">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M39">
+        <v>11.124864</v>
+      </c>
+      <c r="N39">
+        <v>-2.081530666666668</v>
+      </c>
+      <c r="O39">
+        <v>-0.6244592000000002</v>
+      </c>
+      <c r="P39">
+        <v>-1.457071466666667</v>
+      </c>
+      <c r="Q39">
+        <v>5.382928533333333</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1026091044207279</v>
+      </c>
+      <c r="T39">
+        <v>1.387154443928868</v>
+      </c>
+      <c r="U39">
+        <v>0.1566</v>
+      </c>
+      <c r="V39">
+        <v>0.2438681497589543</v>
+      </c>
+      <c r="W39">
+        <v>0.1184102477477478</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.8128938325298478</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1304662837376417</v>
+      </c>
+      <c r="C40">
+        <v>1.960953994796753</v>
+      </c>
+      <c r="D40">
+        <v>74.49795399479676</v>
+      </c>
+      <c r="E40">
+        <v>-39.44</v>
+      </c>
+      <c r="F40">
+        <v>72.96000000000001</v>
+      </c>
+      <c r="G40">
+        <v>0.423</v>
+      </c>
+      <c r="H40">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K40">
+        <v>6.84</v>
+      </c>
+      <c r="L40">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M40">
+        <v>15.234048</v>
+      </c>
+      <c r="N40">
+        <v>-6.19071466666667</v>
+      </c>
+      <c r="O40">
+        <v>-1.857214400000001</v>
+      </c>
+      <c r="P40">
+        <v>-4.333500266666669</v>
+      </c>
+      <c r="Q40">
+        <v>2.506499733333331</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1052459549531855</v>
+      </c>
+      <c r="T40">
+        <v>1.44447728159099</v>
+      </c>
+      <c r="U40">
+        <v>0.2088</v>
+      </c>
+      <c r="V40">
+        <v>0.1780879251529205</v>
+      </c>
+      <c r="W40">
+        <v>0.1716152412280702</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5936264171764019</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1321662837376417</v>
+      </c>
+      <c r="C41">
+        <v>-1.315494143880684</v>
+      </c>
+      <c r="D41">
+        <v>73.14150585611931</v>
+      </c>
+      <c r="E41">
+        <v>-37.52000000000001</v>
+      </c>
+      <c r="F41">
+        <v>74.88</v>
+      </c>
+      <c r="G41">
+        <v>0.423</v>
+      </c>
+      <c r="H41">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K41">
+        <v>6.84</v>
+      </c>
+      <c r="L41">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M41">
+        <v>15.634944</v>
+      </c>
+      <c r="N41">
+        <v>-6.591610666666668</v>
+      </c>
+      <c r="O41">
+        <v>-1.9774832</v>
+      </c>
+      <c r="P41">
+        <v>-4.614127466666668</v>
+      </c>
+      <c r="Q41">
+        <v>2.225872533333332</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1063352329032378</v>
+      </c>
+      <c r="T41">
+        <v>1.468157237026908</v>
+      </c>
+      <c r="U41">
+        <v>0.2088</v>
+      </c>
+      <c r="V41">
+        <v>0.1735215680977175</v>
+      </c>
+      <c r="W41">
+        <v>0.1725686965811966</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5784052269923916</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1338662837376417</v>
+      </c>
+      <c r="C42">
+        <v>-4.543429566059942</v>
+      </c>
+      <c r="D42">
+        <v>71.83357043394007</v>
+      </c>
+      <c r="E42">
+        <v>-35.59999999999999</v>
+      </c>
+      <c r="F42">
+        <v>76.80000000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.423</v>
+      </c>
+      <c r="H42">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K42">
+        <v>6.84</v>
+      </c>
+      <c r="L42">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M42">
+        <v>16.03584</v>
+      </c>
+      <c r="N42">
+        <v>-6.992506666666671</v>
+      </c>
+      <c r="O42">
+        <v>-2.097752000000001</v>
+      </c>
+      <c r="P42">
+        <v>-4.894754666666669</v>
+      </c>
+      <c r="Q42">
+        <v>1.945245333333331</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1074608201182917</v>
+      </c>
+      <c r="T42">
+        <v>1.49262652431069</v>
+      </c>
+      <c r="U42">
+        <v>0.2088</v>
+      </c>
+      <c r="V42">
+        <v>0.1691835288952745</v>
+      </c>
+      <c r="W42">
+        <v>0.1734744791666667</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5639450963175818</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1355662837376417</v>
+      </c>
+      <c r="C43">
+        <v>-7.725409100882075</v>
+      </c>
+      <c r="D43">
+        <v>70.57159089911792</v>
+      </c>
+      <c r="E43">
+        <v>-33.68000000000001</v>
+      </c>
+      <c r="F43">
+        <v>78.72</v>
+      </c>
+      <c r="G43">
+        <v>0.423</v>
+      </c>
+      <c r="H43">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K43">
+        <v>6.84</v>
+      </c>
+      <c r="L43">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M43">
+        <v>16.436736</v>
+      </c>
+      <c r="N43">
+        <v>-7.393402666666667</v>
+      </c>
+      <c r="O43">
+        <v>-2.2180208</v>
+      </c>
+      <c r="P43">
+        <v>-5.175381866666667</v>
+      </c>
+      <c r="Q43">
+        <v>1.664618133333333</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1086245628321611</v>
+      </c>
+      <c r="T43">
+        <v>1.517925278960024</v>
+      </c>
+      <c r="U43">
+        <v>0.2088</v>
+      </c>
+      <c r="V43">
+        <v>0.1650571013612435</v>
+      </c>
+      <c r="W43">
+        <v>0.1743360772357724</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5501903378708116</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1372662837376417</v>
+      </c>
+      <c r="C44">
+        <v>-10.86381300498552</v>
+      </c>
+      <c r="D44">
+        <v>69.35318699501448</v>
+      </c>
+      <c r="E44">
+        <v>-31.76000000000001</v>
+      </c>
+      <c r="F44">
+        <v>80.64</v>
+      </c>
+      <c r="G44">
+        <v>0.423</v>
+      </c>
+      <c r="H44">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K44">
+        <v>6.84</v>
+      </c>
+      <c r="L44">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M44">
+        <v>16.837632</v>
+      </c>
+      <c r="N44">
+        <v>-7.79429866666667</v>
+      </c>
+      <c r="O44">
+        <v>-2.338289600000001</v>
+      </c>
+      <c r="P44">
+        <v>-5.456009066666669</v>
+      </c>
+      <c r="Q44">
+        <v>1.383990933333331</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1098284346051294</v>
+      </c>
+      <c r="T44">
+        <v>1.544096404459334</v>
+      </c>
+      <c r="U44">
+        <v>0.2088</v>
+      </c>
+      <c r="V44">
+        <v>0.161127170376452</v>
+      </c>
+      <c r="W44">
+        <v>0.1751566468253968</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5370905679215066</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1389662837376417</v>
+      </c>
+      <c r="C45">
+        <v>-13.96085994625302</v>
+      </c>
+      <c r="D45">
+        <v>68.17614005374698</v>
+      </c>
+      <c r="E45">
+        <v>-29.84</v>
+      </c>
+      <c r="F45">
+        <v>82.56</v>
+      </c>
+      <c r="G45">
+        <v>0.423</v>
+      </c>
+      <c r="H45">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K45">
+        <v>6.84</v>
+      </c>
+      <c r="L45">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M45">
+        <v>17.238528</v>
+      </c>
+      <c r="N45">
+        <v>-8.195194666666669</v>
+      </c>
+      <c r="O45">
+        <v>-2.458558400000001</v>
+      </c>
+      <c r="P45">
+        <v>-5.736636266666668</v>
+      </c>
+      <c r="Q45">
+        <v>1.103363733333332</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1110745474929387</v>
+      </c>
+      <c r="T45">
+        <v>1.571185815063884</v>
+      </c>
+      <c r="U45">
+        <v>0.2088</v>
+      </c>
+      <c r="V45">
+        <v>0.1573800268793251</v>
+      </c>
+      <c r="W45">
+        <v>0.1759390503875969</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5246000895977505</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1406662837376417</v>
+      </c>
+      <c r="C46">
+        <v>-17.01862048721742</v>
+      </c>
+      <c r="D46">
+        <v>67.03837951278258</v>
+      </c>
+      <c r="E46">
+        <v>-27.92</v>
+      </c>
+      <c r="F46">
+        <v>84.48</v>
+      </c>
+      <c r="G46">
+        <v>0.423</v>
+      </c>
+      <c r="H46">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K46">
+        <v>6.84</v>
+      </c>
+      <c r="L46">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M46">
+        <v>17.639424</v>
+      </c>
+      <c r="N46">
+        <v>-8.596090666666669</v>
+      </c>
+      <c r="O46">
+        <v>-2.578827200000001</v>
+      </c>
+      <c r="P46">
+        <v>-6.017263466666668</v>
+      </c>
+      <c r="Q46">
+        <v>0.8227365333333321</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1123651644124554</v>
+      </c>
+      <c r="T46">
+        <v>1.599242704618596</v>
+      </c>
+      <c r="U46">
+        <v>0.2088</v>
+      </c>
+      <c r="V46">
+        <v>0.1538032080866132</v>
+      </c>
+      <c r="W46">
+        <v>0.1766858901515152</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5126773602887108</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1423662837376417</v>
+      </c>
+      <c r="C47">
+        <v>-20.03902924051818</v>
+      </c>
+      <c r="D47">
+        <v>65.93797075948183</v>
+      </c>
+      <c r="E47">
+        <v>-26</v>
+      </c>
+      <c r="F47">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="G47">
+        <v>0.423</v>
+      </c>
+      <c r="H47">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K47">
+        <v>6.84</v>
+      </c>
+      <c r="L47">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M47">
+        <v>18.04032</v>
+      </c>
+      <c r="N47">
+        <v>-8.996986666666668</v>
+      </c>
+      <c r="O47">
+        <v>-2.699096</v>
+      </c>
+      <c r="P47">
+        <v>-6.297890666666667</v>
+      </c>
+      <c r="Q47">
+        <v>0.5421093333333324</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1137027128563182</v>
+      </c>
+      <c r="T47">
+        <v>1.628319844702571</v>
+      </c>
+      <c r="U47">
+        <v>0.2088</v>
+      </c>
+      <c r="V47">
+        <v>0.1503853590180218</v>
+      </c>
+      <c r="W47">
+        <v>0.177399537037037</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5012845300600728</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1582419456544444</v>
+      </c>
+      <c r="C48">
+        <v>-30.72319433781205</v>
+      </c>
+      <c r="D48">
+        <v>57.17380566218796</v>
+      </c>
+      <c r="E48">
+        <v>-24.08</v>
+      </c>
+      <c r="F48">
+        <v>88.32000000000001</v>
+      </c>
+      <c r="G48">
+        <v>0.423</v>
+      </c>
+      <c r="H48">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K48">
+        <v>6.84</v>
+      </c>
+      <c r="L48">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M48">
+        <v>21.090816</v>
+      </c>
+      <c r="N48">
+        <v>-12.04748266666667</v>
+      </c>
+      <c r="O48">
+        <v>-3.614244800000001</v>
+      </c>
+      <c r="P48">
+        <v>-8.433237866666669</v>
+      </c>
+      <c r="Q48">
+        <v>-1.593237866666669</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1157854703477365</v>
+      </c>
+      <c r="T48">
+        <v>1.673597181472533</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.128634188454349</v>
+      </c>
+      <c r="W48">
+        <v>0.2080821557971015</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.4287806281811634</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1602419456544444</v>
+      </c>
+      <c r="C49">
+        <v>-33.58477684217794</v>
+      </c>
+      <c r="D49">
+        <v>56.23222315782206</v>
+      </c>
+      <c r="E49">
+        <v>-22.16</v>
+      </c>
+      <c r="F49">
+        <v>90.24000000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.423</v>
+      </c>
+      <c r="H49">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K49">
+        <v>6.84</v>
+      </c>
+      <c r="L49">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M49">
+        <v>21.549312</v>
+      </c>
+      <c r="N49">
+        <v>-12.50597866666667</v>
+      </c>
+      <c r="O49">
+        <v>-3.751793600000001</v>
+      </c>
+      <c r="P49">
+        <v>-8.75418506666667</v>
+      </c>
+      <c r="Q49">
+        <v>-1.91418506666667</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1172380263920334</v>
+      </c>
+      <c r="T49">
+        <v>1.705174486783336</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.1258972908276607</v>
+      </c>
+      <c r="W49">
+        <v>0.2087357269503546</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.4196576360922024</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1622419456544444</v>
+      </c>
+      <c r="C50">
+        <v>-36.41584840476062</v>
+      </c>
+      <c r="D50">
+        <v>55.32115159523937</v>
+      </c>
+      <c r="E50">
+        <v>-20.24000000000001</v>
+      </c>
+      <c r="F50">
+        <v>92.16</v>
+      </c>
+      <c r="G50">
+        <v>0.423</v>
+      </c>
+      <c r="H50">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K50">
+        <v>6.84</v>
+      </c>
+      <c r="L50">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M50">
+        <v>22.007808</v>
+      </c>
+      <c r="N50">
+        <v>-12.96447466666667</v>
+      </c>
+      <c r="O50">
+        <v>-3.8893424</v>
+      </c>
+      <c r="P50">
+        <v>-9.075132266666667</v>
+      </c>
+      <c r="Q50">
+        <v>-2.235132266666668</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1187464499764956</v>
+      </c>
+      <c r="T50">
+        <v>1.737966303836861</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1232744306020845</v>
+      </c>
+      <c r="W50">
+        <v>0.2093620659722222</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.410914768673615</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1642419456544444</v>
+      </c>
+      <c r="C51">
+        <v>-39.21786839108376</v>
+      </c>
+      <c r="D51">
+        <v>54.43913160891623</v>
+      </c>
+      <c r="E51">
+        <v>-18.32000000000001</v>
+      </c>
+      <c r="F51">
+        <v>94.08</v>
+      </c>
+      <c r="G51">
+        <v>0.423</v>
+      </c>
+      <c r="H51">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K51">
+        <v>6.84</v>
+      </c>
+      <c r="L51">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M51">
+        <v>22.466304</v>
+      </c>
+      <c r="N51">
+        <v>-13.42297066666667</v>
+      </c>
+      <c r="O51">
+        <v>-4.026891200000001</v>
+      </c>
+      <c r="P51">
+        <v>-9.396079466666666</v>
+      </c>
+      <c r="Q51">
+        <v>-2.556079466666667</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1203140274270151</v>
+      </c>
+      <c r="T51">
+        <v>1.772044074500329</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1207586258959195</v>
+      </c>
+      <c r="W51">
+        <v>0.2099628401360545</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4025287529863983</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1662419456544444</v>
+      </c>
+      <c r="C52">
+        <v>-41.99220455692551</v>
+      </c>
+      <c r="D52">
+        <v>53.58479544307449</v>
+      </c>
+      <c r="E52">
+        <v>-16.40000000000001</v>
+      </c>
+      <c r="F52">
+        <v>96</v>
+      </c>
+      <c r="G52">
+        <v>0.423</v>
+      </c>
+      <c r="H52">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K52">
+        <v>6.84</v>
+      </c>
+      <c r="L52">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M52">
+        <v>22.9248</v>
+      </c>
+      <c r="N52">
+        <v>-13.88146666666667</v>
+      </c>
+      <c r="O52">
+        <v>-4.16444</v>
+      </c>
+      <c r="P52">
+        <v>-9.717026666666669</v>
+      </c>
+      <c r="Q52">
+        <v>-2.877026666666669</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1219443079755554</v>
+      </c>
+      <c r="T52">
+        <v>1.807484955990336</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1183434533780011</v>
+      </c>
+      <c r="W52">
+        <v>0.2105395833333333</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3944781779266704</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1682419456544444</v>
+      </c>
+      <c r="C53">
+        <v>-44.74014012560313</v>
+      </c>
+      <c r="D53">
+        <v>52.75685987439687</v>
+      </c>
+      <c r="E53">
+        <v>-14.48</v>
+      </c>
+      <c r="F53">
+        <v>97.92</v>
+      </c>
+      <c r="G53">
+        <v>0.423</v>
+      </c>
+      <c r="H53">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K53">
+        <v>6.84</v>
+      </c>
+      <c r="L53">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M53">
+        <v>23.383296</v>
+      </c>
+      <c r="N53">
+        <v>-14.33996266666667</v>
+      </c>
+      <c r="O53">
+        <v>-4.3019888</v>
+      </c>
+      <c r="P53">
+        <v>-10.03797386666667</v>
+      </c>
+      <c r="Q53">
+        <v>-3.197973866666668</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1236411305873015</v>
+      </c>
+      <c r="T53">
+        <v>1.844372404071771</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.1160229935078442</v>
+      </c>
+      <c r="W53">
+        <v>0.2110937091503268</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3867433116928141</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1702419456544444</v>
+      </c>
+      <c r="C54">
+        <v>-47.46288021913603</v>
+      </c>
+      <c r="D54">
+        <v>51.95411978086398</v>
+      </c>
+      <c r="E54">
+        <v>-12.56</v>
+      </c>
+      <c r="F54">
+        <v>99.84</v>
+      </c>
+      <c r="G54">
+        <v>0.423</v>
+      </c>
+      <c r="H54">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K54">
+        <v>6.84</v>
+      </c>
+      <c r="L54">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M54">
+        <v>23.841792</v>
+      </c>
+      <c r="N54">
+        <v>-14.79845866666667</v>
+      </c>
+      <c r="O54">
+        <v>-4.4395376</v>
+      </c>
+      <c r="P54">
+        <v>-10.35892106666667</v>
+      </c>
+      <c r="Q54">
+        <v>-3.518921066666667</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1254086541412036</v>
+      </c>
+      <c r="T54">
+        <v>1.8827968291566</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.1137917820942318</v>
+      </c>
+      <c r="W54">
+        <v>0.2116265224358975</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3793059403141061</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1722419456544444</v>
+      </c>
+      <c r="C55">
+        <v>-50.1615577110755</v>
+      </c>
+      <c r="D55">
+        <v>51.1754422889245</v>
+      </c>
+      <c r="E55">
+        <v>-10.64</v>
+      </c>
+      <c r="F55">
+        <v>101.76</v>
+      </c>
+      <c r="G55">
+        <v>0.423</v>
+      </c>
+      <c r="H55">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K55">
+        <v>6.84</v>
+      </c>
+      <c r="L55">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M55">
+        <v>24.300288</v>
+      </c>
+      <c r="N55">
+        <v>-15.25695466666667</v>
+      </c>
+      <c r="O55">
+        <v>-4.577086400000001</v>
+      </c>
+      <c r="P55">
+        <v>-10.67986826666667</v>
+      </c>
+      <c r="Q55">
+        <v>-3.839868266666668</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1272513914633568</v>
+      </c>
+      <c r="T55">
+        <v>1.922856336159932</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.1116447673377369</v>
+      </c>
+      <c r="W55">
+        <v>0.2121392295597485</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.372149224459123</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1742419456544444</v>
+      </c>
+      <c r="C56">
+        <v>-52.83723856078052</v>
+      </c>
+      <c r="D56">
+        <v>50.41976143921949</v>
+      </c>
+      <c r="E56">
+        <v>-8.719999999999999</v>
+      </c>
+      <c r="F56">
+        <v>103.68</v>
+      </c>
+      <c r="G56">
+        <v>0.423</v>
+      </c>
+      <c r="H56">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K56">
+        <v>6.84</v>
+      </c>
+      <c r="L56">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M56">
+        <v>24.758784</v>
+      </c>
+      <c r="N56">
+        <v>-15.71545066666667</v>
+      </c>
+      <c r="O56">
+        <v>-4.714635200000001</v>
+      </c>
+      <c r="P56">
+        <v>-11.00081546666667</v>
+      </c>
+      <c r="Q56">
+        <v>-4.160815466666669</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1291742477995168</v>
+      </c>
+      <c r="T56">
+        <v>1.964657560859061</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.1095772716462973</v>
+      </c>
+      <c r="W56">
+        <v>0.2126329475308642</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3652575721543244</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1762419456544444</v>
+      </c>
+      <c r="C57">
+        <v>-55.49092668195982</v>
+      </c>
+      <c r="D57">
+        <v>49.68607331804019</v>
+      </c>
+      <c r="E57">
+        <v>-6.799999999999997</v>
+      </c>
+      <c r="F57">
+        <v>105.6</v>
+      </c>
+      <c r="G57">
+        <v>0.423</v>
+      </c>
+      <c r="H57">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K57">
+        <v>6.84</v>
+      </c>
+      <c r="L57">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M57">
+        <v>25.21728</v>
+      </c>
+      <c r="N57">
+        <v>-16.17394666666667</v>
+      </c>
+      <c r="O57">
+        <v>-4.852184</v>
+      </c>
+      <c r="P57">
+        <v>-11.32176266666667</v>
+      </c>
+      <c r="Q57">
+        <v>-4.481762666666668</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1311825644172838</v>
+      </c>
+      <c r="T57">
+        <v>2.00831661776704</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.1075849576163646</v>
+      </c>
+      <c r="W57">
+        <v>0.2131087121212121</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3586165253878821</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1782419456544444</v>
+      </c>
+      <c r="C58">
+        <v>-58.12356839224074</v>
+      </c>
+      <c r="D58">
+        <v>48.97343160775927</v>
+      </c>
+      <c r="E58">
+        <v>-4.879999999999995</v>
+      </c>
+      <c r="F58">
+        <v>107.52</v>
+      </c>
+      <c r="G58">
+        <v>0.423</v>
+      </c>
+      <c r="H58">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K58">
+        <v>6.84</v>
+      </c>
+      <c r="L58">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M58">
+        <v>25.675776</v>
+      </c>
+      <c r="N58">
+        <v>-16.63244266666667</v>
+      </c>
+      <c r="O58">
+        <v>-4.989732800000001</v>
+      </c>
+      <c r="P58">
+        <v>-11.64270986666667</v>
+      </c>
+      <c r="Q58">
+        <v>-4.802709866666669</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1332821681540403</v>
+      </c>
+      <c r="T58">
+        <v>2.053960177261746</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.1056637976589295</v>
+      </c>
+      <c r="W58">
+        <v>0.2135674851190476</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3522126588630985</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1802419456544444</v>
+      </c>
+      <c r="C59">
+        <v>-60.73605648523411</v>
+      </c>
+      <c r="D59">
+        <v>48.2809435147659</v>
+      </c>
+      <c r="E59">
+        <v>-2.959999999999994</v>
+      </c>
+      <c r="F59">
+        <v>109.44</v>
+      </c>
+      <c r="G59">
+        <v>0.423</v>
+      </c>
+      <c r="H59">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K59">
+        <v>6.84</v>
+      </c>
+      <c r="L59">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M59">
+        <v>26.134272</v>
+      </c>
+      <c r="N59">
+        <v>-17.09093866666667</v>
+      </c>
+      <c r="O59">
+        <v>-5.127281600000001</v>
+      </c>
+      <c r="P59">
+        <v>-11.96365706666667</v>
+      </c>
+      <c r="Q59">
+        <v>-5.12365706666667</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1354794278785529</v>
+      </c>
+      <c r="T59">
+        <v>2.101726693012019</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.103810046822808</v>
+      </c>
+      <c r="W59">
+        <v>0.2140101608187135</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.34603348940936</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1822419456544444</v>
+      </c>
+      <c r="C60">
+        <v>-63.32923396194059</v>
+      </c>
+      <c r="D60">
+        <v>47.6077660380594</v>
+      </c>
+      <c r="E60">
+        <v>-1.04000000000002</v>
+      </c>
+      <c r="F60">
+        <v>111.36</v>
+      </c>
+      <c r="G60">
+        <v>0.423</v>
+      </c>
+      <c r="H60">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K60">
+        <v>6.84</v>
+      </c>
+      <c r="L60">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M60">
+        <v>26.592768</v>
+      </c>
+      <c r="N60">
+        <v>-17.54943466666667</v>
+      </c>
+      <c r="O60">
+        <v>-5.2648304</v>
+      </c>
+      <c r="P60">
+        <v>-12.28460426666667</v>
+      </c>
+      <c r="Q60">
+        <v>-5.444604266666666</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1377813190185184</v>
+      </c>
+      <c r="T60">
+        <v>2.1517678047504</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.1020202184293113</v>
+      </c>
+      <c r="W60">
+        <v>0.2144375718390805</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.340067394764371</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1842419456544444</v>
+      </c>
+      <c r="C61">
+        <v>-65.90389745428925</v>
+      </c>
+      <c r="D61">
+        <v>46.95310254571074</v>
+      </c>
+      <c r="E61">
+        <v>0.8799999999999955</v>
+      </c>
+      <c r="F61">
+        <v>113.28</v>
+      </c>
+      <c r="G61">
+        <v>0.423</v>
+      </c>
+      <c r="H61">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K61">
+        <v>6.84</v>
+      </c>
+      <c r="L61">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M61">
+        <v>27.051264</v>
+      </c>
+      <c r="N61">
+        <v>-18.00793066666667</v>
+      </c>
+      <c r="O61">
+        <v>-5.402379200000001</v>
+      </c>
+      <c r="P61">
+        <v>-12.60555146666667</v>
+      </c>
+      <c r="Q61">
+        <v>-5.765551466666668</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1401954975311652</v>
+      </c>
+      <c r="T61">
+        <v>2.204249946329678</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.1002910621847467</v>
+      </c>
+      <c r="W61">
+        <v>0.2148504943502825</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3343035406158223</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1862419456544444</v>
+      </c>
+      <c r="C62">
+        <v>-68.46080037004096</v>
+      </c>
+      <c r="D62">
+        <v>46.31619962995903</v>
+      </c>
+      <c r="E62">
+        <v>2.799999999999983</v>
+      </c>
+      <c r="F62">
+        <v>115.2</v>
+      </c>
+      <c r="G62">
+        <v>0.423</v>
+      </c>
+      <c r="H62">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K62">
+        <v>6.84</v>
+      </c>
+      <c r="L62">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M62">
+        <v>27.50976</v>
+      </c>
+      <c r="N62">
+        <v>-18.46642666666667</v>
+      </c>
+      <c r="O62">
+        <v>-5.539928</v>
+      </c>
+      <c r="P62">
+        <v>-12.92649866666667</v>
+      </c>
+      <c r="Q62">
+        <v>-6.086498666666667</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1427303849694443</v>
+      </c>
+      <c r="T62">
+        <v>2.25935619498792</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.09861954448166758</v>
+      </c>
+      <c r="W62">
+        <v>0.2152496527777778</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.328731814938892</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1882419456544444</v>
+      </c>
+      <c r="C63">
+        <v>-71.00065578516059</v>
+      </c>
+      <c r="D63">
+        <v>45.69634421483941</v>
+      </c>
+      <c r="E63">
+        <v>4.719999999999999</v>
+      </c>
+      <c r="F63">
+        <v>117.12</v>
+      </c>
+      <c r="G63">
+        <v>0.423</v>
+      </c>
+      <c r="H63">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K63">
+        <v>6.84</v>
+      </c>
+      <c r="L63">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M63">
+        <v>27.968256</v>
+      </c>
+      <c r="N63">
+        <v>-18.92492266666667</v>
+      </c>
+      <c r="O63">
+        <v>-5.677476800000001</v>
+      </c>
+      <c r="P63">
+        <v>-13.24744586666667</v>
+      </c>
+      <c r="Q63">
+        <v>-6.40744586666667</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1453952666353275</v>
+      </c>
+      <c r="T63">
+        <v>2.317288405115816</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.09700283063770582</v>
+      </c>
+      <c r="W63">
+        <v>0.2156357240437159</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3233427687923527</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1902419456544444</v>
+      </c>
+      <c r="C64">
+        <v>-73.52413910700204</v>
+      </c>
+      <c r="D64">
+        <v>45.09286089299795</v>
+      </c>
+      <c r="E64">
+        <v>6.639999999999986</v>
+      </c>
+      <c r="F64">
+        <v>119.04</v>
+      </c>
+      <c r="G64">
+        <v>0.423</v>
+      </c>
+      <c r="H64">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K64">
+        <v>6.84</v>
+      </c>
+      <c r="L64">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M64">
+        <v>28.426752</v>
+      </c>
+      <c r="N64">
+        <v>-19.38341866666667</v>
+      </c>
+      <c r="O64">
+        <v>-5.8150256</v>
+      </c>
+      <c r="P64">
+        <v>-13.56839306666667</v>
+      </c>
+      <c r="Q64">
+        <v>-6.728393066666667</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.148200405230994</v>
+      </c>
+      <c r="T64">
+        <v>2.378269678934653</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.09543826885322669</v>
+      </c>
+      <c r="W64">
+        <v>0.2160093413978495</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3181275628440891</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1922419456544444</v>
+      </c>
+      <c r="C65">
+        <v>-76.03189052921809</v>
+      </c>
+      <c r="D65">
+        <v>44.50510947078192</v>
+      </c>
+      <c r="E65">
+        <v>8.560000000000002</v>
+      </c>
+      <c r="F65">
+        <v>120.96</v>
+      </c>
+      <c r="G65">
+        <v>0.423</v>
+      </c>
+      <c r="H65">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K65">
+        <v>6.84</v>
+      </c>
+      <c r="L65">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M65">
+        <v>28.885248</v>
+      </c>
+      <c r="N65">
+        <v>-19.84191466666667</v>
+      </c>
+      <c r="O65">
+        <v>-5.952574400000001</v>
+      </c>
+      <c r="P65">
+        <v>-13.88934026666667</v>
+      </c>
+      <c r="Q65">
+        <v>-7.04934026666667</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1511571729399398</v>
+      </c>
+      <c r="T65">
+        <v>2.442547237824778</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.09392337569682627</v>
+      </c>
+      <c r="W65">
+        <v>0.2163710978835979</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3130779189894208</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1942419456544444</v>
+      </c>
+      <c r="C66">
+        <v>-78.52451729715261</v>
+      </c>
+      <c r="D66">
+        <v>43.93248270284737</v>
+      </c>
+      <c r="E66">
+        <v>10.47999999999999</v>
+      </c>
+      <c r="F66">
+        <v>122.88</v>
+      </c>
+      <c r="G66">
+        <v>0.423</v>
+      </c>
+      <c r="H66">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K66">
+        <v>6.84</v>
+      </c>
+      <c r="L66">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M66">
+        <v>29.343744</v>
+      </c>
+      <c r="N66">
+        <v>-20.30041066666667</v>
+      </c>
+      <c r="O66">
+        <v>-6.0901232</v>
+      </c>
+      <c r="P66">
+        <v>-14.21028746666667</v>
+      </c>
+      <c r="Q66">
+        <v>-7.370287466666667</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1542782055216048</v>
+      </c>
+      <c r="T66">
+        <v>2.5103957722088</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.09245582295156336</v>
+      </c>
+      <c r="W66">
+        <v>0.2167215494791667</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3081860765052112</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1962419456544444</v>
+      </c>
+      <c r="C67">
+        <v>-81.0025958005684</v>
+      </c>
+      <c r="D67">
+        <v>43.37440419943161</v>
+      </c>
+      <c r="E67">
+        <v>12.40000000000001</v>
+      </c>
+      <c r="F67">
+        <v>124.8</v>
+      </c>
+      <c r="G67">
+        <v>0.423</v>
+      </c>
+      <c r="H67">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K67">
+        <v>6.84</v>
+      </c>
+      <c r="L67">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M67">
+        <v>29.80224</v>
+      </c>
+      <c r="N67">
+        <v>-20.75890666666667</v>
+      </c>
+      <c r="O67">
+        <v>-6.227672000000001</v>
+      </c>
+      <c r="P67">
+        <v>-14.53123466666667</v>
+      </c>
+      <c r="Q67">
+        <v>-7.69123466666667</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1575775828222221</v>
+      </c>
+      <c r="T67">
+        <v>2.58212136570048</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.09103342567538546</v>
+      </c>
+      <c r="W67">
+        <v>0.217061217948718</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3034447522512849</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1982419456544444</v>
+      </c>
+      <c r="C68">
+        <v>-83.46667350887026</v>
+      </c>
+      <c r="D68">
+        <v>42.83032649112974</v>
+      </c>
+      <c r="E68">
+        <v>14.31999999999999</v>
+      </c>
+      <c r="F68">
+        <v>126.72</v>
+      </c>
+      <c r="G68">
+        <v>0.423</v>
+      </c>
+      <c r="H68">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K68">
+        <v>6.84</v>
+      </c>
+      <c r="L68">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M68">
+        <v>30.260736</v>
+      </c>
+      <c r="N68">
+        <v>-21.21740266666667</v>
+      </c>
+      <c r="O68">
+        <v>-6.3652208</v>
+      </c>
+      <c r="P68">
+        <v>-14.85218186666667</v>
+      </c>
+      <c r="Q68">
+        <v>-8.012181866666669</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1610710411405227</v>
+      </c>
+      <c r="T68">
+        <v>2.658066111750494</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.08965413134697052</v>
+      </c>
+      <c r="W68">
+        <v>0.2173905934343434</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2988471044899018</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2002419456544444</v>
+      </c>
+      <c r="C69">
+        <v>-85.91727076248372</v>
+      </c>
+      <c r="D69">
+        <v>42.29972923751629</v>
+      </c>
+      <c r="E69">
+        <v>16.24000000000001</v>
+      </c>
+      <c r="F69">
+        <v>128.64</v>
+      </c>
+      <c r="G69">
+        <v>0.423</v>
+      </c>
+      <c r="H69">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K69">
+        <v>6.84</v>
+      </c>
+      <c r="L69">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M69">
+        <v>30.71923200000001</v>
+      </c>
+      <c r="N69">
+        <v>-21.67589866666667</v>
+      </c>
+      <c r="O69">
+        <v>-6.502769600000001</v>
+      </c>
+      <c r="P69">
+        <v>-15.17312906666667</v>
+      </c>
+      <c r="Q69">
+        <v>-8.333129066666672</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1647762242053871</v>
+      </c>
+      <c r="T69">
+        <v>2.738613569682327</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.0883160099835829</v>
+      </c>
+      <c r="W69">
+        <v>0.2177101368159204</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2943866999452763</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2022419456544444</v>
+      </c>
+      <c r="C70">
+        <v>-88.35488243270879</v>
+      </c>
+      <c r="D70">
+        <v>41.78211756729122</v>
+      </c>
+      <c r="E70">
+        <v>18.16</v>
+      </c>
+      <c r="F70">
+        <v>130.56</v>
+      </c>
+      <c r="G70">
+        <v>0.423</v>
+      </c>
+      <c r="H70">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K70">
+        <v>6.84</v>
+      </c>
+      <c r="L70">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M70">
+        <v>31.177728</v>
+      </c>
+      <c r="N70">
+        <v>-22.13439466666667</v>
+      </c>
+      <c r="O70">
+        <v>-6.640318400000001</v>
+      </c>
+      <c r="P70">
+        <v>-15.49407626666667</v>
+      </c>
+      <c r="Q70">
+        <v>-8.654076266666667</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1687129812118054</v>
+      </c>
+      <c r="T70">
+        <v>2.824195243734901</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.08701724513088316</v>
+      </c>
+      <c r="W70">
+        <v>0.2180202818627451</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2900574837696106</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2042419456544444</v>
+      </c>
+      <c r="C71">
+        <v>-90.77997946118019</v>
+      </c>
+      <c r="D71">
+        <v>41.27702053881983</v>
+      </c>
+      <c r="E71">
+        <v>20.08000000000001</v>
+      </c>
+      <c r="F71">
+        <v>132.48</v>
+      </c>
+      <c r="G71">
+        <v>0.423</v>
+      </c>
+      <c r="H71">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K71">
+        <v>6.84</v>
+      </c>
+      <c r="L71">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M71">
+        <v>31.63622400000001</v>
+      </c>
+      <c r="N71">
+        <v>-22.59289066666667</v>
+      </c>
+      <c r="O71">
+        <v>-6.777867200000002</v>
+      </c>
+      <c r="P71">
+        <v>-15.81502346666667</v>
+      </c>
+      <c r="Q71">
+        <v>-8.97502346666667</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1729037225412185</v>
+      </c>
+      <c r="T71">
+        <v>2.915298316113446</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.08575612563623267</v>
+      </c>
+      <c r="W71">
+        <v>0.2183214371980677</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2858537521207756</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2062419456544444</v>
+      </c>
+      <c r="C72">
+        <v>-93.1930102889992</v>
+      </c>
+      <c r="D72">
+        <v>40.78398971100081</v>
+      </c>
+      <c r="E72">
+        <v>22</v>
+      </c>
+      <c r="F72">
+        <v>134.4</v>
+      </c>
+      <c r="G72">
+        <v>0.423</v>
+      </c>
+      <c r="H72">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K72">
+        <v>6.84</v>
+      </c>
+      <c r="L72">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M72">
+        <v>32.09472</v>
+      </c>
+      <c r="N72">
+        <v>-23.05138666666667</v>
+      </c>
+      <c r="O72">
+        <v>-6.915416</v>
+      </c>
+      <c r="P72">
+        <v>-16.13597066666667</v>
+      </c>
+      <c r="Q72">
+        <v>-9.295970666666669</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1773738466259258</v>
+      </c>
+      <c r="T72">
+        <v>3.01247492665056</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.08453103812714365</v>
+      </c>
+      <c r="W72">
+        <v>0.2186139880952381</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2817701270904788</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2082419456544444</v>
+      </c>
+      <c r="C73">
+        <v>-95.5944021846538</v>
+      </c>
+      <c r="D73">
+        <v>40.30259781534619</v>
+      </c>
+      <c r="E73">
+        <v>23.91999999999999</v>
+      </c>
+      <c r="F73">
+        <v>136.32</v>
+      </c>
+      <c r="G73">
+        <v>0.423</v>
+      </c>
+      <c r="H73">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K73">
+        <v>6.84</v>
+      </c>
+      <c r="L73">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M73">
+        <v>32.553216</v>
+      </c>
+      <c r="N73">
+        <v>-23.50988266666667</v>
+      </c>
+      <c r="O73">
+        <v>-7.0529648</v>
+      </c>
+      <c r="P73">
+        <v>-16.45691786666666</v>
+      </c>
+      <c r="Q73">
+        <v>-9.616917866666665</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.182152255130268</v>
+      </c>
+      <c r="T73">
+        <v>3.116353372397131</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.0833404601253529</v>
+      </c>
+      <c r="W73">
+        <v>0.2188982981220657</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2778015337511763</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2102419456544444</v>
+      </c>
+      <c r="C74">
+        <v>-97.98456247899136</v>
+      </c>
+      <c r="D74">
+        <v>39.83243752100865</v>
+      </c>
+      <c r="E74">
+        <v>25.84</v>
+      </c>
+      <c r="F74">
+        <v>138.24</v>
+      </c>
+      <c r="G74">
+        <v>0.423</v>
+      </c>
+      <c r="H74">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K74">
+        <v>6.84</v>
+      </c>
+      <c r="L74">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M74">
+        <v>33.011712</v>
+      </c>
+      <c r="N74">
+        <v>-23.96837866666667</v>
+      </c>
+      <c r="O74">
+        <v>-7.190513600000001</v>
+      </c>
+      <c r="P74">
+        <v>-16.77786506666667</v>
+      </c>
+      <c r="Q74">
+        <v>-9.937865066666671</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1872719785277776</v>
+      </c>
+      <c r="T74">
+        <v>3.2276517071256</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.08218295373472298</v>
+      </c>
+      <c r="W74">
+        <v>0.2191747106481482</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2739431791157433</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2122419456544444</v>
+      </c>
+      <c r="C75">
+        <v>-100.3638797147466</v>
+      </c>
+      <c r="D75">
+        <v>39.37312028525337</v>
+      </c>
+      <c r="E75">
+        <v>27.75999999999999</v>
+      </c>
+      <c r="F75">
+        <v>140.16</v>
+      </c>
+      <c r="G75">
+        <v>0.423</v>
+      </c>
+      <c r="H75">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K75">
+        <v>6.84</v>
+      </c>
+      <c r="L75">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M75">
+        <v>33.470208</v>
+      </c>
+      <c r="N75">
+        <v>-24.42687466666667</v>
+      </c>
+      <c r="O75">
+        <v>-7.328062399999999</v>
+      </c>
+      <c r="P75">
+        <v>-17.09881226666667</v>
+      </c>
+      <c r="Q75">
+        <v>-10.25881226666667</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.192770940695473</v>
+      </c>
+      <c r="T75">
+        <v>3.347194362945066</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.08105715984794597</v>
+      </c>
+      <c r="W75">
+        <v>0.2194435502283105</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2701905328264865</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2142419456544444</v>
+      </c>
+      <c r="C76">
+        <v>-102.732724717444</v>
+      </c>
+      <c r="D76">
+        <v>38.92427528255597</v>
+      </c>
+      <c r="E76">
+        <v>29.67999999999998</v>
+      </c>
+      <c r="F76">
+        <v>142.08</v>
+      </c>
+      <c r="G76">
+        <v>0.423</v>
+      </c>
+      <c r="H76">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K76">
+        <v>6.84</v>
+      </c>
+      <c r="L76">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M76">
+        <v>33.928704</v>
+      </c>
+      <c r="N76">
+        <v>-24.88537066666666</v>
+      </c>
+      <c r="O76">
+        <v>-7.465611199999999</v>
+      </c>
+      <c r="P76">
+        <v>-17.41975946666667</v>
+      </c>
+      <c r="Q76">
+        <v>-10.57975946666667</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1986928999529912</v>
+      </c>
+      <c r="T76">
+        <v>3.475932607673723</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07996179282297373</v>
+      </c>
+      <c r="W76">
+        <v>0.2197051238738739</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2665393094099124</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2162419456544444</v>
+      </c>
+      <c r="C77">
+        <v>-105.0914515938767</v>
+      </c>
+      <c r="D77">
+        <v>38.48554840612329</v>
+      </c>
+      <c r="E77">
+        <v>31.59999999999999</v>
+      </c>
+      <c r="F77">
+        <v>144</v>
+      </c>
+      <c r="G77">
+        <v>0.423</v>
+      </c>
+      <c r="H77">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K77">
+        <v>6.84</v>
+      </c>
+      <c r="L77">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M77">
+        <v>34.3872</v>
+      </c>
+      <c r="N77">
+        <v>-25.34386666666667</v>
+      </c>
+      <c r="O77">
+        <v>-7.60316</v>
+      </c>
+      <c r="P77">
+        <v>-17.74070666666667</v>
+      </c>
+      <c r="Q77">
+        <v>-10.90070666666667</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2050886159511109</v>
+      </c>
+      <c r="T77">
+        <v>3.614969911980672</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07889563558533406</v>
+      </c>
+      <c r="W77">
+        <v>0.2199597222222222</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2629854519511136</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2182419456544444</v>
+      </c>
+      <c r="C78">
+        <v>-107.4403986638136</v>
+      </c>
+      <c r="D78">
+        <v>38.05660133618641</v>
+      </c>
+      <c r="E78">
+        <v>33.52000000000001</v>
+      </c>
+      <c r="F78">
+        <v>145.92</v>
+      </c>
+      <c r="G78">
+        <v>0.423</v>
+      </c>
+      <c r="H78">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K78">
+        <v>6.84</v>
+      </c>
+      <c r="L78">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M78">
+        <v>34.845696</v>
+      </c>
+      <c r="N78">
+        <v>-25.80236266666667</v>
+      </c>
+      <c r="O78">
+        <v>-7.740708800000001</v>
+      </c>
+      <c r="P78">
+        <v>-18.06165386666667</v>
+      </c>
+      <c r="Q78">
+        <v>-11.22165386666667</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2120173082824072</v>
+      </c>
+      <c r="T78">
+        <v>3.7655936583132</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07785753511710598</v>
+      </c>
+      <c r="W78">
+        <v>0.2202076206140351</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.25952511705702</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2202419456544444</v>
+      </c>
+      <c r="C79">
+        <v>-109.7798893300862</v>
+      </c>
+      <c r="D79">
+        <v>37.63711066991383</v>
+      </c>
+      <c r="E79">
+        <v>35.44</v>
+      </c>
+      <c r="F79">
+        <v>147.84</v>
+      </c>
+      <c r="G79">
+        <v>0.423</v>
+      </c>
+      <c r="H79">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K79">
+        <v>6.84</v>
+      </c>
+      <c r="L79">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M79">
+        <v>35.304192</v>
+      </c>
+      <c r="N79">
+        <v>-26.26085866666667</v>
+      </c>
+      <c r="O79">
+        <v>-7.8782576</v>
+      </c>
+      <c r="P79">
+        <v>-18.38260106666667</v>
+      </c>
+      <c r="Q79">
+        <v>-11.54260106666667</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2195484955990336</v>
+      </c>
+      <c r="T79">
+        <v>3.929315121718122</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07684639829740331</v>
+      </c>
+      <c r="W79">
+        <v>0.2204490800865801</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2561546609913444</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2222419456544444</v>
+      </c>
+      <c r="C80">
+        <v>-112.1102328917578</v>
+      </c>
+      <c r="D80">
+        <v>37.22676710824217</v>
+      </c>
+      <c r="E80">
+        <v>37.35999999999999</v>
+      </c>
+      <c r="F80">
+        <v>149.76</v>
+      </c>
+      <c r="G80">
+        <v>0.423</v>
+      </c>
+      <c r="H80">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K80">
+        <v>6.84</v>
+      </c>
+      <c r="L80">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M80">
+        <v>35.762688</v>
+      </c>
+      <c r="N80">
+        <v>-26.71935466666666</v>
+      </c>
+      <c r="O80">
+        <v>-8.015806399999999</v>
+      </c>
+      <c r="P80">
+        <v>-18.70354826666667</v>
+      </c>
+      <c r="Q80">
+        <v>-11.86354826666667</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2277643363080806</v>
+      </c>
+      <c r="T80">
+        <v>4.107920354523491</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07586118806282123</v>
+      </c>
+      <c r="W80">
+        <v>0.2206843482905983</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2528706268760708</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2242419456544444</v>
+      </c>
+      <c r="C81">
+        <v>-114.431725304673</v>
+      </c>
+      <c r="D81">
+        <v>36.825274695327</v>
+      </c>
+      <c r="E81">
+        <v>39.28</v>
+      </c>
+      <c r="F81">
+        <v>151.68</v>
+      </c>
+      <c r="G81">
+        <v>0.423</v>
+      </c>
+      <c r="H81">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K81">
+        <v>6.84</v>
+      </c>
+      <c r="L81">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M81">
+        <v>36.221184</v>
+      </c>
+      <c r="N81">
+        <v>-27.17785066666667</v>
+      </c>
+      <c r="O81">
+        <v>-8.1533552</v>
+      </c>
+      <c r="P81">
+        <v>-19.02449546666667</v>
+      </c>
+      <c r="Q81">
+        <v>-12.18449546666667</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2367626380370368</v>
+      </c>
+      <c r="T81">
+        <v>4.303535609500801</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07490091985949436</v>
+      </c>
+      <c r="W81">
+        <v>0.2209136603375528</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2496697328649813</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2262419456544444</v>
+      </c>
+      <c r="C82">
+        <v>-116.7446498933157</v>
+      </c>
+      <c r="D82">
+        <v>36.43235010668434</v>
+      </c>
+      <c r="E82">
+        <v>41.20000000000002</v>
+      </c>
+      <c r="F82">
+        <v>153.6</v>
+      </c>
+      <c r="G82">
+        <v>0.423</v>
+      </c>
+      <c r="H82">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K82">
+        <v>6.84</v>
+      </c>
+      <c r="L82">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M82">
+        <v>36.67968</v>
+      </c>
+      <c r="N82">
+        <v>-27.63634666666667</v>
+      </c>
+      <c r="O82">
+        <v>-8.290904000000001</v>
+      </c>
+      <c r="P82">
+        <v>-19.34544266666667</v>
+      </c>
+      <c r="Q82">
+        <v>-12.50544266666667</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2466607699388887</v>
+      </c>
+      <c r="T82">
+        <v>4.518712389975841</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.07396465836125068</v>
+      </c>
+      <c r="W82">
+        <v>0.2211372395833334</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.246548861204169</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2282419456544444</v>
+      </c>
+      <c r="C83">
+        <v>-119.0492780175764</v>
+      </c>
+      <c r="D83">
+        <v>36.04772198242362</v>
+      </c>
+      <c r="E83">
+        <v>43.12</v>
+      </c>
+      <c r="F83">
+        <v>155.52</v>
+      </c>
+      <c r="G83">
+        <v>0.423</v>
+      </c>
+      <c r="H83">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K83">
+        <v>6.84</v>
+      </c>
+      <c r="L83">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M83">
+        <v>37.138176</v>
+      </c>
+      <c r="N83">
+        <v>-28.09484266666667</v>
+      </c>
+      <c r="O83">
+        <v>-8.428452800000001</v>
+      </c>
+      <c r="P83">
+        <v>-19.66638986666667</v>
+      </c>
+      <c r="Q83">
+        <v>-12.82638986666667</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2576008104619881</v>
+      </c>
+      <c r="T83">
+        <v>4.756539357869307</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.07305151443086487</v>
+      </c>
+      <c r="W83">
+        <v>0.2213552983539095</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.243505048102883</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2302419456544444</v>
+      </c>
+      <c r="C84">
+        <v>-121.3458696977246</v>
+      </c>
+      <c r="D84">
+        <v>35.67113030227544</v>
+      </c>
+      <c r="E84">
+        <v>45.03999999999999</v>
+      </c>
+      <c r="F84">
+        <v>157.44</v>
+      </c>
+      <c r="G84">
+        <v>0.423</v>
+      </c>
+      <c r="H84">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K84">
+        <v>6.84</v>
+      </c>
+      <c r="L84">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M84">
+        <v>37.596672</v>
+      </c>
+      <c r="N84">
+        <v>-28.55333866666667</v>
+      </c>
+      <c r="O84">
+        <v>-8.5660016</v>
+      </c>
+      <c r="P84">
+        <v>-19.98733706666667</v>
+      </c>
+      <c r="Q84">
+        <v>-13.14733706666667</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2697564110432096</v>
+      </c>
+      <c r="T84">
+        <v>5.020791544417601</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.07216064230365922</v>
+      </c>
+      <c r="W84">
+        <v>0.2215680386178862</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2405354743455307</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2322419456544444</v>
+      </c>
+      <c r="C85">
+        <v>-123.6346742006114</v>
+      </c>
+      <c r="D85">
+        <v>35.30232579938859</v>
+      </c>
+      <c r="E85">
+        <v>46.96000000000001</v>
+      </c>
+      <c r="F85">
+        <v>159.36</v>
+      </c>
+      <c r="G85">
+        <v>0.423</v>
+      </c>
+      <c r="H85">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K85">
+        <v>6.84</v>
+      </c>
+      <c r="L85">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M85">
+        <v>38.055168</v>
+      </c>
+      <c r="N85">
+        <v>-29.01183466666667</v>
+      </c>
+      <c r="O85">
+        <v>-8.703550400000001</v>
+      </c>
+      <c r="P85">
+        <v>-20.30828426666667</v>
+      </c>
+      <c r="Q85">
+        <v>-13.46828426666667</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2833420822810456</v>
+      </c>
+      <c r="T85">
+        <v>5.316132223500991</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07129123697469945</v>
+      </c>
+      <c r="W85">
+        <v>0.2217756526104418</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2376374565823315</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2342419456544444</v>
+      </c>
+      <c r="C86">
+        <v>-125.9159305898801</v>
+      </c>
+      <c r="D86">
+        <v>34.94106941011988</v>
+      </c>
+      <c r="E86">
+        <v>48.88</v>
+      </c>
+      <c r="F86">
+        <v>161.28</v>
+      </c>
+      <c r="G86">
+        <v>0.423</v>
+      </c>
+      <c r="H86">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K86">
+        <v>6.84</v>
+      </c>
+      <c r="L86">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M86">
+        <v>38.51366400000001</v>
+      </c>
+      <c r="N86">
+        <v>-29.47033066666667</v>
+      </c>
+      <c r="O86">
+        <v>-8.841099200000002</v>
+      </c>
+      <c r="P86">
+        <v>-20.62923146666667</v>
+      </c>
+      <c r="Q86">
+        <v>-13.78923146666667</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2986259624236108</v>
+      </c>
+      <c r="T86">
+        <v>5.6483904874698</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07044253177261969</v>
+      </c>
+      <c r="W86">
+        <v>0.2219783234126984</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2348084392420656</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2362419456544444</v>
+      </c>
+      <c r="C87">
+        <v>-128.189868242736</v>
+      </c>
+      <c r="D87">
+        <v>34.58713175726396</v>
+      </c>
+      <c r="E87">
+        <v>50.79999999999998</v>
+      </c>
+      <c r="F87">
+        <v>163.2</v>
+      </c>
+      <c r="G87">
+        <v>0.423</v>
+      </c>
+      <c r="H87">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K87">
+        <v>6.84</v>
+      </c>
+      <c r="L87">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M87">
+        <v>38.97216</v>
+      </c>
+      <c r="N87">
+        <v>-29.92882666666667</v>
+      </c>
+      <c r="O87">
+        <v>-8.978648</v>
+      </c>
+      <c r="P87">
+        <v>-20.95017866666667</v>
+      </c>
+      <c r="Q87">
+        <v>-14.11017866666667</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3159476932518515</v>
+      </c>
+      <c r="T87">
+        <v>6.02494985330112</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06961379610470653</v>
+      </c>
+      <c r="W87">
+        <v>0.2221762254901961</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2320459870156885</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2382419456544444</v>
+      </c>
+      <c r="C88">
+        <v>-130.4567073356237</v>
+      </c>
+      <c r="D88">
+        <v>34.24029266437634</v>
+      </c>
+      <c r="E88">
+        <v>52.72</v>
+      </c>
+      <c r="F88">
+        <v>165.12</v>
+      </c>
+      <c r="G88">
+        <v>0.423</v>
+      </c>
+      <c r="H88">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K88">
+        <v>6.84</v>
+      </c>
+      <c r="L88">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M88">
+        <v>39.43065600000001</v>
+      </c>
+      <c r="N88">
+        <v>-30.38732266666667</v>
+      </c>
+      <c r="O88">
+        <v>-9.116196800000001</v>
+      </c>
+      <c r="P88">
+        <v>-21.27112586666667</v>
+      </c>
+      <c r="Q88">
+        <v>-14.43112586666667</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3357439570555552</v>
+      </c>
+      <c r="T88">
+        <v>6.4553034142512</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06880433335930296</v>
+      </c>
+      <c r="W88">
+        <v>0.2223695251937985</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2293477778643432</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2402419456544444</v>
+      </c>
+      <c r="C89">
+        <v>-132.7166593009717</v>
+      </c>
+      <c r="D89">
+        <v>33.90034069902834</v>
+      </c>
+      <c r="E89">
+        <v>54.63999999999999</v>
+      </c>
+      <c r="F89">
+        <v>167.04</v>
+      </c>
+      <c r="G89">
+        <v>0.423</v>
+      </c>
+      <c r="H89">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K89">
+        <v>6.84</v>
+      </c>
+      <c r="L89">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M89">
+        <v>39.889152</v>
+      </c>
+      <c r="N89">
+        <v>-30.84581866666667</v>
+      </c>
+      <c r="O89">
+        <v>-9.2537456</v>
+      </c>
+      <c r="P89">
+        <v>-21.59207306666667</v>
+      </c>
+      <c r="Q89">
+        <v>-14.75207306666667</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3585857999059825</v>
+      </c>
+      <c r="T89">
+        <v>6.951865215347445</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.0680134789528742</v>
+      </c>
+      <c r="W89">
+        <v>0.2225583812260536</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2267115965095806</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2422419456544444</v>
+      </c>
+      <c r="C90">
+        <v>-134.9699272569969</v>
+      </c>
+      <c r="D90">
+        <v>33.5670727430031</v>
+      </c>
+      <c r="E90">
+        <v>56.56</v>
+      </c>
+      <c r="F90">
+        <v>168.96</v>
+      </c>
+      <c r="G90">
+        <v>0.423</v>
+      </c>
+      <c r="H90">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K90">
+        <v>6.84</v>
+      </c>
+      <c r="L90">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M90">
+        <v>40.34764800000001</v>
+      </c>
+      <c r="N90">
+        <v>-31.30431466666667</v>
+      </c>
+      <c r="O90">
+        <v>-9.391294400000001</v>
+      </c>
+      <c r="P90">
+        <v>-21.91302026666667</v>
+      </c>
+      <c r="Q90">
+        <v>-15.07302026666667</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3852346165648144</v>
+      </c>
+      <c r="T90">
+        <v>7.531187316626401</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06724059851022789</v>
+      </c>
+      <c r="W90">
+        <v>0.2227429450757576</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2241353283674263</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2442419456544444</v>
+      </c>
+      <c r="C91">
+        <v>-137.2167064124033</v>
+      </c>
+      <c r="D91">
+        <v>33.2402935875967</v>
+      </c>
+      <c r="E91">
+        <v>58.47999999999999</v>
+      </c>
+      <c r="F91">
+        <v>170.88</v>
+      </c>
+      <c r="G91">
+        <v>0.423</v>
+      </c>
+      <c r="H91">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K91">
+        <v>6.84</v>
+      </c>
+      <c r="L91">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M91">
+        <v>40.806144</v>
+      </c>
+      <c r="N91">
+        <v>-31.76281066666667</v>
+      </c>
+      <c r="O91">
+        <v>-9.528843200000001</v>
+      </c>
+      <c r="P91">
+        <v>-22.23396746666667</v>
+      </c>
+      <c r="Q91">
+        <v>-15.39396746666667</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4167286726161612</v>
+      </c>
+      <c r="T91">
+        <v>8.215840709046983</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06648508616741634</v>
+      </c>
+      <c r="W91">
+        <v>0.222923361423221</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2216169538913878</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2462419456544444</v>
+      </c>
+      <c r="C92">
+        <v>-139.4571844476698</v>
+      </c>
+      <c r="D92">
+        <v>32.91981555233021</v>
+      </c>
+      <c r="E92">
+        <v>60.40000000000001</v>
+      </c>
+      <c r="F92">
+        <v>172.8</v>
+      </c>
+      <c r="G92">
+        <v>0.423</v>
+      </c>
+      <c r="H92">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K92">
+        <v>6.84</v>
+      </c>
+      <c r="L92">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M92">
+        <v>41.26464000000001</v>
+      </c>
+      <c r="N92">
+        <v>-32.22130666666668</v>
+      </c>
+      <c r="O92">
+        <v>-9.666392000000004</v>
+      </c>
+      <c r="P92">
+        <v>-22.55491466666668</v>
+      </c>
+      <c r="Q92">
+        <v>-15.71491466666668</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4545215398777773</v>
+      </c>
+      <c r="T92">
+        <v>9.037424779951682</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06574636298777839</v>
+      </c>
+      <c r="W92">
+        <v>0.2230997685185185</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2191545432925945</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2482419456544444</v>
+      </c>
+      <c r="C93">
+        <v>-141.6915418744924</v>
+      </c>
+      <c r="D93">
+        <v>32.60545812550757</v>
+      </c>
+      <c r="E93">
+        <v>62.31999999999999</v>
+      </c>
+      <c r="F93">
+        <v>174.72</v>
+      </c>
+      <c r="G93">
+        <v>0.423</v>
+      </c>
+      <c r="H93">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K93">
+        <v>6.84</v>
+      </c>
+      <c r="L93">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M93">
+        <v>41.723136</v>
+      </c>
+      <c r="N93">
+        <v>-32.67980266666667</v>
+      </c>
+      <c r="O93">
+        <v>-9.803940800000001</v>
+      </c>
+      <c r="P93">
+        <v>-22.87586186666667</v>
+      </c>
+      <c r="Q93">
+        <v>-16.03586186666668</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5007128220864194</v>
+      </c>
+      <c r="T93">
+        <v>10.0415830888352</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06502387548241818</v>
+      </c>
+      <c r="W93">
+        <v>0.2232722985347985</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2167462516080605</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2502419456544444</v>
+      </c>
+      <c r="C94">
+        <v>-143.9199523748271</v>
+      </c>
+      <c r="D94">
+        <v>32.29704762517293</v>
+      </c>
+      <c r="E94">
+        <v>64.24000000000001</v>
+      </c>
+      <c r="F94">
+        <v>176.64</v>
+      </c>
+      <c r="G94">
+        <v>0.423</v>
+      </c>
+      <c r="H94">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K94">
+        <v>6.84</v>
+      </c>
+      <c r="L94">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M94">
+        <v>42.18163200000001</v>
+      </c>
+      <c r="N94">
+        <v>-33.13829866666667</v>
+      </c>
+      <c r="O94">
+        <v>-9.941489600000001</v>
+      </c>
+      <c r="P94">
+        <v>-23.19680906666667</v>
+      </c>
+      <c r="Q94">
+        <v>-16.35680906666667</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5584519248472219</v>
+      </c>
+      <c r="T94">
+        <v>11.29678097493961</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06431709422717451</v>
+      </c>
+      <c r="W94">
+        <v>0.2234410778985507</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2143903140905817</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2522419456544444</v>
+      </c>
+      <c r="C95">
+        <v>-146.1425831208704</v>
+      </c>
+      <c r="D95">
+        <v>31.9944168791296</v>
+      </c>
+      <c r="E95">
+        <v>66.16</v>
+      </c>
+      <c r="F95">
+        <v>178.56</v>
+      </c>
+      <c r="G95">
+        <v>0.423</v>
+      </c>
+      <c r="H95">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K95">
+        <v>6.84</v>
+      </c>
+      <c r="L95">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M95">
+        <v>42.640128</v>
+      </c>
+      <c r="N95">
+        <v>-33.59679466666667</v>
+      </c>
+      <c r="O95">
+        <v>-10.0790384</v>
+      </c>
+      <c r="P95">
+        <v>-23.51775626666667</v>
+      </c>
+      <c r="Q95">
+        <v>-16.67775626666667</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6326879141111108</v>
+      </c>
+      <c r="T95">
+        <v>12.91060682850241</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06362551256881779</v>
+      </c>
+      <c r="W95">
+        <v>0.2236062275985663</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2120850418960594</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2542419456544444</v>
+      </c>
+      <c r="C96">
+        <v>-148.3595950772185</v>
+      </c>
+      <c r="D96">
+        <v>31.69740492278153</v>
+      </c>
+      <c r="E96">
+        <v>68.08000000000001</v>
+      </c>
+      <c r="F96">
+        <v>180.48</v>
+      </c>
+      <c r="G96">
+        <v>0.423</v>
+      </c>
+      <c r="H96">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K96">
+        <v>6.84</v>
+      </c>
+      <c r="L96">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M96">
+        <v>43.09862400000001</v>
+      </c>
+      <c r="N96">
+        <v>-34.05529066666668</v>
+      </c>
+      <c r="O96">
+        <v>-10.2165872</v>
+      </c>
+      <c r="P96">
+        <v>-23.83870346666668</v>
+      </c>
+      <c r="Q96">
+        <v>-16.99870346666668</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7316692331296295</v>
+      </c>
+      <c r="T96">
+        <v>15.06237463325281</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06294864541383037</v>
+      </c>
+      <c r="W96">
+        <v>0.2237678634751773</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2098288180461011</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2562419456544444</v>
+      </c>
+      <c r="C97">
+        <v>-150.5711432863497</v>
+      </c>
+      <c r="D97">
+        <v>31.40585671365031</v>
+      </c>
+      <c r="E97">
+        <v>70</v>
+      </c>
+      <c r="F97">
+        <v>182.4</v>
+      </c>
+      <c r="G97">
+        <v>0.423</v>
+      </c>
+      <c r="H97">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K97">
+        <v>6.84</v>
+      </c>
+      <c r="L97">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M97">
+        <v>43.55712</v>
+      </c>
+      <c r="N97">
+        <v>-34.51378666666668</v>
+      </c>
+      <c r="O97">
+        <v>-10.354136</v>
+      </c>
+      <c r="P97">
+        <v>-24.15965066666667</v>
+      </c>
+      <c r="Q97">
+        <v>-17.31965066666667</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8702430797555558</v>
+      </c>
+      <c r="T97">
+        <v>18.07484955990339</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.06228602809368478</v>
+      </c>
+      <c r="W97">
+        <v>0.2239260964912281</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2076200936456158</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2582419456544444</v>
+      </c>
+      <c r="C98">
+        <v>-152.7773771384967</v>
+      </c>
+      <c r="D98">
+        <v>31.11962286150332</v>
+      </c>
+      <c r="E98">
+        <v>71.91999999999999</v>
+      </c>
+      <c r="F98">
+        <v>184.32</v>
+      </c>
+      <c r="G98">
+        <v>0.423</v>
+      </c>
+      <c r="H98">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K98">
+        <v>6.84</v>
+      </c>
+      <c r="L98">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M98">
+        <v>44.015616</v>
+      </c>
+      <c r="N98">
+        <v>-34.97228266666667</v>
+      </c>
+      <c r="O98">
+        <v>-10.4916848</v>
+      </c>
+      <c r="P98">
+        <v>-24.48059786666667</v>
+      </c>
+      <c r="Q98">
+        <v>-17.64059786666667</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.078103849694442</v>
+      </c>
+      <c r="T98">
+        <v>22.59356194987918</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06163721530104224</v>
+      </c>
+      <c r="W98">
+        <v>0.2240810329861111</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2054573843368074</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2602419456544444</v>
+      </c>
+      <c r="C99">
+        <v>-154.9784406268935</v>
+      </c>
+      <c r="D99">
+        <v>30.83855937310655</v>
+      </c>
+      <c r="E99">
+        <v>73.84</v>
+      </c>
+      <c r="F99">
+        <v>186.24</v>
+      </c>
+      <c r="G99">
+        <v>0.423</v>
+      </c>
+      <c r="H99">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K99">
+        <v>6.84</v>
+      </c>
+      <c r="L99">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M99">
+        <v>44.47411200000001</v>
+      </c>
+      <c r="N99">
+        <v>-35.43077866666667</v>
+      </c>
+      <c r="O99">
+        <v>-10.6292336</v>
+      </c>
+      <c r="P99">
+        <v>-24.80154506666667</v>
+      </c>
+      <c r="Q99">
+        <v>-17.96154506666667</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.424538466259257</v>
+      </c>
+      <c r="T99">
+        <v>30.12474926650558</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06100178009175314</v>
+      </c>
+      <c r="W99">
+        <v>0.2242327749140894</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2033392669725106</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2622419456544444</v>
+      </c>
+      <c r="C100">
+        <v>-157.1744725893147</v>
+      </c>
+      <c r="D100">
+        <v>30.56252741068532</v>
+      </c>
+      <c r="E100">
+        <v>75.75999999999999</v>
+      </c>
+      <c r="F100">
+        <v>188.16</v>
+      </c>
+      <c r="G100">
+        <v>0.423</v>
+      </c>
+      <c r="H100">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K100">
+        <v>6.84</v>
+      </c>
+      <c r="L100">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M100">
+        <v>44.932608</v>
+      </c>
+      <c r="N100">
+        <v>-35.88927466666667</v>
+      </c>
+      <c r="O100">
+        <v>-10.7667824</v>
+      </c>
+      <c r="P100">
+        <v>-25.12249226666667</v>
+      </c>
+      <c r="Q100">
+        <v>-18.28249226666667</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.117407699388885</v>
+      </c>
+      <c r="T100">
+        <v>45.18712389975836</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06037931294795975</v>
+      </c>
+      <c r="W100">
+        <v>0.2243814200680272</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2012643764931993</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2642419456544444</v>
+      </c>
+      <c r="C101">
+        <v>-159.365606936758</v>
+      </c>
+      <c r="D101">
+        <v>30.29139306324201</v>
+      </c>
+      <c r="E101">
+        <v>77.67999999999998</v>
+      </c>
+      <c r="F101">
+        <v>190.08</v>
+      </c>
+      <c r="G101">
+        <v>0.423</v>
+      </c>
+      <c r="H101">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>15.88333333333333</v>
+      </c>
+      <c r="K101">
+        <v>6.84</v>
+      </c>
+      <c r="L101">
+        <v>9.043333333333333</v>
+      </c>
+      <c r="M101">
+        <v>45.391104</v>
+      </c>
+      <c r="N101">
+        <v>-36.34777066666666</v>
+      </c>
+      <c r="O101">
+        <v>-10.9043312</v>
+      </c>
+      <c r="P101">
+        <v>-25.44343946666666</v>
+      </c>
+      <c r="Q101">
+        <v>-18.60343946666666</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.196015398777769</v>
+      </c>
+      <c r="T101">
+        <v>90.37424779951672</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05976942089798035</v>
+      </c>
+      <c r="W101">
+        <v>0.2245270622895623</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1992314029932679</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_retail_general.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_retail_general.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08739319017856015</v>
+        <v>0.08716251060802448</v>
       </c>
       <c r="C2">
-        <v>104.7608326263723</v>
+        <v>103.9069978934473</v>
       </c>
       <c r="D2">
-        <v>104.3148326263724</v>
+        <v>104.7169978934473</v>
       </c>
       <c r="E2">
-        <v>-70.5</v>
+        <v>-69.244</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.256</v>
       </c>
       <c r="G2">
         <v>0.446</v>
@@ -1439,28 +1439,28 @@
         <v>9.77</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06317679999999999</v>
       </c>
       <c r="N2">
-        <v>9.77</v>
+        <v>9.706823199999999</v>
       </c>
       <c r="O2">
-        <v>2.931</v>
+        <v>2.91204696</v>
       </c>
       <c r="P2">
-        <v>6.839</v>
+        <v>6.794776239999999</v>
       </c>
       <c r="Q2">
-        <v>14.569</v>
+        <v>14.52477624</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08739319017856015</v>
+        <v>0.08768728344244897</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9673737515577128</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>154.6453761507389</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08716251060802448</v>
+        <v>0.0869318310374888</v>
       </c>
       <c r="C3">
-        <v>103.9069978934473</v>
+        <v>103.0562760996115</v>
       </c>
       <c r="D3">
-        <v>104.7169978934473</v>
+        <v>105.1222760996115</v>
       </c>
       <c r="E3">
-        <v>-69.244</v>
+        <v>-67.988</v>
       </c>
       <c r="F3">
-        <v>1.256</v>
+        <v>2.512</v>
       </c>
       <c r="G3">
         <v>0.446</v>
@@ -1521,28 +1521,28 @@
         <v>9.77</v>
       </c>
       <c r="M3">
-        <v>0.06317679999999999</v>
+        <v>0.1263536</v>
       </c>
       <c r="N3">
-        <v>9.706823199999999</v>
+        <v>9.6436464</v>
       </c>
       <c r="O3">
-        <v>2.91204696</v>
+        <v>2.89309392</v>
       </c>
       <c r="P3">
-        <v>6.794776239999999</v>
+        <v>6.75055248</v>
       </c>
       <c r="Q3">
-        <v>14.52477624</v>
+        <v>14.48055248</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08768728344244897</v>
+        <v>0.08798737860968245</v>
       </c>
       <c r="T3">
-        <v>0.9673737515577128</v>
+        <v>0.9743043558818116</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.6453761507389</v>
+        <v>77.32268807536944</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0869318310374888</v>
+        <v>0.08670115146695311</v>
       </c>
       <c r="C4">
-        <v>103.0562760996115</v>
+        <v>102.2087035286029</v>
       </c>
       <c r="D4">
-        <v>105.1222760996115</v>
+        <v>105.5307035286029</v>
       </c>
       <c r="E4">
-        <v>-67.988</v>
+        <v>-66.732</v>
       </c>
       <c r="F4">
-        <v>2.512</v>
+        <v>3.768</v>
       </c>
       <c r="G4">
         <v>0.446</v>
@@ -1603,28 +1603,28 @@
         <v>9.77</v>
       </c>
       <c r="M4">
-        <v>0.1263536</v>
+        <v>0.1895304</v>
       </c>
       <c r="N4">
-        <v>9.6436464</v>
+        <v>9.580469599999999</v>
       </c>
       <c r="O4">
-        <v>2.89309392</v>
+        <v>2.87414088</v>
       </c>
       <c r="P4">
-        <v>6.75055248</v>
+        <v>6.706328719999999</v>
       </c>
       <c r="Q4">
-        <v>14.48055248</v>
+        <v>14.43632872</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08798737860968245</v>
+        <v>0.08829366130613722</v>
       </c>
       <c r="T4">
-        <v>0.9743043558818116</v>
+        <v>0.9813778592641392</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.32268807536944</v>
+        <v>51.54845871691295</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08670115146695311</v>
+        <v>0.08647047189641743</v>
       </c>
       <c r="C5">
-        <v>102.2087035286029</v>
+        <v>101.364317030246</v>
       </c>
       <c r="D5">
-        <v>105.5307035286029</v>
+        <v>105.942317030246</v>
       </c>
       <c r="E5">
-        <v>-66.732</v>
+        <v>-65.476</v>
       </c>
       <c r="F5">
-        <v>3.768</v>
+        <v>5.024</v>
       </c>
       <c r="G5">
         <v>0.446</v>
@@ -1685,28 +1685,28 @@
         <v>9.77</v>
       </c>
       <c r="M5">
-        <v>0.1895304</v>
+        <v>0.2527072</v>
       </c>
       <c r="N5">
-        <v>9.580469599999999</v>
+        <v>9.5172928</v>
       </c>
       <c r="O5">
-        <v>2.87414088</v>
+        <v>2.85518784</v>
       </c>
       <c r="P5">
-        <v>6.706328719999999</v>
+        <v>6.662104960000001</v>
       </c>
       <c r="Q5">
-        <v>14.43632872</v>
+        <v>14.39210496</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08829366130613722</v>
+        <v>0.08860632489210149</v>
       </c>
       <c r="T5">
-        <v>0.9813778592641392</v>
+        <v>0.9885987273002654</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.54845871691295</v>
+        <v>38.66134403768473</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08647047189641743</v>
+        <v>0.08623979232588175</v>
       </c>
       <c r="C6">
-        <v>101.364317030246</v>
+        <v>100.5231540315349</v>
       </c>
       <c r="D6">
-        <v>105.942317030246</v>
+        <v>106.3571540315349</v>
       </c>
       <c r="E6">
-        <v>-65.476</v>
+        <v>-64.22</v>
       </c>
       <c r="F6">
-        <v>5.024</v>
+        <v>6.28</v>
       </c>
       <c r="G6">
         <v>0.446</v>
@@ -1767,28 +1767,28 @@
         <v>9.77</v>
       </c>
       <c r="M6">
-        <v>0.2527072</v>
+        <v>0.315884</v>
       </c>
       <c r="N6">
-        <v>9.5172928</v>
+        <v>9.454115999999999</v>
       </c>
       <c r="O6">
-        <v>2.85518784</v>
+        <v>2.8362348</v>
       </c>
       <c r="P6">
-        <v>6.662104960000001</v>
+        <v>6.617881199999999</v>
       </c>
       <c r="Q6">
-        <v>14.39210496</v>
+        <v>14.3478812</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08860632489210149</v>
+        <v>0.08892557086934921</v>
       </c>
       <c r="T6">
-        <v>0.9885987273002654</v>
+        <v>0.9959716136108363</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.66134403768473</v>
+        <v>30.92907523014777</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08623979232588175</v>
+        <v>0.08600911275534608</v>
       </c>
       <c r="C7">
-        <v>100.5231540315349</v>
+        <v>99.68525254797774</v>
       </c>
       <c r="D7">
-        <v>106.3571540315349</v>
+        <v>106.7752525479777</v>
       </c>
       <c r="E7">
-        <v>-64.22</v>
+        <v>-62.964</v>
       </c>
       <c r="F7">
-        <v>6.28</v>
+        <v>7.536</v>
       </c>
       <c r="G7">
         <v>0.446</v>
@@ -1849,28 +1849,28 @@
         <v>9.77</v>
       </c>
       <c r="M7">
-        <v>0.315884</v>
+        <v>0.3790608</v>
       </c>
       <c r="N7">
-        <v>9.454115999999999</v>
+        <v>9.3909392</v>
       </c>
       <c r="O7">
-        <v>2.8362348</v>
+        <v>2.81728176</v>
       </c>
       <c r="P7">
-        <v>6.617881199999999</v>
+        <v>6.57365744</v>
       </c>
       <c r="Q7">
-        <v>14.3478812</v>
+        <v>14.30365744</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08892557086934921</v>
+        <v>0.08925160931419795</v>
       </c>
       <c r="T7">
-        <v>0.9959716136108363</v>
+        <v>1.003501369842909</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.92907523014777</v>
+        <v>25.77422935845648</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08600911275534608</v>
+        <v>0.0857784331848104</v>
       </c>
       <c r="C8">
-        <v>99.68525254797774</v>
+        <v>98.85065119520999</v>
       </c>
       <c r="D8">
-        <v>106.7752525479777</v>
+        <v>107.19665119521</v>
       </c>
       <c r="E8">
-        <v>-62.964</v>
+        <v>-61.708</v>
       </c>
       <c r="F8">
-        <v>7.536</v>
+        <v>8.791999999999998</v>
       </c>
       <c r="G8">
         <v>0.446</v>
@@ -1931,28 +1931,28 @@
         <v>9.77</v>
       </c>
       <c r="M8">
-        <v>0.3790608</v>
+        <v>0.4422375999999999</v>
       </c>
       <c r="N8">
-        <v>9.3909392</v>
+        <v>9.327762399999999</v>
       </c>
       <c r="O8">
-        <v>2.81728176</v>
+        <v>2.79832872</v>
       </c>
       <c r="P8">
-        <v>6.57365744</v>
+        <v>6.529433679999999</v>
       </c>
       <c r="Q8">
-        <v>14.30365744</v>
+        <v>14.25943368</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08925160931419795</v>
+        <v>0.0895846593385058</v>
       </c>
       <c r="T8">
-        <v>1.003501369842909</v>
+        <v>1.011193056316531</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.77422935845648</v>
+        <v>22.0921965929627</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08577843318481039</v>
+        <v>0.0855477536142747</v>
       </c>
       <c r="C9">
-        <v>98.85065119521002</v>
+        <v>98.0193892008835</v>
       </c>
       <c r="D9">
-        <v>107.19665119521</v>
+        <v>107.6213892008835</v>
       </c>
       <c r="E9">
-        <v>-61.708</v>
+        <v>-60.452</v>
       </c>
       <c r="F9">
-        <v>8.792</v>
+        <v>10.048</v>
       </c>
       <c r="G9">
         <v>0.446</v>
@@ -2013,28 +2013,28 @@
         <v>9.77</v>
       </c>
       <c r="M9">
-        <v>0.4422376</v>
+        <v>0.5054143999999999</v>
       </c>
       <c r="N9">
-        <v>9.327762399999999</v>
+        <v>9.2645856</v>
       </c>
       <c r="O9">
-        <v>2.79832872</v>
+        <v>2.77937568</v>
       </c>
       <c r="P9">
-        <v>6.529433679999999</v>
+        <v>6.485209920000001</v>
       </c>
       <c r="Q9">
-        <v>14.25943368</v>
+        <v>14.21520992</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0895846593385058</v>
+        <v>0.08992494958073338</v>
       </c>
       <c r="T9">
-        <v>1.011193056316531</v>
+        <v>1.019051953365667</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.0921965929627</v>
+        <v>19.33067201884236</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0855477536142747</v>
+        <v>0.08531707404373905</v>
       </c>
       <c r="C10">
-        <v>98.0193892008835</v>
+        <v>97.19150641683937</v>
       </c>
       <c r="D10">
-        <v>107.6213892008835</v>
+        <v>108.0495064168394</v>
       </c>
       <c r="E10">
-        <v>-60.452</v>
+        <v>-59.196</v>
       </c>
       <c r="F10">
-        <v>10.048</v>
+        <v>11.304</v>
       </c>
       <c r="G10">
         <v>0.446</v>
@@ -2095,28 +2095,28 @@
         <v>9.77</v>
       </c>
       <c r="M10">
-        <v>0.5054143999999999</v>
+        <v>0.5685911999999999</v>
       </c>
       <c r="N10">
-        <v>9.2645856</v>
+        <v>9.201408799999999</v>
       </c>
       <c r="O10">
-        <v>2.77937568</v>
+        <v>2.76042264</v>
       </c>
       <c r="P10">
-        <v>6.485209920000001</v>
+        <v>6.44098616</v>
       </c>
       <c r="Q10">
-        <v>14.21520992</v>
+        <v>14.17098616</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08992494958073338</v>
+        <v>0.09027271872938356</v>
       </c>
       <c r="T10">
-        <v>1.019051953365667</v>
+        <v>1.027083573426872</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.33067201884236</v>
+        <v>17.18281957230432</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08531707404373905</v>
+        <v>0.08508639447320335</v>
       </c>
       <c r="C11">
-        <v>97.19150641683937</v>
+        <v>96.36704333157314</v>
       </c>
       <c r="D11">
-        <v>108.0495064168394</v>
+        <v>108.4810433315731</v>
       </c>
       <c r="E11">
-        <v>-59.196</v>
+        <v>-57.94</v>
       </c>
       <c r="F11">
-        <v>11.304</v>
+        <v>12.56</v>
       </c>
       <c r="G11">
         <v>0.446</v>
@@ -2177,28 +2177,28 @@
         <v>9.77</v>
       </c>
       <c r="M11">
-        <v>0.5685911999999999</v>
+        <v>0.6317679999999999</v>
       </c>
       <c r="N11">
-        <v>9.201408799999999</v>
+        <v>9.138232</v>
       </c>
       <c r="O11">
-        <v>2.76042264</v>
+        <v>2.7414696</v>
       </c>
       <c r="P11">
-        <v>6.44098616</v>
+        <v>6.3967624</v>
       </c>
       <c r="Q11">
-        <v>14.17098616</v>
+        <v>14.1267624</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09027271872938356</v>
+        <v>0.09062821608133706</v>
       </c>
       <c r="T11">
-        <v>1.027083573426872</v>
+        <v>1.035293673933881</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.18281957230432</v>
+        <v>15.46453761507389</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08508639447320335</v>
+        <v>0.08485571490266768</v>
       </c>
       <c r="C12">
-        <v>96.36704333157314</v>
+        <v>95.54604108299873</v>
       </c>
       <c r="D12">
-        <v>108.4810433315731</v>
+        <v>108.9160410829987</v>
       </c>
       <c r="E12">
-        <v>-57.94</v>
+        <v>-56.684</v>
       </c>
       <c r="F12">
-        <v>12.56</v>
+        <v>13.816</v>
       </c>
       <c r="G12">
         <v>0.446</v>
@@ -2259,28 +2259,28 @@
         <v>9.77</v>
       </c>
       <c r="M12">
-        <v>0.631768</v>
+        <v>0.6949447999999999</v>
       </c>
       <c r="N12">
-        <v>9.138232</v>
+        <v>9.0750552</v>
       </c>
       <c r="O12">
-        <v>2.7414696</v>
+        <v>2.72251656</v>
       </c>
       <c r="P12">
-        <v>6.3967624</v>
+        <v>6.35253864</v>
       </c>
       <c r="Q12">
-        <v>14.1267624</v>
+        <v>14.08253864</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09062821608133706</v>
+        <v>0.09099170213782884</v>
       </c>
       <c r="T12">
-        <v>1.035293673933881</v>
+        <v>1.043688271081498</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.46453761507389</v>
+        <v>14.05867055915808</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08485571490266768</v>
+        <v>0.08462503533213199</v>
       </c>
       <c r="C13">
-        <v>95.54604108299873</v>
+        <v>94.72854147152184</v>
       </c>
       <c r="D13">
-        <v>108.9160410829987</v>
+        <v>109.3545414715218</v>
       </c>
       <c r="E13">
-        <v>-56.684</v>
+        <v>-55.428</v>
       </c>
       <c r="F13">
-        <v>13.816</v>
+        <v>15.072</v>
       </c>
       <c r="G13">
         <v>0.446</v>
@@ -2341,28 +2341,28 @@
         <v>9.77</v>
       </c>
       <c r="M13">
-        <v>0.6949447999999999</v>
+        <v>0.7581216</v>
       </c>
       <c r="N13">
-        <v>9.0750552</v>
+        <v>9.011878400000001</v>
       </c>
       <c r="O13">
-        <v>2.72251656</v>
+        <v>2.70356352</v>
       </c>
       <c r="P13">
-        <v>6.35253864</v>
+        <v>6.308314880000001</v>
       </c>
       <c r="Q13">
-        <v>14.08253864</v>
+        <v>14.03831488</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09099170213782884</v>
+        <v>0.09136344924105907</v>
       </c>
       <c r="T13">
-        <v>1.043688271081498</v>
+        <v>1.052273654527923</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.05867055915808</v>
+        <v>12.88711467922824</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08462503533213199</v>
+        <v>0.08453085576159632</v>
       </c>
       <c r="C14">
-        <v>94.72854147152184</v>
+        <v>93.65258477512843</v>
       </c>
       <c r="D14">
-        <v>109.3545414715218</v>
+        <v>109.5345847751284</v>
       </c>
       <c r="E14">
-        <v>-55.428</v>
+        <v>-54.172</v>
       </c>
       <c r="F14">
-        <v>15.072</v>
+        <v>16.328</v>
       </c>
       <c r="G14">
         <v>0.446</v>
@@ -2423,45 +2423,45 @@
         <v>9.77</v>
       </c>
       <c r="M14">
-        <v>0.7581216</v>
+        <v>0.8457903999999999</v>
       </c>
       <c r="N14">
-        <v>9.011878400000001</v>
+        <v>8.924209599999999</v>
       </c>
       <c r="O14">
-        <v>2.70356352</v>
+        <v>2.67726288</v>
       </c>
       <c r="P14">
-        <v>6.308314880000001</v>
+        <v>6.24694672</v>
       </c>
       <c r="Q14">
-        <v>14.03831488</v>
+        <v>13.97694672</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09136344924105907</v>
+        <v>0.09174374225470841</v>
       </c>
       <c r="T14">
-        <v>1.052273654527923</v>
+        <v>1.061056403111049</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>12.88711467922824</v>
+        <v>11.55132524559276</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08453085576159632</v>
+        <v>0.08431067619106063</v>
       </c>
       <c r="C15">
-        <v>93.65258477512843</v>
+        <v>92.81982467537983</v>
       </c>
       <c r="D15">
-        <v>109.5345847751284</v>
+        <v>109.9578246753798</v>
       </c>
       <c r="E15">
-        <v>-54.172</v>
+        <v>-52.916</v>
       </c>
       <c r="F15">
-        <v>16.328</v>
+        <v>17.584</v>
       </c>
       <c r="G15">
         <v>0.446</v>
@@ -2505,28 +2505,28 @@
         <v>9.77</v>
       </c>
       <c r="M15">
-        <v>0.8457903999999999</v>
+        <v>0.9108512</v>
       </c>
       <c r="N15">
-        <v>8.924209599999999</v>
+        <v>8.8591488</v>
       </c>
       <c r="O15">
-        <v>2.67726288</v>
+        <v>2.65774464</v>
       </c>
       <c r="P15">
-        <v>6.24694672</v>
+        <v>6.20140416</v>
       </c>
       <c r="Q15">
-        <v>13.97694672</v>
+        <v>13.93140416</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09174374225470841</v>
+        <v>0.09213287929193097</v>
       </c>
       <c r="T15">
-        <v>1.061056403111049</v>
+        <v>1.070043401661223</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.55132524559276</v>
+        <v>10.72623058519328</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08431067619106063</v>
+        <v>0.08409049662052495</v>
       </c>
       <c r="C16">
-        <v>92.81982467537983</v>
+        <v>91.99034804745298</v>
       </c>
       <c r="D16">
-        <v>109.9578246753798</v>
+        <v>110.384348047453</v>
       </c>
       <c r="E16">
-        <v>-52.916</v>
+        <v>-51.66</v>
       </c>
       <c r="F16">
-        <v>17.584</v>
+        <v>18.84</v>
       </c>
       <c r="G16">
         <v>0.446</v>
@@ -2587,28 +2587,28 @@
         <v>9.77</v>
       </c>
       <c r="M16">
-        <v>0.9108512</v>
+        <v>0.9759120000000001</v>
       </c>
       <c r="N16">
-        <v>8.8591488</v>
+        <v>8.794087999999999</v>
       </c>
       <c r="O16">
-        <v>2.65774464</v>
+        <v>2.638226399999999</v>
       </c>
       <c r="P16">
-        <v>6.20140416</v>
+        <v>6.1558616</v>
       </c>
       <c r="Q16">
-        <v>13.93140416</v>
+        <v>13.8858616</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09213287929193097</v>
+        <v>0.09253117249473523</v>
       </c>
       <c r="T16">
-        <v>1.070043401661223</v>
+        <v>1.079241859000814</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.72623058519328</v>
+        <v>10.01114854618039</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08409049662052495</v>
+        <v>0.08406071704998927</v>
       </c>
       <c r="C17">
-        <v>91.99034804745298</v>
+        <v>90.79229005093141</v>
       </c>
       <c r="D17">
-        <v>110.384348047453</v>
+        <v>110.4422900509314</v>
       </c>
       <c r="E17">
-        <v>-51.66</v>
+        <v>-50.404</v>
       </c>
       <c r="F17">
-        <v>18.84</v>
+        <v>20.096</v>
       </c>
       <c r="G17">
         <v>0.446</v>
@@ -2669,45 +2669,45 @@
         <v>9.77</v>
       </c>
       <c r="M17">
-        <v>0.975912</v>
+        <v>1.075136</v>
       </c>
       <c r="N17">
-        <v>8.794088</v>
+        <v>8.694863999999999</v>
       </c>
       <c r="O17">
-        <v>2.6382264</v>
+        <v>2.6084592</v>
       </c>
       <c r="P17">
-        <v>6.1558616</v>
+        <v>6.0864048</v>
       </c>
       <c r="Q17">
-        <v>13.8858616</v>
+        <v>13.8164048</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09253117249473523</v>
+        <v>0.09293894886903485</v>
       </c>
       <c r="T17">
-        <v>1.079241859000814</v>
+        <v>1.088659327229442</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.01114854618039</v>
+        <v>9.087222453717482</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08406071704998927</v>
+        <v>0.08385243747945358</v>
       </c>
       <c r="C18">
-        <v>90.79229005093141</v>
+        <v>89.94324561994041</v>
       </c>
       <c r="D18">
-        <v>110.4422900509314</v>
+        <v>110.8492456199404</v>
       </c>
       <c r="E18">
-        <v>-50.404</v>
+        <v>-49.148</v>
       </c>
       <c r="F18">
-        <v>20.096</v>
+        <v>21.352</v>
       </c>
       <c r="G18">
         <v>0.446</v>
@@ -2751,28 +2751,28 @@
         <v>9.77</v>
       </c>
       <c r="M18">
-        <v>1.075136</v>
+        <v>1.142332</v>
       </c>
       <c r="N18">
-        <v>8.694863999999999</v>
+        <v>8.627668</v>
       </c>
       <c r="O18">
-        <v>2.6084592</v>
+        <v>2.5883004</v>
       </c>
       <c r="P18">
-        <v>6.0864048</v>
+        <v>6.0393676</v>
       </c>
       <c r="Q18">
-        <v>13.8164048</v>
+        <v>13.7693676</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09293894886903485</v>
+        <v>0.09335655118006456</v>
       </c>
       <c r="T18">
-        <v>1.088659327229442</v>
+        <v>1.098303722403339</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.087222453717482</v>
+        <v>8.552679956439984</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08385243747945358</v>
+        <v>0.0836441579089179</v>
       </c>
       <c r="C19">
-        <v>89.94324561994041</v>
+        <v>89.09721136447034</v>
       </c>
       <c r="D19">
-        <v>110.8492456199404</v>
+        <v>111.2592113644703</v>
       </c>
       <c r="E19">
-        <v>-49.148</v>
+        <v>-47.892</v>
       </c>
       <c r="F19">
-        <v>21.352</v>
+        <v>22.608</v>
       </c>
       <c r="G19">
         <v>0.446</v>
@@ -2833,28 +2833,28 @@
         <v>9.77</v>
       </c>
       <c r="M19">
-        <v>1.142332</v>
+        <v>1.209528</v>
       </c>
       <c r="N19">
-        <v>8.627668</v>
+        <v>8.560471999999999</v>
       </c>
       <c r="O19">
-        <v>2.5883004</v>
+        <v>2.5681416</v>
       </c>
       <c r="P19">
-        <v>6.0393676</v>
+        <v>5.992330399999999</v>
       </c>
       <c r="Q19">
-        <v>13.7693676</v>
+        <v>13.7223304</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09335655118006456</v>
+        <v>0.09378433891331452</v>
       </c>
       <c r="T19">
-        <v>1.098303722403339</v>
+        <v>1.108183346727818</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.552679956439984</v>
+        <v>8.077531069971096</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08364415790891791</v>
+        <v>0.08343587833838224</v>
       </c>
       <c r="C20">
-        <v>89.09721136447033</v>
+        <v>88.25422080707352</v>
       </c>
       <c r="D20">
-        <v>111.2592113644703</v>
+        <v>111.6722208070735</v>
       </c>
       <c r="E20">
-        <v>-47.892</v>
+        <v>-46.636</v>
       </c>
       <c r="F20">
-        <v>22.608</v>
+        <v>23.864</v>
       </c>
       <c r="G20">
         <v>0.446</v>
@@ -2915,28 +2915,28 @@
         <v>9.77</v>
       </c>
       <c r="M20">
-        <v>1.209528</v>
+        <v>1.276724</v>
       </c>
       <c r="N20">
-        <v>8.560472000000001</v>
+        <v>8.493276</v>
       </c>
       <c r="O20">
-        <v>2.5681416</v>
+        <v>2.5479828</v>
       </c>
       <c r="P20">
-        <v>5.9923304</v>
+        <v>5.9452932</v>
       </c>
       <c r="Q20">
-        <v>13.7223304</v>
+        <v>13.6752932</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09378433891331452</v>
+        <v>0.09422268930664474</v>
       </c>
       <c r="T20">
-        <v>1.108183346727818</v>
+        <v>1.118306912393643</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.077531069971098</v>
+        <v>7.652397855762091</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08343587833838224</v>
+        <v>0.08333959876784655</v>
       </c>
       <c r="C21">
-        <v>88.25422080707352</v>
+        <v>87.19017716759666</v>
       </c>
       <c r="D21">
-        <v>111.6722208070735</v>
+        <v>111.8641771675967</v>
       </c>
       <c r="E21">
-        <v>-46.636</v>
+        <v>-45.38</v>
       </c>
       <c r="F21">
-        <v>23.864</v>
+        <v>25.12</v>
       </c>
       <c r="G21">
         <v>0.446</v>
@@ -2997,45 +2997,45 @@
         <v>9.77</v>
       </c>
       <c r="M21">
-        <v>1.276724</v>
+        <v>1.364016</v>
       </c>
       <c r="N21">
-        <v>8.493276</v>
+        <v>8.405984</v>
       </c>
       <c r="O21">
-        <v>2.5479828</v>
+        <v>2.5217952</v>
       </c>
       <c r="P21">
-        <v>5.9452932</v>
+        <v>5.8841888</v>
       </c>
       <c r="Q21">
-        <v>13.6752932</v>
+        <v>13.6141888</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09422268930664474</v>
+        <v>0.09467199845980818</v>
       </c>
       <c r="T21">
-        <v>1.118306912393643</v>
+        <v>1.128683567201113</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.652397855762091</v>
+        <v>7.162672578620779</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08333959876784655</v>
+        <v>0.08313691919731087</v>
       </c>
       <c r="C22">
-        <v>87.19017716759666</v>
+        <v>86.3404320365816</v>
       </c>
       <c r="D22">
-        <v>111.8641771675967</v>
+        <v>112.2704320365816</v>
       </c>
       <c r="E22">
-        <v>-45.38</v>
+        <v>-44.124</v>
       </c>
       <c r="F22">
-        <v>25.12</v>
+        <v>26.376</v>
       </c>
       <c r="G22">
         <v>0.446</v>
@@ -3079,28 +3079,28 @@
         <v>9.77</v>
       </c>
       <c r="M22">
-        <v>1.364016</v>
+        <v>1.4322168</v>
       </c>
       <c r="N22">
-        <v>8.405984</v>
+        <v>8.337783199999999</v>
       </c>
       <c r="O22">
-        <v>2.5217952</v>
+        <v>2.501334959999999</v>
       </c>
       <c r="P22">
-        <v>5.8841888</v>
+        <v>5.836448239999999</v>
       </c>
       <c r="Q22">
-        <v>13.6141888</v>
+        <v>13.56644824</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09467199845980818</v>
+        <v>0.09513268252824161</v>
       </c>
       <c r="T22">
-        <v>1.128683567201113</v>
+        <v>1.139322922130291</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.162672578620779</v>
+        <v>6.821592932019787</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08313691919731087</v>
+        <v>0.08293423962677518</v>
       </c>
       <c r="C23">
-        <v>86.3404320365816</v>
+        <v>85.4936484360737</v>
       </c>
       <c r="D23">
-        <v>112.2704320365816</v>
+        <v>112.6796484360737</v>
       </c>
       <c r="E23">
-        <v>-44.124</v>
+        <v>-42.868</v>
       </c>
       <c r="F23">
-        <v>26.376</v>
+        <v>27.632</v>
       </c>
       <c r="G23">
         <v>0.446</v>
@@ -3161,28 +3161,28 @@
         <v>9.77</v>
       </c>
       <c r="M23">
-        <v>1.4322168</v>
+        <v>1.5004176</v>
       </c>
       <c r="N23">
-        <v>8.337783200000001</v>
+        <v>8.269582399999999</v>
       </c>
       <c r="O23">
-        <v>2.50133496</v>
+        <v>2.48087472</v>
       </c>
       <c r="P23">
-        <v>5.836448240000001</v>
+        <v>5.78870768</v>
       </c>
       <c r="Q23">
-        <v>13.56644824</v>
+        <v>13.51870768</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0951326825282416</v>
+        <v>0.09560517900868613</v>
       </c>
       <c r="T23">
-        <v>1.139322922130291</v>
+        <v>1.150235081032012</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.82159293201979</v>
+        <v>6.511520526018889</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08293423962677518</v>
+        <v>0.08273156005623949</v>
       </c>
       <c r="C24">
-        <v>85.4936484360737</v>
+        <v>84.64985886813835</v>
       </c>
       <c r="D24">
-        <v>112.6796484360737</v>
+        <v>113.0918588681384</v>
       </c>
       <c r="E24">
-        <v>-42.868</v>
+        <v>-41.61199999999999</v>
       </c>
       <c r="F24">
-        <v>27.632</v>
+        <v>28.888</v>
       </c>
       <c r="G24">
         <v>0.446</v>
@@ -3243,28 +3243,28 @@
         <v>9.77</v>
       </c>
       <c r="M24">
-        <v>1.5004176</v>
+        <v>1.5686184</v>
       </c>
       <c r="N24">
-        <v>8.269582399999999</v>
+        <v>8.201381599999999</v>
       </c>
       <c r="O24">
-        <v>2.48087472</v>
+        <v>2.46041448</v>
       </c>
       <c r="P24">
-        <v>5.78870768</v>
+        <v>5.74096712</v>
       </c>
       <c r="Q24">
-        <v>13.51870768</v>
+        <v>13.47096712</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09560517900868613</v>
+        <v>0.09608994812498636</v>
       </c>
       <c r="T24">
-        <v>1.150235081032012</v>
+        <v>1.16143067263248</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.511520526018889</v>
+        <v>6.228410937931112</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08273156005623949</v>
+        <v>0.08269688048570384</v>
       </c>
       <c r="C25">
-        <v>84.64985886813835</v>
+        <v>83.46469266200096</v>
       </c>
       <c r="D25">
-        <v>113.0918588681384</v>
+        <v>113.162692662001</v>
       </c>
       <c r="E25">
-        <v>-41.61199999999999</v>
+        <v>-40.35599999999999</v>
       </c>
       <c r="F25">
-        <v>28.888</v>
+        <v>30.144</v>
       </c>
       <c r="G25">
         <v>0.446</v>
@@ -3325,45 +3325,45 @@
         <v>9.77</v>
       </c>
       <c r="M25">
-        <v>1.5686184</v>
+        <v>1.6669632</v>
       </c>
       <c r="N25">
-        <v>8.201381599999999</v>
+        <v>8.1030368</v>
       </c>
       <c r="O25">
-        <v>2.46041448</v>
+        <v>2.43091104</v>
       </c>
       <c r="P25">
-        <v>5.74096712</v>
+        <v>5.67212576</v>
       </c>
       <c r="Q25">
-        <v>13.47096712</v>
+        <v>13.40212576</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09608994812498636</v>
+        <v>0.09658747432329451</v>
       </c>
       <c r="T25">
-        <v>1.16143067263248</v>
+        <v>1.172920885064538</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.228410937931112</v>
+        <v>5.860957218491686</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08269688048570384</v>
+        <v>0.08250120091516815</v>
       </c>
       <c r="C26">
-        <v>83.46469266200097</v>
+        <v>82.61004128338811</v>
       </c>
       <c r="D26">
-        <v>113.162692662001</v>
+        <v>113.5640412833881</v>
       </c>
       <c r="E26">
-        <v>-40.356</v>
+        <v>-39.1</v>
       </c>
       <c r="F26">
-        <v>30.144</v>
+        <v>31.4</v>
       </c>
       <c r="G26">
         <v>0.446</v>
@@ -3407,28 +3407,28 @@
         <v>9.77</v>
       </c>
       <c r="M26">
-        <v>1.6669632</v>
+        <v>1.73642</v>
       </c>
       <c r="N26">
-        <v>8.1030368</v>
+        <v>8.033579999999999</v>
       </c>
       <c r="O26">
-        <v>2.43091104</v>
+        <v>2.410073999999999</v>
       </c>
       <c r="P26">
-        <v>5.67212576</v>
+        <v>5.623505999999999</v>
       </c>
       <c r="Q26">
-        <v>13.40212576</v>
+        <v>13.353506</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09658747432329451</v>
+        <v>0.09709826788689085</v>
       </c>
       <c r="T26">
-        <v>1.172920885064538</v>
+        <v>1.184717503161452</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.860957218491686</v>
+        <v>5.626518929752018</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08250120091516815</v>
+        <v>0.08230552134463245</v>
       </c>
       <c r="C27">
-        <v>82.61004128338811</v>
+        <v>81.75824692492273</v>
       </c>
       <c r="D27">
-        <v>113.5640412833881</v>
+        <v>113.9682469249227</v>
       </c>
       <c r="E27">
-        <v>-39.1</v>
+        <v>-37.844</v>
       </c>
       <c r="F27">
-        <v>31.4</v>
+        <v>32.656</v>
       </c>
       <c r="G27">
         <v>0.446</v>
@@ -3489,28 +3489,28 @@
         <v>9.77</v>
       </c>
       <c r="M27">
-        <v>1.73642</v>
+        <v>1.8058768</v>
       </c>
       <c r="N27">
-        <v>8.033579999999999</v>
+        <v>7.9641232</v>
       </c>
       <c r="O27">
-        <v>2.410073999999999</v>
+        <v>2.38923696</v>
       </c>
       <c r="P27">
-        <v>5.623505999999999</v>
+        <v>5.57488624</v>
       </c>
       <c r="Q27">
-        <v>13.353506</v>
+        <v>13.30488624</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09709826788689085</v>
+        <v>0.09762286668193576</v>
       </c>
       <c r="T27">
-        <v>1.184717503161452</v>
+        <v>1.196832948774498</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.626518929752018</v>
+        <v>5.410114355530786</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08230552134463245</v>
+        <v>0.08210984177409678</v>
       </c>
       <c r="C28">
-        <v>81.75824692492273</v>
+        <v>80.90934020233485</v>
       </c>
       <c r="D28">
-        <v>113.9682469249227</v>
+        <v>114.3753402023349</v>
       </c>
       <c r="E28">
-        <v>-37.844</v>
+        <v>-36.588</v>
       </c>
       <c r="F28">
-        <v>32.656</v>
+        <v>33.912</v>
       </c>
       <c r="G28">
         <v>0.446</v>
@@ -3571,28 +3571,28 @@
         <v>9.77</v>
       </c>
       <c r="M28">
-        <v>1.8058768</v>
+        <v>1.8753336</v>
       </c>
       <c r="N28">
-        <v>7.9641232</v>
+        <v>7.894666399999999</v>
       </c>
       <c r="O28">
-        <v>2.38923696</v>
+        <v>2.36839992</v>
       </c>
       <c r="P28">
-        <v>5.57488624</v>
+        <v>5.526266479999999</v>
       </c>
       <c r="Q28">
-        <v>13.30488624</v>
+        <v>13.25626648</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09762286668193576</v>
+        <v>0.09816183804670793</v>
       </c>
       <c r="T28">
-        <v>1.196832948774498</v>
+        <v>1.20928032440434</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.410114355530786</v>
+        <v>5.209739749770387</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08210984177409678</v>
+        <v>0.0819141622035611</v>
       </c>
       <c r="C29">
-        <v>80.90934020233485</v>
+        <v>80.06335217035891</v>
       </c>
       <c r="D29">
-        <v>114.3753402023349</v>
+        <v>114.7853521703589</v>
       </c>
       <c r="E29">
-        <v>-36.588</v>
+        <v>-35.332</v>
       </c>
       <c r="F29">
-        <v>33.912</v>
+        <v>35.168</v>
       </c>
       <c r="G29">
         <v>0.446</v>
@@ -3653,28 +3653,28 @@
         <v>9.77</v>
       </c>
       <c r="M29">
-        <v>1.8753336</v>
+        <v>1.9447904</v>
       </c>
       <c r="N29">
-        <v>7.894666399999999</v>
+        <v>7.825209599999999</v>
       </c>
       <c r="O29">
-        <v>2.36839992</v>
+        <v>2.347562879999999</v>
       </c>
       <c r="P29">
-        <v>5.526266479999999</v>
+        <v>5.477646719999999</v>
       </c>
       <c r="Q29">
-        <v>13.25626648</v>
+        <v>13.20764672</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09816183804670793</v>
+        <v>0.09871578083827931</v>
       </c>
       <c r="T29">
-        <v>1.20928032440434</v>
+        <v>1.222073460468344</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.209739749770387</v>
+        <v>5.023677615850016</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0819141622035611</v>
+        <v>0.08171848263302542</v>
       </c>
       <c r="C30">
-        <v>80.06335217035891</v>
+        <v>79.22031433063049</v>
       </c>
       <c r="D30">
-        <v>114.7853521703589</v>
+        <v>115.1983143306305</v>
       </c>
       <c r="E30">
-        <v>-35.332</v>
+        <v>-34.076</v>
       </c>
       <c r="F30">
-        <v>35.168</v>
+        <v>36.424</v>
       </c>
       <c r="G30">
         <v>0.446</v>
@@ -3735,28 +3735,28 @@
         <v>9.77</v>
       </c>
       <c r="M30">
-        <v>1.9447904</v>
+        <v>2.0142472</v>
       </c>
       <c r="N30">
-        <v>7.825209599999999</v>
+        <v>7.7557528</v>
       </c>
       <c r="O30">
-        <v>2.347562879999999</v>
+        <v>2.32672584</v>
       </c>
       <c r="P30">
-        <v>5.477646719999999</v>
+        <v>5.42902696</v>
       </c>
       <c r="Q30">
-        <v>13.20764672</v>
+        <v>13.15902696</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09871578083827931</v>
+        <v>0.09928532765214848</v>
       </c>
       <c r="T30">
-        <v>1.222073460468344</v>
+        <v>1.235226966562321</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.023677615850016</v>
+        <v>4.850447353234498</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08171848263302542</v>
+        <v>0.08152280306248973</v>
       </c>
       <c r="C31">
-        <v>79.2203143306305</v>
+        <v>78.38025863975466</v>
       </c>
       <c r="D31">
-        <v>115.1983143306305</v>
+        <v>115.6142586397547</v>
       </c>
       <c r="E31">
-        <v>-34.07600000000001</v>
+        <v>-32.82</v>
       </c>
       <c r="F31">
-        <v>36.42399999999999</v>
+        <v>37.68</v>
       </c>
       <c r="G31">
         <v>0.446</v>
@@ -3817,28 +3817,28 @@
         <v>9.77</v>
       </c>
       <c r="M31">
-        <v>2.0142472</v>
+        <v>2.083704</v>
       </c>
       <c r="N31">
-        <v>7.7557528</v>
+        <v>7.686296</v>
       </c>
       <c r="O31">
-        <v>2.32672584</v>
+        <v>2.3058888</v>
       </c>
       <c r="P31">
-        <v>5.42902696</v>
+        <v>5.3804072</v>
       </c>
       <c r="Q31">
-        <v>13.15902696</v>
+        <v>13.1104072</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09928532765214848</v>
+        <v>0.0998711472321282</v>
       </c>
       <c r="T31">
-        <v>1.235226966562321</v>
+        <v>1.248756287116125</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.850447353234498</v>
+        <v>4.688765774793349</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08152280306248973</v>
+        <v>0.08132712349195405</v>
       </c>
       <c r="C32">
-        <v>78.38025863975466</v>
+        <v>77.54321751754924</v>
       </c>
       <c r="D32">
-        <v>115.6142586397547</v>
+        <v>116.0332175175492</v>
       </c>
       <c r="E32">
-        <v>-32.82</v>
+        <v>-31.564</v>
       </c>
       <c r="F32">
-        <v>37.68</v>
+        <v>38.936</v>
       </c>
       <c r="G32">
         <v>0.446</v>
@@ -3899,28 +3899,28 @@
         <v>9.77</v>
       </c>
       <c r="M32">
-        <v>2.083704</v>
+        <v>2.1531608</v>
       </c>
       <c r="N32">
-        <v>7.686296</v>
+        <v>7.616839199999999</v>
       </c>
       <c r="O32">
-        <v>2.3058888</v>
+        <v>2.28505176</v>
       </c>
       <c r="P32">
-        <v>5.3804072</v>
+        <v>5.331787439999999</v>
       </c>
       <c r="Q32">
-        <v>13.1104072</v>
+        <v>13.06178744</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0998711472321282</v>
+        <v>0.1004739470897885</v>
       </c>
       <c r="T32">
-        <v>1.248756287116125</v>
+        <v>1.26267776188888</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.688765774793349</v>
+        <v>4.537515265929047</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08132712349195405</v>
+        <v>0.08169144392141837</v>
       </c>
       <c r="C33">
-        <v>77.54321751754924</v>
+        <v>75.50961060338065</v>
       </c>
       <c r="D33">
-        <v>116.0332175175492</v>
+        <v>115.2556106033806</v>
       </c>
       <c r="E33">
-        <v>-31.564</v>
+        <v>-30.308</v>
       </c>
       <c r="F33">
-        <v>38.936</v>
+        <v>40.192</v>
       </c>
       <c r="G33">
         <v>0.446</v>
@@ -3981,45 +3981,45 @@
         <v>9.77</v>
       </c>
       <c r="M33">
-        <v>2.1531608</v>
+        <v>2.3230976</v>
       </c>
       <c r="N33">
-        <v>7.616839199999999</v>
+        <v>7.446902399999999</v>
       </c>
       <c r="O33">
-        <v>2.28505176</v>
+        <v>2.23407072</v>
       </c>
       <c r="P33">
-        <v>5.331787439999999</v>
+        <v>5.212831679999999</v>
       </c>
       <c r="Q33">
-        <v>13.06178744</v>
+        <v>12.94283168</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1004739470897885</v>
+        <v>0.101094476355027</v>
       </c>
       <c r="T33">
-        <v>1.26267776188888</v>
+        <v>1.27700869180201</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.537515265929047</v>
+        <v>4.205591706521499</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08169144392141837</v>
+        <v>0.08151326435088269</v>
       </c>
       <c r="C34">
-        <v>75.50961060338065</v>
+        <v>74.6326112979655</v>
       </c>
       <c r="D34">
-        <v>115.2556106033806</v>
+        <v>115.6346112979655</v>
       </c>
       <c r="E34">
-        <v>-30.308</v>
+        <v>-29.052</v>
       </c>
       <c r="F34">
-        <v>40.192</v>
+        <v>41.448</v>
       </c>
       <c r="G34">
         <v>0.446</v>
@@ -4063,28 +4063,28 @@
         <v>9.77</v>
       </c>
       <c r="M34">
-        <v>2.3230976</v>
+        <v>2.3956944</v>
       </c>
       <c r="N34">
-        <v>7.446902399999999</v>
+        <v>7.3743056</v>
       </c>
       <c r="O34">
-        <v>2.23407072</v>
+        <v>2.21229168</v>
       </c>
       <c r="P34">
-        <v>5.212831679999999</v>
+        <v>5.16201392</v>
       </c>
       <c r="Q34">
-        <v>12.94283168</v>
+        <v>12.89201392</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.101094476355027</v>
+        <v>0.1017335288819145</v>
       </c>
       <c r="T34">
-        <v>1.27700869180201</v>
+        <v>1.291767410667771</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.205591706521499</v>
+        <v>4.078149533596605</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08151326435088269</v>
+        <v>0.08216808478034701</v>
       </c>
       <c r="C35">
-        <v>74.6326112979655</v>
+        <v>71.99586733899767</v>
       </c>
       <c r="D35">
-        <v>115.6346112979655</v>
+        <v>114.2538673389977</v>
       </c>
       <c r="E35">
-        <v>-29.052</v>
+        <v>-27.796</v>
       </c>
       <c r="F35">
-        <v>41.448</v>
+        <v>42.704</v>
       </c>
       <c r="G35">
         <v>0.446</v>
@@ -4145,45 +4145,45 @@
         <v>9.77</v>
       </c>
       <c r="M35">
-        <v>2.3956944</v>
+        <v>2.6177552</v>
       </c>
       <c r="N35">
-        <v>7.3743056</v>
+        <v>7.1522448</v>
       </c>
       <c r="O35">
-        <v>2.21229168</v>
+        <v>2.14567344</v>
       </c>
       <c r="P35">
-        <v>5.16201392</v>
+        <v>5.006571360000001</v>
       </c>
       <c r="Q35">
-        <v>12.89201392</v>
+        <v>12.73657136</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1017335288819145</v>
+        <v>0.1023919466368894</v>
       </c>
       <c r="T35">
-        <v>1.291767410667771</v>
+        <v>1.306973363438555</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.078149533596605</v>
+        <v>3.732205364351869</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08216808478034701</v>
+        <v>0.08201440520981133</v>
       </c>
       <c r="C36">
-        <v>71.99586733899767</v>
+        <v>71.06094410416907</v>
       </c>
       <c r="D36">
-        <v>114.2538673389977</v>
+        <v>114.5749441041691</v>
       </c>
       <c r="E36">
-        <v>-27.796</v>
+        <v>-26.54</v>
       </c>
       <c r="F36">
-        <v>42.704</v>
+        <v>43.96</v>
       </c>
       <c r="G36">
         <v>0.446</v>
@@ -4227,28 +4227,28 @@
         <v>9.77</v>
       </c>
       <c r="M36">
-        <v>2.6177552</v>
+        <v>2.694748</v>
       </c>
       <c r="N36">
-        <v>7.1522448</v>
+        <v>7.075251999999999</v>
       </c>
       <c r="O36">
-        <v>2.14567344</v>
+        <v>2.1225756</v>
       </c>
       <c r="P36">
-        <v>5.006571360000001</v>
+        <v>4.9526764</v>
       </c>
       <c r="Q36">
-        <v>12.73657136</v>
+        <v>12.6826764</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1023919466368894</v>
+        <v>0.1030706233997098</v>
       </c>
       <c r="T36">
-        <v>1.306973363438555</v>
+        <v>1.322647191679209</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.732205364351869</v>
+        <v>3.625570925370387</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08201440520981133</v>
+        <v>0.08186072563927567</v>
       </c>
       <c r="C37">
-        <v>71.06094410416907</v>
+        <v>70.12783053780575</v>
       </c>
       <c r="D37">
-        <v>114.5749441041691</v>
+        <v>114.8978305378057</v>
       </c>
       <c r="E37">
-        <v>-26.54</v>
+        <v>-25.284</v>
       </c>
       <c r="F37">
-        <v>43.96</v>
+        <v>45.216</v>
       </c>
       <c r="G37">
         <v>0.446</v>
@@ -4309,28 +4309,28 @@
         <v>9.77</v>
       </c>
       <c r="M37">
-        <v>2.694748</v>
+        <v>2.7717408</v>
       </c>
       <c r="N37">
-        <v>7.075251999999999</v>
+        <v>6.9982592</v>
       </c>
       <c r="O37">
-        <v>2.1225756</v>
+        <v>2.09947776</v>
       </c>
       <c r="P37">
-        <v>4.9526764</v>
+        <v>4.89878144</v>
       </c>
       <c r="Q37">
-        <v>12.6826764</v>
+        <v>12.62878144</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1030706233997098</v>
+        <v>0.1037705088113682</v>
       </c>
       <c r="T37">
-        <v>1.322647191679209</v>
+        <v>1.338810827052384</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.625570925370387</v>
+        <v>3.524860621887876</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08186072563927568</v>
+        <v>0.08243224606873999</v>
       </c>
       <c r="C38">
-        <v>70.12783053780572</v>
+        <v>67.68015034380457</v>
       </c>
       <c r="D38">
-        <v>114.8978305378057</v>
+        <v>113.7061503438046</v>
       </c>
       <c r="E38">
-        <v>-25.28400000000001</v>
+        <v>-24.02800000000001</v>
       </c>
       <c r="F38">
-        <v>45.21599999999999</v>
+        <v>46.47199999999999</v>
       </c>
       <c r="G38">
         <v>0.446</v>
@@ -4391,45 +4391,45 @@
         <v>9.77</v>
       </c>
       <c r="M38">
-        <v>2.771740799999999</v>
+        <v>2.9788552</v>
       </c>
       <c r="N38">
-        <v>6.9982592</v>
+        <v>6.7911448</v>
       </c>
       <c r="O38">
-        <v>2.09947776</v>
+        <v>2.03734344</v>
       </c>
       <c r="P38">
-        <v>4.89878144</v>
+        <v>4.75380136</v>
       </c>
       <c r="Q38">
-        <v>12.62878144</v>
+        <v>12.48380136</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1037705088113682</v>
+        <v>0.1044926128075238</v>
       </c>
       <c r="T38">
-        <v>1.338810827052384</v>
+        <v>1.355487593707247</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.524860621887877</v>
+        <v>3.279783455066899</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08243224606873999</v>
+        <v>0.08229816649820429</v>
       </c>
       <c r="C39">
-        <v>67.68015034380457</v>
+        <v>66.70149558298104</v>
       </c>
       <c r="D39">
-        <v>113.7061503438046</v>
+        <v>113.983495582981</v>
       </c>
       <c r="E39">
-        <v>-24.02800000000001</v>
+        <v>-22.772</v>
       </c>
       <c r="F39">
-        <v>46.47199999999999</v>
+        <v>47.728</v>
       </c>
       <c r="G39">
         <v>0.446</v>
@@ -4473,28 +4473,28 @@
         <v>9.77</v>
       </c>
       <c r="M39">
-        <v>2.9788552</v>
+        <v>3.0593648</v>
       </c>
       <c r="N39">
-        <v>6.7911448</v>
+        <v>6.710635199999999</v>
       </c>
       <c r="O39">
-        <v>2.03734344</v>
+        <v>2.01319056</v>
       </c>
       <c r="P39">
-        <v>4.75380136</v>
+        <v>4.697444639999999</v>
       </c>
       <c r="Q39">
-        <v>12.48380136</v>
+        <v>12.42744464</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1044926128075238</v>
+        <v>0.1052380104809747</v>
       </c>
       <c r="T39">
-        <v>1.355487593707247</v>
+        <v>1.372702320576782</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.279783455066899</v>
+        <v>3.193473364144086</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08229816649820429</v>
+        <v>0.08216408692766861</v>
       </c>
       <c r="C40">
-        <v>66.70149558298104</v>
+        <v>65.72419709813386</v>
       </c>
       <c r="D40">
-        <v>113.983495582981</v>
+        <v>114.2621970981339</v>
       </c>
       <c r="E40">
-        <v>-22.772</v>
+        <v>-21.516</v>
       </c>
       <c r="F40">
-        <v>47.728</v>
+        <v>48.984</v>
       </c>
       <c r="G40">
         <v>0.446</v>
@@ -4555,28 +4555,28 @@
         <v>9.77</v>
       </c>
       <c r="M40">
-        <v>3.0593648</v>
+        <v>3.139874400000001</v>
       </c>
       <c r="N40">
-        <v>6.710635199999999</v>
+        <v>6.6301256</v>
       </c>
       <c r="O40">
-        <v>2.01319056</v>
+        <v>1.98903768</v>
       </c>
       <c r="P40">
-        <v>4.697444639999999</v>
+        <v>4.641087919999999</v>
       </c>
       <c r="Q40">
-        <v>12.42744464</v>
+        <v>12.37108792</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1052380104809747</v>
+        <v>0.1060078474224076</v>
       </c>
       <c r="T40">
-        <v>1.372702320576782</v>
+        <v>1.390481464720729</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.193473364144086</v>
+        <v>3.111589431730135</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08216408692766861</v>
+        <v>0.08203000735713294</v>
       </c>
       <c r="C41">
-        <v>65.72419709813386</v>
+        <v>64.74826486235617</v>
       </c>
       <c r="D41">
-        <v>114.2621970981339</v>
+        <v>114.5422648623562</v>
       </c>
       <c r="E41">
-        <v>-21.516</v>
+        <v>-20.26</v>
       </c>
       <c r="F41">
-        <v>48.984</v>
+        <v>50.24</v>
       </c>
       <c r="G41">
         <v>0.446</v>
@@ -4637,28 +4637,28 @@
         <v>9.77</v>
       </c>
       <c r="M41">
-        <v>3.139874400000001</v>
+        <v>3.220384</v>
       </c>
       <c r="N41">
-        <v>6.6301256</v>
+        <v>6.549615999999999</v>
       </c>
       <c r="O41">
-        <v>1.98903768</v>
+        <v>1.9648848</v>
       </c>
       <c r="P41">
-        <v>4.641087919999999</v>
+        <v>4.5847312</v>
       </c>
       <c r="Q41">
-        <v>12.37108792</v>
+        <v>12.3147312</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1060078474224076</v>
+        <v>0.1068033455952216</v>
       </c>
       <c r="T41">
-        <v>1.390481464720729</v>
+        <v>1.408853247002808</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.111589431730135</v>
+        <v>3.033799695936882</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08203000735713294</v>
+        <v>0.08413452778659725</v>
       </c>
       <c r="C42">
-        <v>64.74826486235617</v>
+        <v>59.24878808173747</v>
       </c>
       <c r="D42">
-        <v>114.5422648623562</v>
+        <v>110.2987880817375</v>
       </c>
       <c r="E42">
-        <v>-20.26</v>
+        <v>-19.004</v>
       </c>
       <c r="F42">
-        <v>50.24</v>
+        <v>51.496</v>
       </c>
       <c r="G42">
         <v>0.446</v>
@@ -4719,45 +4719,45 @@
         <v>9.77</v>
       </c>
       <c r="M42">
-        <v>3.220384</v>
+        <v>3.702562400000001</v>
       </c>
       <c r="N42">
-        <v>6.549615999999999</v>
+        <v>6.067437599999999</v>
       </c>
       <c r="O42">
-        <v>1.9648848</v>
+        <v>1.82023128</v>
       </c>
       <c r="P42">
-        <v>4.5847312</v>
+        <v>4.247206319999999</v>
       </c>
       <c r="Q42">
-        <v>12.3147312</v>
+        <v>11.97720632</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1068033455952216</v>
+        <v>0.107625809807792</v>
       </c>
       <c r="T42">
-        <v>1.408853247002808</v>
+        <v>1.427847801565634</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.033799695936882</v>
+        <v>2.63871312472681</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08413452778659725</v>
+        <v>0.08405504821606158</v>
       </c>
       <c r="C43">
-        <v>59.24878808173747</v>
+        <v>58.14732677324798</v>
       </c>
       <c r="D43">
-        <v>110.2987880817375</v>
+        <v>110.453326773248</v>
       </c>
       <c r="E43">
-        <v>-19.004</v>
+        <v>-17.748</v>
       </c>
       <c r="F43">
-        <v>51.496</v>
+        <v>52.752</v>
       </c>
       <c r="G43">
         <v>0.446</v>
@@ -4801,28 +4801,28 @@
         <v>9.77</v>
       </c>
       <c r="M43">
-        <v>3.702562400000001</v>
+        <v>3.7928688</v>
       </c>
       <c r="N43">
-        <v>6.067437599999999</v>
+        <v>5.977131199999999</v>
       </c>
       <c r="O43">
-        <v>1.82023128</v>
+        <v>1.79313936</v>
       </c>
       <c r="P43">
-        <v>4.247206319999999</v>
+        <v>4.183991839999999</v>
       </c>
       <c r="Q43">
-        <v>11.97720632</v>
+        <v>11.91399184</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.107625809807792</v>
+        <v>0.1084766348552786</v>
       </c>
       <c r="T43">
-        <v>1.427847801565634</v>
+        <v>1.447497340768559</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.63871312472681</v>
+        <v>2.575886621757125</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08405504821606158</v>
+        <v>0.0839755686455259</v>
       </c>
       <c r="C44">
-        <v>58.14732677324798</v>
+        <v>57.04629911803239</v>
       </c>
       <c r="D44">
-        <v>110.453326773248</v>
+        <v>110.6082991180324</v>
       </c>
       <c r="E44">
-        <v>-17.748</v>
+        <v>-16.492</v>
       </c>
       <c r="F44">
-        <v>52.752</v>
+        <v>54.008</v>
       </c>
       <c r="G44">
         <v>0.446</v>
@@ -4883,28 +4883,28 @@
         <v>9.77</v>
       </c>
       <c r="M44">
-        <v>3.7928688</v>
+        <v>3.8831752</v>
       </c>
       <c r="N44">
-        <v>5.9771312</v>
+        <v>5.886824799999999</v>
       </c>
       <c r="O44">
-        <v>1.79313936</v>
+        <v>1.76604744</v>
       </c>
       <c r="P44">
-        <v>4.18399184</v>
+        <v>4.12077736</v>
       </c>
       <c r="Q44">
-        <v>11.91399184</v>
+        <v>11.85077736</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1084766348552786</v>
+        <v>0.1093573134132033</v>
       </c>
       <c r="T44">
-        <v>1.447497340768558</v>
+        <v>1.467836337487375</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.575886621757125</v>
+        <v>2.515982281716261</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0839755686455259</v>
+        <v>0.08509728907499021</v>
       </c>
       <c r="C45">
-        <v>57.04629911803239</v>
+        <v>53.64258504139723</v>
       </c>
       <c r="D45">
-        <v>110.6082991180324</v>
+        <v>108.4605850413972</v>
       </c>
       <c r="E45">
-        <v>-16.492</v>
+        <v>-15.236</v>
       </c>
       <c r="F45">
-        <v>54.008</v>
+        <v>55.264</v>
       </c>
       <c r="G45">
         <v>0.446</v>
@@ -4965,45 +4965,45 @@
         <v>9.77</v>
       </c>
       <c r="M45">
-        <v>3.8831752</v>
+        <v>4.1890112</v>
       </c>
       <c r="N45">
-        <v>5.886824799999999</v>
+        <v>5.580988799999999</v>
       </c>
       <c r="O45">
-        <v>1.76604744</v>
+        <v>1.67429664</v>
       </c>
       <c r="P45">
-        <v>4.12077736</v>
+        <v>3.90669216</v>
       </c>
       <c r="Q45">
-        <v>11.85077736</v>
+        <v>11.63669216</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1093573134132033</v>
+        <v>0.1102694447767682</v>
       </c>
       <c r="T45">
-        <v>1.467836337487375</v>
+        <v>1.488901726946149</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.515982281716261</v>
+        <v>2.332292642234997</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08509728907499021</v>
+        <v>0.08504510950445454</v>
       </c>
       <c r="C46">
-        <v>53.64258504139723</v>
+        <v>52.48463987652482</v>
       </c>
       <c r="D46">
-        <v>108.4605850413972</v>
+        <v>108.5586398765248</v>
       </c>
       <c r="E46">
-        <v>-15.236</v>
+        <v>-13.98</v>
       </c>
       <c r="F46">
-        <v>55.264</v>
+        <v>56.52</v>
       </c>
       <c r="G46">
         <v>0.446</v>
@@ -5047,28 +5047,28 @@
         <v>9.77</v>
       </c>
       <c r="M46">
-        <v>4.1890112</v>
+        <v>4.284216</v>
       </c>
       <c r="N46">
-        <v>5.580988799999999</v>
+        <v>5.485784</v>
       </c>
       <c r="O46">
-        <v>1.67429664</v>
+        <v>1.6457352</v>
       </c>
       <c r="P46">
-        <v>3.90669216</v>
+        <v>3.8400488</v>
       </c>
       <c r="Q46">
-        <v>11.63669216</v>
+        <v>11.5700488</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1102694447767682</v>
+        <v>0.1112147445535537</v>
       </c>
       <c r="T46">
-        <v>1.488901726946149</v>
+        <v>1.51073313056706</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.332292642234997</v>
+        <v>2.280463916851998</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08504510950445454</v>
+        <v>0.08499292993391885</v>
       </c>
       <c r="C47">
-        <v>52.48463987652482</v>
+        <v>51.32687216691624</v>
       </c>
       <c r="D47">
-        <v>108.5586398765248</v>
+        <v>108.6568721669162</v>
       </c>
       <c r="E47">
-        <v>-13.98</v>
+        <v>-12.724</v>
       </c>
       <c r="F47">
-        <v>56.52</v>
+        <v>57.776</v>
       </c>
       <c r="G47">
         <v>0.446</v>
@@ -5129,28 +5129,28 @@
         <v>9.77</v>
       </c>
       <c r="M47">
-        <v>4.284216</v>
+        <v>4.379420800000001</v>
       </c>
       <c r="N47">
-        <v>5.485784</v>
+        <v>5.390579199999999</v>
       </c>
       <c r="O47">
-        <v>1.6457352</v>
+        <v>1.61717376</v>
       </c>
       <c r="P47">
-        <v>3.8400488</v>
+        <v>3.773405439999999</v>
       </c>
       <c r="Q47">
-        <v>11.5700488</v>
+        <v>11.50340544</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1112147445535537</v>
+        <v>0.1121950554331831</v>
       </c>
       <c r="T47">
-        <v>1.51073313056706</v>
+        <v>1.533373104692449</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.280463916851998</v>
+        <v>2.230888614311737</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08499292993391885</v>
+        <v>0.08494075036338319</v>
       </c>
       <c r="C48">
-        <v>51.32687216691624</v>
+        <v>50.16928239473364</v>
       </c>
       <c r="D48">
-        <v>108.6568721669162</v>
+        <v>108.7552823947336</v>
       </c>
       <c r="E48">
-        <v>-12.724</v>
+        <v>-11.468</v>
       </c>
       <c r="F48">
-        <v>57.776</v>
+        <v>59.032</v>
       </c>
       <c r="G48">
         <v>0.446</v>
@@ -5211,28 +5211,28 @@
         <v>9.77</v>
       </c>
       <c r="M48">
-        <v>4.379420800000001</v>
+        <v>4.4746256</v>
       </c>
       <c r="N48">
-        <v>5.390579199999999</v>
+        <v>5.295374399999999</v>
       </c>
       <c r="O48">
-        <v>1.61717376</v>
+        <v>1.58861232</v>
       </c>
       <c r="P48">
-        <v>3.773405439999999</v>
+        <v>3.706762079999999</v>
       </c>
       <c r="Q48">
-        <v>11.50340544</v>
+        <v>11.43676208</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1121950554331831</v>
+        <v>0.1132123591761947</v>
       </c>
       <c r="T48">
-        <v>1.533373104692449</v>
+        <v>1.55686741746408</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.230888614311737</v>
+        <v>2.183422899113615</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08494075036338319</v>
+        <v>0.08488857079284749</v>
       </c>
       <c r="C49">
-        <v>50.16928239473364</v>
+        <v>49.01187104388772</v>
       </c>
       <c r="D49">
-        <v>108.7552823947336</v>
+        <v>108.8538710438877</v>
       </c>
       <c r="E49">
-        <v>-11.468</v>
+        <v>-10.212</v>
       </c>
       <c r="F49">
-        <v>59.032</v>
+        <v>60.288</v>
       </c>
       <c r="G49">
         <v>0.446</v>
@@ -5293,28 +5293,28 @@
         <v>9.77</v>
       </c>
       <c r="M49">
-        <v>4.4746256</v>
+        <v>4.569830400000001</v>
       </c>
       <c r="N49">
-        <v>5.295374399999999</v>
+        <v>5.200169599999999</v>
       </c>
       <c r="O49">
-        <v>1.58861232</v>
+        <v>1.56005088</v>
       </c>
       <c r="P49">
-        <v>3.706762079999999</v>
+        <v>3.640118719999999</v>
       </c>
       <c r="Q49">
-        <v>11.43676208</v>
+        <v>11.37011872</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1132123591761947</v>
+        <v>0.1142687899862452</v>
       </c>
       <c r="T49">
-        <v>1.55686741746408</v>
+        <v>1.581265357650004</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.183422899113615</v>
+        <v>2.137934922048748</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08488857079284749</v>
+        <v>0.08483639122231182</v>
       </c>
       <c r="C50">
-        <v>49.01187104388772</v>
+        <v>47.85463860004521</v>
       </c>
       <c r="D50">
-        <v>108.8538710438877</v>
+        <v>108.9526386000452</v>
       </c>
       <c r="E50">
-        <v>-10.212</v>
+        <v>-8.956000000000003</v>
       </c>
       <c r="F50">
-        <v>60.288</v>
+        <v>61.544</v>
       </c>
       <c r="G50">
         <v>0.446</v>
@@ -5375,28 +5375,28 @@
         <v>9.77</v>
       </c>
       <c r="M50">
-        <v>4.5698304</v>
+        <v>4.6650352</v>
       </c>
       <c r="N50">
-        <v>5.2001696</v>
+        <v>5.104964799999999</v>
       </c>
       <c r="O50">
-        <v>1.56005088</v>
+        <v>1.53148944</v>
       </c>
       <c r="P50">
-        <v>3.64011872</v>
+        <v>3.57347536</v>
       </c>
       <c r="Q50">
-        <v>11.37011872</v>
+        <v>11.30347536</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1142687899862452</v>
+        <v>0.1153666494555134</v>
       </c>
       <c r="T50">
-        <v>1.581265357650004</v>
+        <v>1.606620079804004</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.137934922048748</v>
+        <v>2.094303597108977</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08483639122231182</v>
+        <v>0.08478421165177613</v>
       </c>
       <c r="C51">
-        <v>47.85463860004521</v>
+        <v>46.6975855506373</v>
       </c>
       <c r="D51">
-        <v>108.9526386000452</v>
+        <v>109.0515855506373</v>
       </c>
       <c r="E51">
-        <v>-8.956000000000003</v>
+        <v>-7.700000000000003</v>
       </c>
       <c r="F51">
-        <v>61.544</v>
+        <v>62.8</v>
       </c>
       <c r="G51">
         <v>0.446</v>
@@ -5457,28 +5457,28 @@
         <v>9.77</v>
       </c>
       <c r="M51">
-        <v>4.6650352</v>
+        <v>4.76024</v>
       </c>
       <c r="N51">
-        <v>5.104964799999999</v>
+        <v>5.009759999999999</v>
       </c>
       <c r="O51">
-        <v>1.53148944</v>
+        <v>1.502928</v>
       </c>
       <c r="P51">
-        <v>3.57347536</v>
+        <v>3.506831999999999</v>
       </c>
       <c r="Q51">
-        <v>11.30347536</v>
+        <v>11.236832</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1153666494555134</v>
+        <v>0.1165084233035523</v>
       </c>
       <c r="T51">
-        <v>1.606620079804004</v>
+        <v>1.632988990844163</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.094303597108977</v>
+        <v>2.052417525166798</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08478421165177613</v>
+        <v>0.08473203208124044</v>
       </c>
       <c r="C52">
-        <v>46.6975855506373</v>
+        <v>45.54071238486739</v>
       </c>
       <c r="D52">
-        <v>109.0515855506373</v>
+        <v>109.1507123848674</v>
       </c>
       <c r="E52">
-        <v>-7.700000000000003</v>
+        <v>-6.444000000000003</v>
       </c>
       <c r="F52">
-        <v>62.8</v>
+        <v>64.056</v>
       </c>
       <c r="G52">
         <v>0.446</v>
@@ -5539,28 +5539,28 @@
         <v>9.77</v>
       </c>
       <c r="M52">
-        <v>4.76024</v>
+        <v>4.8554448</v>
       </c>
       <c r="N52">
-        <v>5.009759999999999</v>
+        <v>4.9145552</v>
       </c>
       <c r="O52">
-        <v>1.502928</v>
+        <v>1.47436656</v>
       </c>
       <c r="P52">
-        <v>3.506831999999999</v>
+        <v>3.44018864</v>
       </c>
       <c r="Q52">
-        <v>11.236832</v>
+        <v>11.17018864</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1165084233035523</v>
+        <v>0.1176968001657968</v>
       </c>
       <c r="T52">
-        <v>1.632988990844163</v>
+        <v>1.660434183967595</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.052417525166798</v>
+        <v>2.012174044281175</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08473203208124044</v>
+        <v>0.08984865251070479</v>
       </c>
       <c r="C53">
-        <v>45.54071238486739</v>
+        <v>35.35191816950879</v>
       </c>
       <c r="D53">
-        <v>109.1507123848674</v>
+        <v>100.2179181695088</v>
       </c>
       <c r="E53">
-        <v>-6.444000000000003</v>
+        <v>-5.188000000000002</v>
       </c>
       <c r="F53">
-        <v>64.056</v>
+        <v>65.312</v>
       </c>
       <c r="G53">
         <v>0.446</v>
@@ -5621,45 +5621,45 @@
         <v>9.77</v>
       </c>
       <c r="M53">
-        <v>4.8554448</v>
+        <v>5.87808</v>
       </c>
       <c r="N53">
-        <v>4.9145552</v>
+        <v>3.89192</v>
       </c>
       <c r="O53">
-        <v>1.47436656</v>
+        <v>1.167576</v>
       </c>
       <c r="P53">
-        <v>3.44018864</v>
+        <v>2.724344</v>
       </c>
       <c r="Q53">
-        <v>11.17018864</v>
+        <v>10.454344</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1176968001657968</v>
+        <v>0.1189346927306349</v>
       </c>
       <c r="T53">
-        <v>1.660434183967595</v>
+        <v>1.689022926804502</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.012174044281175</v>
+        <v>1.662107354782514</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08984865251070479</v>
+        <v>0.0898958729401691</v>
       </c>
       <c r="C54">
-        <v>35.35191816950879</v>
+        <v>34.02028279285663</v>
       </c>
       <c r="D54">
-        <v>100.2179181695088</v>
+        <v>100.1422827928566</v>
       </c>
       <c r="E54">
-        <v>-5.188000000000002</v>
+        <v>-3.932000000000002</v>
       </c>
       <c r="F54">
-        <v>65.312</v>
+        <v>66.568</v>
       </c>
       <c r="G54">
         <v>0.446</v>
@@ -5703,28 +5703,28 @@
         <v>9.77</v>
       </c>
       <c r="M54">
-        <v>5.87808</v>
+        <v>5.99112</v>
       </c>
       <c r="N54">
-        <v>3.89192</v>
+        <v>3.77888</v>
       </c>
       <c r="O54">
-        <v>1.167576</v>
+        <v>1.133664</v>
       </c>
       <c r="P54">
-        <v>2.724344</v>
+        <v>2.645216</v>
       </c>
       <c r="Q54">
-        <v>10.454344</v>
+        <v>10.375216</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1189346927306349</v>
+        <v>0.1202252615748279</v>
       </c>
       <c r="T54">
-        <v>1.689022926804502</v>
+        <v>1.718828211889789</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.662107354782514</v>
+        <v>1.630746838654542</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0898958729401691</v>
+        <v>0.08994309336963341</v>
       </c>
       <c r="C55">
-        <v>34.02028279285663</v>
+        <v>32.68876149552463</v>
       </c>
       <c r="D55">
-        <v>100.1422827928566</v>
+        <v>100.0667614955246</v>
       </c>
       <c r="E55">
-        <v>-3.932000000000002</v>
+        <v>-2.676000000000002</v>
       </c>
       <c r="F55">
-        <v>66.568</v>
+        <v>67.824</v>
       </c>
       <c r="G55">
         <v>0.446</v>
@@ -5785,28 +5785,28 @@
         <v>9.77</v>
       </c>
       <c r="M55">
-        <v>5.99112</v>
+        <v>6.104159999999999</v>
       </c>
       <c r="N55">
-        <v>3.77888</v>
+        <v>3.66584</v>
       </c>
       <c r="O55">
-        <v>1.133664</v>
+        <v>1.099752</v>
       </c>
       <c r="P55">
-        <v>2.645216</v>
+        <v>2.566088</v>
       </c>
       <c r="Q55">
-        <v>10.375216</v>
+        <v>10.296088</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1202252615748279</v>
+        <v>0.1215719421078987</v>
       </c>
       <c r="T55">
-        <v>1.718828211889789</v>
+        <v>1.749929378935305</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.630746838654542</v>
+        <v>1.600547823123903</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08994309336963341</v>
+        <v>0.08999031379909772</v>
       </c>
       <c r="C56">
-        <v>32.68876149552463</v>
+        <v>31.35735401961192</v>
       </c>
       <c r="D56">
-        <v>100.0667614955246</v>
+        <v>99.99135401961192</v>
       </c>
       <c r="E56">
-        <v>-2.676000000000002</v>
+        <v>-1.420000000000002</v>
       </c>
       <c r="F56">
-        <v>67.824</v>
+        <v>69.08</v>
       </c>
       <c r="G56">
         <v>0.446</v>
@@ -5867,28 +5867,28 @@
         <v>9.77</v>
       </c>
       <c r="M56">
-        <v>6.104159999999999</v>
+        <v>6.2172</v>
       </c>
       <c r="N56">
-        <v>3.66584</v>
+        <v>3.5528</v>
       </c>
       <c r="O56">
-        <v>1.099752</v>
+        <v>1.06584</v>
       </c>
       <c r="P56">
-        <v>2.566088</v>
+        <v>2.48696</v>
       </c>
       <c r="Q56">
-        <v>10.296088</v>
+        <v>10.21696</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1215719421078987</v>
+        <v>0.1229784751091061</v>
       </c>
       <c r="T56">
-        <v>1.749929378935305</v>
+        <v>1.782412820071734</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.600547823123903</v>
+        <v>1.571446953612559</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08999031379909772</v>
+        <v>0.09003753422856206</v>
       </c>
       <c r="C57">
-        <v>31.35735401961192</v>
+        <v>30.02606010799444</v>
       </c>
       <c r="D57">
-        <v>99.99135401961192</v>
+        <v>99.91606010799444</v>
       </c>
       <c r="E57">
-        <v>-1.420000000000002</v>
+        <v>-0.1640000000000015</v>
       </c>
       <c r="F57">
-        <v>69.08</v>
+        <v>70.336</v>
       </c>
       <c r="G57">
         <v>0.446</v>
@@ -5949,28 +5949,28 @@
         <v>9.77</v>
       </c>
       <c r="M57">
-        <v>6.2172</v>
+        <v>6.33024</v>
       </c>
       <c r="N57">
-        <v>3.5528</v>
+        <v>3.43976</v>
       </c>
       <c r="O57">
-        <v>1.06584</v>
+        <v>1.031928</v>
       </c>
       <c r="P57">
-        <v>2.48696</v>
+        <v>2.407832</v>
       </c>
       <c r="Q57">
-        <v>10.21696</v>
+        <v>10.137832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1229784751091061</v>
+        <v>0.1244489414285501</v>
       </c>
       <c r="T57">
-        <v>1.782412820071734</v>
+        <v>1.816372781259818</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.571446953612559</v>
+        <v>1.543385400869477</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09003753422856206</v>
+        <v>0.09008475465802637</v>
       </c>
       <c r="C58">
-        <v>30.02606010799444</v>
+        <v>28.69487950432215</v>
       </c>
       <c r="D58">
-        <v>99.91606010799444</v>
+        <v>99.84087950432215</v>
       </c>
       <c r="E58">
-        <v>-0.1640000000000015</v>
+        <v>1.091999999999999</v>
       </c>
       <c r="F58">
-        <v>70.336</v>
+        <v>71.592</v>
       </c>
       <c r="G58">
         <v>0.446</v>
@@ -6031,28 +6031,28 @@
         <v>9.77</v>
       </c>
       <c r="M58">
-        <v>6.33024</v>
+        <v>6.44328</v>
       </c>
       <c r="N58">
-        <v>3.43976</v>
+        <v>3.32672</v>
       </c>
       <c r="O58">
-        <v>1.031928</v>
+        <v>0.9980159999999999</v>
       </c>
       <c r="P58">
-        <v>2.407832</v>
+        <v>2.328704</v>
       </c>
       <c r="Q58">
-        <v>10.137832</v>
+        <v>10.058704</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1244489414285501</v>
+        <v>0.1259878015302939</v>
       </c>
       <c r="T58">
-        <v>1.816372781259818</v>
+        <v>1.851912275526418</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.543385400869477</v>
+        <v>1.516308464012118</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09008475465802637</v>
+        <v>0.1160253626166144</v>
       </c>
       <c r="C59">
-        <v>28.69487950432215</v>
+        <v>-1.760833731803416</v>
       </c>
       <c r="D59">
-        <v>99.84087950432215</v>
+        <v>70.64116626819659</v>
       </c>
       <c r="E59">
-        <v>1.091999999999999</v>
+        <v>2.347999999999999</v>
       </c>
       <c r="F59">
-        <v>71.592</v>
+        <v>72.848</v>
       </c>
       <c r="G59">
         <v>0.446</v>
@@ -6113,45 +6113,45 @@
         <v>9.77</v>
       </c>
       <c r="M59">
-        <v>6.44328</v>
+        <v>10.6940864</v>
       </c>
       <c r="N59">
-        <v>3.32672</v>
+        <v>-0.924086400000002</v>
       </c>
       <c r="O59">
-        <v>0.9980159999999999</v>
+        <v>-0.2772259200000006</v>
       </c>
       <c r="P59">
-        <v>2.328704</v>
+        <v>-0.6468604800000014</v>
       </c>
       <c r="Q59">
-        <v>10.058704</v>
+        <v>7.083139519999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1259878015302939</v>
+        <v>0.1290889282803832</v>
       </c>
       <c r="T59">
-        <v>1.851912275526418</v>
+        <v>1.923531830955733</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.3</v>
+        <v>0.2740767084133526</v>
       </c>
       <c r="W59">
-        <v>0.063</v>
+        <v>0.1065655392049198</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.516308464012118</v>
+        <v>0.9135890280445086</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1160253626166145</v>
+        <v>0.1170353626166145</v>
       </c>
       <c r="C60">
-        <v>-1.760833731803402</v>
+        <v>-3.812172004816745</v>
       </c>
       <c r="D60">
-        <v>70.64116626819659</v>
+        <v>69.84582799518326</v>
       </c>
       <c r="E60">
-        <v>2.347999999999985</v>
+        <v>3.603999999999999</v>
       </c>
       <c r="F60">
-        <v>72.84799999999998</v>
+        <v>74.104</v>
       </c>
       <c r="G60">
         <v>0.446</v>
@@ -6195,37 +6195,37 @@
         <v>9.77</v>
       </c>
       <c r="M60">
-        <v>10.6940864</v>
+        <v>10.8784672</v>
       </c>
       <c r="N60">
-        <v>-0.9240863999999984</v>
+        <v>-1.108467200000002</v>
       </c>
       <c r="O60">
-        <v>-0.2772259199999995</v>
+        <v>-0.3325401600000005</v>
       </c>
       <c r="P60">
-        <v>-0.6468604799999988</v>
+        <v>-0.7759270400000011</v>
       </c>
       <c r="Q60">
-        <v>7.083139520000001</v>
+        <v>6.95407296</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1290889282803832</v>
+        <v>0.1311203655555145</v>
       </c>
       <c r="T60">
-        <v>1.923531830955733</v>
+        <v>1.970447241466848</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2740767084133527</v>
+        <v>0.2694313404741432</v>
       </c>
       <c r="W60">
-        <v>0.1065655392049198</v>
+        <v>0.1072474792183958</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9135890280445089</v>
+        <v>0.8981044682471441</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1170353626166145</v>
+        <v>0.1180453626166145</v>
       </c>
       <c r="C61">
-        <v>-3.812172004816745</v>
+        <v>-5.845800481624835</v>
       </c>
       <c r="D61">
-        <v>69.84582799518326</v>
+        <v>69.06819951837517</v>
       </c>
       <c r="E61">
-        <v>3.603999999999999</v>
+        <v>4.859999999999999</v>
       </c>
       <c r="F61">
-        <v>74.104</v>
+        <v>75.36</v>
       </c>
       <c r="G61">
         <v>0.446</v>
@@ -6277,37 +6277,37 @@
         <v>9.77</v>
       </c>
       <c r="M61">
-        <v>10.8784672</v>
+        <v>11.062848</v>
       </c>
       <c r="N61">
-        <v>-1.108467200000002</v>
+        <v>-1.292848000000001</v>
       </c>
       <c r="O61">
-        <v>-0.3325401600000005</v>
+        <v>-0.3878544000000003</v>
       </c>
       <c r="P61">
-        <v>-0.7759270400000011</v>
+        <v>-0.9049936000000007</v>
       </c>
       <c r="Q61">
-        <v>6.95407296</v>
+        <v>6.825006399999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1311203655555145</v>
+        <v>0.1332533746944024</v>
       </c>
       <c r="T61">
-        <v>1.970447241466848</v>
+        <v>2.019708422503519</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2694313404741432</v>
+        <v>0.2649408181329075</v>
       </c>
       <c r="W61">
-        <v>0.1072474792183958</v>
+        <v>0.1079066878980892</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8981044682471441</v>
+        <v>0.8831360604430251</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1180453626166145</v>
+        <v>0.1190553626166145</v>
       </c>
       <c r="C62">
-        <v>-5.845800481624835</v>
+        <v>-7.862304165109251</v>
       </c>
       <c r="D62">
-        <v>69.06819951837517</v>
+        <v>68.30769583489075</v>
       </c>
       <c r="E62">
-        <v>4.859999999999999</v>
+        <v>6.116</v>
       </c>
       <c r="F62">
-        <v>75.36</v>
+        <v>76.616</v>
       </c>
       <c r="G62">
         <v>0.446</v>
@@ -6359,37 +6359,37 @@
         <v>9.77</v>
       </c>
       <c r="M62">
-        <v>11.062848</v>
+        <v>11.2472288</v>
       </c>
       <c r="N62">
-        <v>-1.292848000000001</v>
+        <v>-1.477228800000001</v>
       </c>
       <c r="O62">
-        <v>-0.3878544000000003</v>
+        <v>-0.4431686400000002</v>
       </c>
       <c r="P62">
-        <v>-0.9049936000000007</v>
+        <v>-1.034060160000001</v>
       </c>
       <c r="Q62">
-        <v>6.825006399999999</v>
+        <v>6.695939839999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1332533746944024</v>
+        <v>0.1354957689173358</v>
       </c>
       <c r="T62">
-        <v>2.019708422503519</v>
+        <v>2.071495817952327</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2649408181329075</v>
+        <v>0.260597526032368</v>
       </c>
       <c r="W62">
-        <v>0.1079066878980892</v>
+        <v>0.1085442831784484</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8831360604430251</v>
+        <v>0.8686584201078935</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1190553626166145</v>
+        <v>0.1200653626166145</v>
       </c>
       <c r="C63">
-        <v>-7.862304165109251</v>
+        <v>-9.862242573110279</v>
       </c>
       <c r="D63">
-        <v>68.30769583489075</v>
+        <v>67.56375742688972</v>
       </c>
       <c r="E63">
-        <v>6.116</v>
+        <v>7.372</v>
       </c>
       <c r="F63">
-        <v>76.616</v>
+        <v>77.872</v>
       </c>
       <c r="G63">
         <v>0.446</v>
@@ -6441,37 +6441,37 @@
         <v>9.77</v>
       </c>
       <c r="M63">
-        <v>11.2472288</v>
+        <v>11.4316096</v>
       </c>
       <c r="N63">
-        <v>-1.477228800000001</v>
+        <v>-1.661609600000002</v>
       </c>
       <c r="O63">
-        <v>-0.4431686400000002</v>
+        <v>-0.4984828800000006</v>
       </c>
       <c r="P63">
-        <v>-1.034060160000001</v>
+        <v>-1.163126720000002</v>
       </c>
       <c r="Q63">
-        <v>6.695939839999999</v>
+        <v>6.566873279999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1354957689173358</v>
+        <v>0.1378561838888446</v>
       </c>
       <c r="T63">
-        <v>2.071495817952327</v>
+        <v>2.126008865793178</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.260597526032368</v>
+        <v>0.2563943401286202</v>
       </c>
       <c r="W63">
-        <v>0.1085442831784484</v>
+        <v>0.1091613108691186</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8686584201078935</v>
+        <v>0.8546478004287339</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1200653626166145</v>
+        <v>0.1210753626166144</v>
       </c>
       <c r="C64">
-        <v>-9.862242573110279</v>
+        <v>-11.84615111126196</v>
       </c>
       <c r="D64">
-        <v>67.56375742688972</v>
+        <v>66.83584888873804</v>
       </c>
       <c r="E64">
-        <v>7.372</v>
+        <v>8.628</v>
       </c>
       <c r="F64">
-        <v>77.872</v>
+        <v>79.128</v>
       </c>
       <c r="G64">
         <v>0.446</v>
@@ -6523,37 +6523,37 @@
         <v>9.77</v>
       </c>
       <c r="M64">
-        <v>11.4316096</v>
+        <v>11.6159904</v>
       </c>
       <c r="N64">
-        <v>-1.661609600000002</v>
+        <v>-1.845990400000002</v>
       </c>
       <c r="O64">
-        <v>-0.4984828800000006</v>
+        <v>-0.5537971200000005</v>
       </c>
       <c r="P64">
-        <v>-1.163126720000002</v>
+        <v>-1.292193280000001</v>
       </c>
       <c r="Q64">
-        <v>6.566873279999999</v>
+        <v>6.437806719999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1378561838888446</v>
+        <v>0.1403441888588134</v>
       </c>
       <c r="T64">
-        <v>2.126008865793178</v>
+        <v>2.183468564868669</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2563943401286202</v>
+        <v>0.2523245886980072</v>
       </c>
       <c r="W64">
-        <v>0.1091613108691186</v>
+        <v>0.1097587503791325</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8546478004287339</v>
+        <v>0.8410819623266905</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1210753626166144</v>
+        <v>0.1220853626166145</v>
       </c>
       <c r="C65">
-        <v>-11.84615111126196</v>
+        <v>-13.81454235803039</v>
       </c>
       <c r="D65">
-        <v>66.83584888873804</v>
+        <v>66.12345764196961</v>
       </c>
       <c r="E65">
-        <v>8.628</v>
+        <v>9.884</v>
       </c>
       <c r="F65">
-        <v>79.128</v>
+        <v>80.384</v>
       </c>
       <c r="G65">
         <v>0.446</v>
@@ -6605,37 +6605,37 @@
         <v>9.77</v>
       </c>
       <c r="M65">
-        <v>11.6159904</v>
+        <v>11.8003712</v>
       </c>
       <c r="N65">
-        <v>-1.845990400000002</v>
+        <v>-2.030371200000001</v>
       </c>
       <c r="O65">
-        <v>-0.5537971200000005</v>
+        <v>-0.6091113600000003</v>
       </c>
       <c r="P65">
-        <v>-1.292193280000001</v>
+        <v>-1.421259840000001</v>
       </c>
       <c r="Q65">
-        <v>6.437806719999999</v>
+        <v>6.308740159999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1403441888588134</v>
+        <v>0.1429704163271138</v>
       </c>
       <c r="T65">
-        <v>2.183468564868669</v>
+        <v>2.244120469448355</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2523245886980072</v>
+        <v>0.2483820169996008</v>
       </c>
       <c r="W65">
-        <v>0.1097587503791325</v>
+        <v>0.1103375199044586</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8410819623266905</v>
+        <v>0.827940056665336</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1220853626166145</v>
+        <v>0.1230953626166145</v>
       </c>
       <c r="C66">
-        <v>-13.81454235803039</v>
+        <v>-15.76790726843669</v>
       </c>
       <c r="D66">
-        <v>66.12345764196961</v>
+        <v>65.42609273156332</v>
       </c>
       <c r="E66">
-        <v>9.884</v>
+        <v>11.14</v>
       </c>
       <c r="F66">
-        <v>80.384</v>
+        <v>81.64</v>
       </c>
       <c r="G66">
         <v>0.446</v>
@@ -6687,37 +6687,37 @@
         <v>9.77</v>
       </c>
       <c r="M66">
-        <v>11.8003712</v>
+        <v>11.984752</v>
       </c>
       <c r="N66">
-        <v>-2.030371200000001</v>
+        <v>-2.214752000000002</v>
       </c>
       <c r="O66">
-        <v>-0.6091113600000003</v>
+        <v>-0.6644256000000007</v>
       </c>
       <c r="P66">
-        <v>-1.421259840000001</v>
+        <v>-1.550326400000002</v>
       </c>
       <c r="Q66">
-        <v>6.308740159999999</v>
+        <v>6.179673599999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1429704163271138</v>
+        <v>0.1457467139364599</v>
       </c>
       <c r="T66">
-        <v>2.244120469448355</v>
+        <v>2.308238197146879</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2483820169996008</v>
+        <v>0.2445607551996069</v>
       </c>
       <c r="W66">
-        <v>0.1103375199044586</v>
+        <v>0.1108984811366977</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.827940056665336</v>
+        <v>0.815202517332023</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1230953626166145</v>
+        <v>0.1241053626166145</v>
       </c>
       <c r="C67">
-        <v>-15.76790726843669</v>
+        <v>-17.70671630240538</v>
       </c>
       <c r="D67">
-        <v>65.42609273156332</v>
+        <v>64.74328369759462</v>
       </c>
       <c r="E67">
-        <v>11.14</v>
+        <v>12.396</v>
       </c>
       <c r="F67">
-        <v>81.64</v>
+        <v>82.896</v>
       </c>
       <c r="G67">
         <v>0.446</v>
@@ -6769,37 +6769,37 @@
         <v>9.77</v>
       </c>
       <c r="M67">
-        <v>11.984752</v>
+        <v>12.1691328</v>
       </c>
       <c r="N67">
-        <v>-2.214752000000002</v>
+        <v>-2.399132800000002</v>
       </c>
       <c r="O67">
-        <v>-0.6644256000000007</v>
+        <v>-0.7197398400000006</v>
       </c>
       <c r="P67">
-        <v>-1.550326400000002</v>
+        <v>-1.679392960000001</v>
       </c>
       <c r="Q67">
-        <v>6.179673599999999</v>
+        <v>6.050607039999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1457467139364599</v>
+        <v>0.1486863231698851</v>
       </c>
       <c r="T67">
-        <v>2.308238197146879</v>
+        <v>2.376127555886493</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2445607551996069</v>
+        <v>0.2408552892117341</v>
       </c>
       <c r="W67">
-        <v>0.1108984811366977</v>
+        <v>0.1114424435437174</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.815202517332023</v>
+        <v>0.8028509640391136</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1241053626166145</v>
+        <v>0.1630734471596581</v>
       </c>
       <c r="C68">
-        <v>-17.70671630240538</v>
+        <v>-37.54841940642585</v>
       </c>
       <c r="D68">
-        <v>64.74328369759462</v>
+        <v>46.15758059357415</v>
       </c>
       <c r="E68">
-        <v>12.396</v>
+        <v>13.652</v>
       </c>
       <c r="F68">
-        <v>82.896</v>
+        <v>84.152</v>
       </c>
       <c r="G68">
         <v>0.446</v>
@@ -6851,45 +6851,45 @@
         <v>9.77</v>
       </c>
       <c r="M68">
-        <v>12.1691328</v>
+        <v>16.8977216</v>
       </c>
       <c r="N68">
-        <v>-2.399132800000002</v>
+        <v>-7.127721600000001</v>
       </c>
       <c r="O68">
-        <v>-0.7197398400000006</v>
+        <v>-2.13831648</v>
       </c>
       <c r="P68">
-        <v>-1.679392960000001</v>
+        <v>-4.989405120000001</v>
       </c>
       <c r="Q68">
-        <v>6.050607039999999</v>
+        <v>2.74059488</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1486863231698851</v>
+        <v>0.1571922255175896</v>
       </c>
       <c r="T68">
-        <v>2.376127555886493</v>
+        <v>2.57256871865103</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.2408552892117341</v>
+        <v>0.1734553373160083</v>
       </c>
       <c r="W68">
-        <v>0.1114424435437174</v>
+        <v>0.1659701682669456</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8028509640391136</v>
+        <v>0.5781844577200277</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1630734471596581</v>
+        <v>0.1646234471596581</v>
       </c>
       <c r="C69">
-        <v>-37.54841940642585</v>
+        <v>-39.32551701477139</v>
       </c>
       <c r="D69">
-        <v>46.15758059357415</v>
+        <v>45.63648298522861</v>
       </c>
       <c r="E69">
-        <v>13.652</v>
+        <v>14.908</v>
       </c>
       <c r="F69">
-        <v>84.152</v>
+        <v>85.408</v>
       </c>
       <c r="G69">
         <v>0.446</v>
@@ -6933,37 +6933,37 @@
         <v>9.77</v>
       </c>
       <c r="M69">
-        <v>16.8977216</v>
+        <v>17.1499264</v>
       </c>
       <c r="N69">
-        <v>-7.127721600000001</v>
+        <v>-7.379926400000002</v>
       </c>
       <c r="O69">
-        <v>-2.13831648</v>
+        <v>-2.21397792</v>
       </c>
       <c r="P69">
-        <v>-4.989405120000001</v>
+        <v>-5.165948480000002</v>
       </c>
       <c r="Q69">
-        <v>2.74059488</v>
+        <v>2.564051519999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1571922255175896</v>
+        <v>0.1606732325650143</v>
       </c>
       <c r="T69">
-        <v>2.57256871865103</v>
+        <v>2.652961491108875</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1734553373160083</v>
+        <v>0.1709045235319493</v>
       </c>
       <c r="W69">
-        <v>0.1659701682669456</v>
+        <v>0.1664823716747846</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5781844577200277</v>
+        <v>0.5696817451064979</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1646234471596581</v>
+        <v>0.1661734471596581</v>
       </c>
       <c r="C70">
-        <v>-39.32551701477139</v>
+        <v>-41.09098007270193</v>
       </c>
       <c r="D70">
-        <v>45.63648298522861</v>
+        <v>45.12701992729807</v>
       </c>
       <c r="E70">
-        <v>14.908</v>
+        <v>16.164</v>
       </c>
       <c r="F70">
-        <v>85.408</v>
+        <v>86.664</v>
       </c>
       <c r="G70">
         <v>0.446</v>
@@ -7015,37 +7015,37 @@
         <v>9.77</v>
       </c>
       <c r="M70">
-        <v>17.1499264</v>
+        <v>17.4021312</v>
       </c>
       <c r="N70">
-        <v>-7.379926400000002</v>
+        <v>-7.6321312</v>
       </c>
       <c r="O70">
-        <v>-2.21397792</v>
+        <v>-2.28963936</v>
       </c>
       <c r="P70">
-        <v>-5.165948480000002</v>
+        <v>-5.34249184</v>
       </c>
       <c r="Q70">
-        <v>2.564051519999999</v>
+        <v>2.38750816</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1606732325650143</v>
+        <v>0.1643788207122728</v>
       </c>
       <c r="T70">
-        <v>2.652961491108875</v>
+        <v>2.738540894047871</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1709045235319493</v>
+        <v>0.1684276463793124</v>
       </c>
       <c r="W70">
-        <v>0.1664823716747846</v>
+        <v>0.1669797286070341</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5696817451064979</v>
+        <v>0.5614254879310414</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1661734471596581</v>
+        <v>0.1677234471596581</v>
       </c>
       <c r="C71">
-        <v>-41.09098007270193</v>
+        <v>-42.8451939254627</v>
       </c>
       <c r="D71">
-        <v>45.12701992729807</v>
+        <v>44.6288060745373</v>
       </c>
       <c r="E71">
-        <v>16.164</v>
+        <v>17.42</v>
       </c>
       <c r="F71">
-        <v>86.664</v>
+        <v>87.92</v>
       </c>
       <c r="G71">
         <v>0.446</v>
@@ -7097,37 +7097,37 @@
         <v>9.77</v>
       </c>
       <c r="M71">
-        <v>17.4021312</v>
+        <v>17.654336</v>
       </c>
       <c r="N71">
-        <v>-7.6321312</v>
+        <v>-7.884336000000001</v>
       </c>
       <c r="O71">
-        <v>-2.28963936</v>
+        <v>-2.3653008</v>
       </c>
       <c r="P71">
-        <v>-5.34249184</v>
+        <v>-5.519035200000001</v>
       </c>
       <c r="Q71">
-        <v>2.38750816</v>
+        <v>2.210964799999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1643788207122728</v>
+        <v>0.1683314480693486</v>
       </c>
       <c r="T71">
-        <v>2.738540894047871</v>
+        <v>2.829825590516133</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1684276463793124</v>
+        <v>0.1660215371453223</v>
       </c>
       <c r="W71">
-        <v>0.1669797286070341</v>
+        <v>0.1674628753412193</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5614254879310414</v>
+        <v>0.5534051238177409</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1677234471596581</v>
+        <v>0.1692734471596581</v>
       </c>
       <c r="C72">
-        <v>-42.8451939254627</v>
+        <v>-44.58852708688152</v>
       </c>
       <c r="D72">
-        <v>44.6288060745373</v>
+        <v>44.14147291311848</v>
       </c>
       <c r="E72">
-        <v>17.42</v>
+        <v>18.676</v>
       </c>
       <c r="F72">
-        <v>87.92</v>
+        <v>89.176</v>
       </c>
       <c r="G72">
         <v>0.446</v>
@@ -7179,37 +7179,37 @@
         <v>9.77</v>
       </c>
       <c r="M72">
-        <v>17.654336</v>
+        <v>17.9065408</v>
       </c>
       <c r="N72">
-        <v>-7.884336000000001</v>
+        <v>-8.136540800000002</v>
       </c>
       <c r="O72">
-        <v>-2.3653008</v>
+        <v>-2.440962240000001</v>
       </c>
       <c r="P72">
-        <v>-5.519035200000001</v>
+        <v>-5.695578560000001</v>
       </c>
       <c r="Q72">
-        <v>2.210964799999999</v>
+        <v>2.034421439999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1683314480693486</v>
+        <v>0.1725566704165675</v>
       </c>
       <c r="T72">
-        <v>2.829825590516133</v>
+        <v>2.927405783292552</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1660215371453223</v>
+        <v>0.1636832056362332</v>
       </c>
       <c r="W72">
-        <v>0.1674628753412193</v>
+        <v>0.1679324123082444</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5534051238177409</v>
+        <v>0.5456106854541106</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1692734471596581</v>
+        <v>0.1708234471596581</v>
       </c>
       <c r="C73">
-        <v>-44.58852708688151</v>
+        <v>-46.32133214841232</v>
       </c>
       <c r="D73">
-        <v>44.14147291311848</v>
+        <v>43.66466785158767</v>
       </c>
       <c r="E73">
-        <v>18.67599999999999</v>
+        <v>19.93199999999999</v>
       </c>
       <c r="F73">
-        <v>89.17599999999999</v>
+        <v>90.43199999999999</v>
       </c>
       <c r="G73">
         <v>0.446</v>
@@ -7261,37 +7261,37 @@
         <v>9.77</v>
       </c>
       <c r="M73">
-        <v>17.9065408</v>
+        <v>18.1587456</v>
       </c>
       <c r="N73">
-        <v>-8.136540799999999</v>
+        <v>-8.3887456</v>
       </c>
       <c r="O73">
-        <v>-2.44096224</v>
+        <v>-2.51662368</v>
       </c>
       <c r="P73">
-        <v>-5.69557856</v>
+        <v>-5.87212192</v>
       </c>
       <c r="Q73">
-        <v>2.034421440000001</v>
+        <v>1.857878080000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1725566704165675</v>
+        <v>0.1770836943600163</v>
       </c>
       <c r="T73">
-        <v>2.927405783292551</v>
+        <v>3.031955989838713</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1636832056362332</v>
+        <v>0.1614098277801744</v>
       </c>
       <c r="W73">
-        <v>0.1679324123082444</v>
+        <v>0.168388906581741</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5456106854541107</v>
+        <v>0.538032759267248</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1708234471596581</v>
+        <v>0.1723734471596581</v>
       </c>
       <c r="C74">
-        <v>-46.32133214841232</v>
+        <v>-48.04394662989294</v>
       </c>
       <c r="D74">
-        <v>43.66466785158767</v>
+        <v>43.19805337010705</v>
       </c>
       <c r="E74">
-        <v>19.93199999999999</v>
+        <v>21.18799999999999</v>
       </c>
       <c r="F74">
-        <v>90.43199999999999</v>
+        <v>91.68799999999999</v>
       </c>
       <c r="G74">
         <v>0.446</v>
@@ -7343,37 +7343,37 @@
         <v>9.77</v>
       </c>
       <c r="M74">
-        <v>18.1587456</v>
+        <v>18.4109504</v>
       </c>
       <c r="N74">
-        <v>-8.3887456</v>
+        <v>-8.640950399999998</v>
       </c>
       <c r="O74">
-        <v>-2.51662368</v>
+        <v>-2.592285119999999</v>
       </c>
       <c r="P74">
-        <v>-5.87212192</v>
+        <v>-6.048665279999998</v>
       </c>
       <c r="Q74">
-        <v>1.857878080000001</v>
+        <v>1.681334720000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1770836943600163</v>
+        <v>0.1819460534103872</v>
       </c>
       <c r="T74">
-        <v>3.031955989838713</v>
+        <v>3.144250656129036</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1614098277801744</v>
+        <v>0.1591987342489392</v>
       </c>
       <c r="W74">
-        <v>0.168388906581741</v>
+        <v>0.168832894162813</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.538032759267248</v>
+        <v>0.5306624474964639</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1723734471596581</v>
+        <v>0.1739234471596581</v>
       </c>
       <c r="C75">
-        <v>-48.04394662989294</v>
+        <v>-49.75669377633063</v>
       </c>
       <c r="D75">
-        <v>43.19805337010705</v>
+        <v>42.74130622366936</v>
       </c>
       <c r="E75">
-        <v>21.18799999999999</v>
+        <v>22.44399999999999</v>
       </c>
       <c r="F75">
-        <v>91.68799999999999</v>
+        <v>92.94399999999999</v>
       </c>
       <c r="G75">
         <v>0.446</v>
@@ -7425,37 +7425,37 @@
         <v>9.77</v>
       </c>
       <c r="M75">
-        <v>18.4109504</v>
+        <v>18.6631552</v>
       </c>
       <c r="N75">
-        <v>-8.640950399999998</v>
+        <v>-8.893155199999999</v>
       </c>
       <c r="O75">
-        <v>-2.592285119999999</v>
+        <v>-2.667946559999999</v>
       </c>
       <c r="P75">
-        <v>-6.048665279999998</v>
+        <v>-6.22520864</v>
       </c>
       <c r="Q75">
-        <v>1.681334720000002</v>
+        <v>1.50479136</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1819460534103872</v>
+        <v>0.1871824400800176</v>
       </c>
       <c r="T75">
-        <v>3.144250656129036</v>
+        <v>3.26518337367246</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1591987342489392</v>
+        <v>0.1570474000023319</v>
       </c>
       <c r="W75">
-        <v>0.168832894162813</v>
+        <v>0.1692648820795318</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5306624474964639</v>
+        <v>0.5234913333411062</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1739234471596581</v>
+        <v>0.1754734471596581</v>
       </c>
       <c r="C76">
-        <v>-49.75669377633063</v>
+        <v>-51.45988330466856</v>
       </c>
       <c r="D76">
-        <v>42.74130622366936</v>
+        <v>42.29411669533143</v>
       </c>
       <c r="E76">
-        <v>22.44399999999999</v>
+        <v>23.69999999999999</v>
       </c>
       <c r="F76">
-        <v>92.94399999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="G76">
         <v>0.446</v>
@@ -7507,37 +7507,37 @@
         <v>9.77</v>
       </c>
       <c r="M76">
-        <v>18.6631552</v>
+        <v>18.91536</v>
       </c>
       <c r="N76">
-        <v>-8.893155199999999</v>
+        <v>-9.14536</v>
       </c>
       <c r="O76">
-        <v>-2.667946559999999</v>
+        <v>-2.743608</v>
       </c>
       <c r="P76">
-        <v>-6.22520864</v>
+        <v>-6.401752</v>
       </c>
       <c r="Q76">
-        <v>1.50479136</v>
+        <v>1.328248</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1871824400800176</v>
+        <v>0.1928377376832183</v>
       </c>
       <c r="T76">
-        <v>3.26518337367246</v>
+        <v>3.395790708619359</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1570474000023319</v>
+        <v>0.1549534346689674</v>
       </c>
       <c r="W76">
-        <v>0.1692648820795318</v>
+        <v>0.1696853503184713</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5234913333411062</v>
+        <v>0.5165114488965581</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1754734471596581</v>
+        <v>0.1770234471596581</v>
       </c>
       <c r="C77">
-        <v>-51.45988330466856</v>
+        <v>-53.15381210415855</v>
       </c>
       <c r="D77">
-        <v>42.29411669533143</v>
+        <v>41.85618789584146</v>
       </c>
       <c r="E77">
-        <v>23.69999999999999</v>
+        <v>24.956</v>
       </c>
       <c r="F77">
-        <v>94.19999999999999</v>
+        <v>95.456</v>
       </c>
       <c r="G77">
         <v>0.446</v>
@@ -7589,37 +7589,37 @@
         <v>9.77</v>
       </c>
       <c r="M77">
-        <v>18.91536</v>
+        <v>19.1675648</v>
       </c>
       <c r="N77">
-        <v>-9.14536</v>
+        <v>-9.397564800000001</v>
       </c>
       <c r="O77">
-        <v>-2.743608</v>
+        <v>-2.81926944</v>
       </c>
       <c r="P77">
-        <v>-6.401752</v>
+        <v>-6.578295360000001</v>
       </c>
       <c r="Q77">
-        <v>1.328248</v>
+        <v>1.151704639999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1928377376832183</v>
+        <v>0.1989643100866857</v>
       </c>
       <c r="T77">
-        <v>3.395790708619359</v>
+        <v>3.537281988145166</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1549534346689674</v>
+        <v>0.152914573686481</v>
       </c>
       <c r="W77">
-        <v>0.1696853503184713</v>
+        <v>0.1700947536037546</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5165114488965581</v>
+        <v>0.5097152456216034</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1770234471596581</v>
+        <v>0.1785734471596581</v>
       </c>
       <c r="C78">
-        <v>-53.15381210415855</v>
+        <v>-54.8387648936681</v>
       </c>
       <c r="D78">
-        <v>41.85618789584146</v>
+        <v>41.42723510633191</v>
       </c>
       <c r="E78">
-        <v>24.956</v>
+        <v>26.212</v>
       </c>
       <c r="F78">
-        <v>95.456</v>
+        <v>96.712</v>
       </c>
       <c r="G78">
         <v>0.446</v>
@@ -7671,37 +7671,37 @@
         <v>9.77</v>
       </c>
       <c r="M78">
-        <v>19.1675648</v>
+        <v>19.4197696</v>
       </c>
       <c r="N78">
-        <v>-9.397564800000001</v>
+        <v>-9.649769600000003</v>
       </c>
       <c r="O78">
-        <v>-2.81926944</v>
+        <v>-2.894930880000001</v>
       </c>
       <c r="P78">
-        <v>-6.578295360000001</v>
+        <v>-6.754838720000002</v>
       </c>
       <c r="Q78">
-        <v>1.151704639999999</v>
+        <v>0.9751612799999982</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1989643100866857</v>
+        <v>0.2056236279165416</v>
       </c>
       <c r="T78">
-        <v>3.537281988145166</v>
+        <v>3.691076857194956</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.152914573686481</v>
+        <v>0.1509286701321111</v>
       </c>
       <c r="W78">
-        <v>0.1700947536037546</v>
+        <v>0.1704935230374721</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5097152456216034</v>
+        <v>0.5030955671070371</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1785734471596581</v>
+        <v>0.2081409257496557</v>
       </c>
       <c r="C79">
-        <v>-54.8387648936681</v>
+        <v>-62.86916949998767</v>
       </c>
       <c r="D79">
-        <v>41.42723510633191</v>
+        <v>34.65283050001234</v>
       </c>
       <c r="E79">
-        <v>26.212</v>
+        <v>27.468</v>
       </c>
       <c r="F79">
-        <v>96.712</v>
+        <v>97.968</v>
       </c>
       <c r="G79">
         <v>0.446</v>
@@ -7753,45 +7753,45 @@
         <v>9.77</v>
       </c>
       <c r="M79">
-        <v>19.4197696</v>
+        <v>23.1008544</v>
       </c>
       <c r="N79">
-        <v>-9.649769600000003</v>
+        <v>-13.3308544</v>
       </c>
       <c r="O79">
-        <v>-2.894930880000001</v>
+        <v>-3.999256320000001</v>
       </c>
       <c r="P79">
-        <v>-6.754838720000002</v>
+        <v>-9.331598080000003</v>
       </c>
       <c r="Q79">
-        <v>0.9751612799999982</v>
+        <v>-1.601598080000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2056236279165416</v>
+        <v>0.2161496045945555</v>
       </c>
       <c r="T79">
-        <v>3.691076857194956</v>
+        <v>3.934171006802668</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1509286701321111</v>
+        <v>0.1268784240291995</v>
       </c>
       <c r="W79">
-        <v>0.1704935230374721</v>
+        <v>0.2058820676139148</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5030955671070371</v>
+        <v>0.4229280800973317</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2081409257496557</v>
+        <v>0.2100409257496557</v>
       </c>
       <c r="C80">
-        <v>-62.86916949998767</v>
+        <v>-64.4855185692725</v>
       </c>
       <c r="D80">
-        <v>34.65283050001234</v>
+        <v>34.29248143072751</v>
       </c>
       <c r="E80">
-        <v>27.468</v>
+        <v>28.724</v>
       </c>
       <c r="F80">
-        <v>97.968</v>
+        <v>99.224</v>
       </c>
       <c r="G80">
         <v>0.446</v>
@@ -7835,37 +7835,37 @@
         <v>9.77</v>
       </c>
       <c r="M80">
-        <v>23.1008544</v>
+        <v>23.3970192</v>
       </c>
       <c r="N80">
-        <v>-13.3308544</v>
+        <v>-13.6270192</v>
       </c>
       <c r="O80">
-        <v>-3.999256320000001</v>
+        <v>-4.08810576</v>
       </c>
       <c r="P80">
-        <v>-9.331598080000003</v>
+        <v>-9.538913440000002</v>
       </c>
       <c r="Q80">
-        <v>-1.601598080000002</v>
+        <v>-1.808913440000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2161496045945555</v>
+        <v>0.2242614905276296</v>
       </c>
       <c r="T80">
-        <v>3.934171006802668</v>
+        <v>4.121512483317082</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1268784240291995</v>
+        <v>0.1252723680288299</v>
       </c>
       <c r="W80">
-        <v>0.2058820676139148</v>
+        <v>0.2062607756188019</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4229280800973317</v>
+        <v>0.4175745600960997</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2100409257496557</v>
+        <v>0.2119409257496558</v>
       </c>
       <c r="C81">
-        <v>-64.4855185692725</v>
+        <v>-66.0944503486493</v>
       </c>
       <c r="D81">
-        <v>34.29248143072751</v>
+        <v>33.93954965135071</v>
       </c>
       <c r="E81">
-        <v>28.724</v>
+        <v>29.98</v>
       </c>
       <c r="F81">
-        <v>99.224</v>
+        <v>100.48</v>
       </c>
       <c r="G81">
         <v>0.446</v>
@@ -7917,37 +7917,37 @@
         <v>9.77</v>
       </c>
       <c r="M81">
-        <v>23.3970192</v>
+        <v>23.693184</v>
       </c>
       <c r="N81">
-        <v>-13.6270192</v>
+        <v>-13.923184</v>
       </c>
       <c r="O81">
-        <v>-4.08810576</v>
+        <v>-4.176955200000001</v>
       </c>
       <c r="P81">
-        <v>-9.538913440000002</v>
+        <v>-9.746228800000001</v>
       </c>
       <c r="Q81">
-        <v>-1.808913440000001</v>
+        <v>-2.0162288</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2242614905276296</v>
+        <v>0.2331845650540111</v>
       </c>
       <c r="T81">
-        <v>4.121512483317082</v>
+        <v>4.327588107482936</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1252723680288299</v>
+        <v>0.1237064634284695</v>
       </c>
       <c r="W81">
-        <v>0.2062607756188019</v>
+        <v>0.2066300159235669</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4175745600960997</v>
+        <v>0.4123548780948985</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2119409257496558</v>
+        <v>0.2138409257496557</v>
       </c>
       <c r="C82">
-        <v>-66.0944503486493</v>
+        <v>-67.69619151724368</v>
       </c>
       <c r="D82">
-        <v>33.93954965135071</v>
+        <v>33.59380848275632</v>
       </c>
       <c r="E82">
-        <v>29.98</v>
+        <v>31.236</v>
       </c>
       <c r="F82">
-        <v>100.48</v>
+        <v>101.736</v>
       </c>
       <c r="G82">
         <v>0.446</v>
@@ -7999,37 +7999,37 @@
         <v>9.77</v>
       </c>
       <c r="M82">
-        <v>23.693184</v>
+        <v>23.9893488</v>
       </c>
       <c r="N82">
-        <v>-13.923184</v>
+        <v>-14.2193488</v>
       </c>
       <c r="O82">
-        <v>-4.176955200000001</v>
+        <v>-4.265804640000001</v>
       </c>
       <c r="P82">
-        <v>-9.746228800000001</v>
+        <v>-9.953544160000002</v>
       </c>
       <c r="Q82">
-        <v>-2.0162288</v>
+        <v>-2.223544160000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2331845650540111</v>
+        <v>0.2430469105831696</v>
       </c>
       <c r="T82">
-        <v>4.327588107482936</v>
+        <v>4.555355902613617</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1237064634284695</v>
+        <v>0.1221792231392292</v>
       </c>
       <c r="W82">
-        <v>0.2066300159235669</v>
+        <v>0.2069901391837698</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4123548780948985</v>
+        <v>0.407264077130764</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2138409257496557</v>
+        <v>0.2157409257496558</v>
       </c>
       <c r="C83">
-        <v>-67.69619151724368</v>
+        <v>-69.29095961063283</v>
       </c>
       <c r="D83">
-        <v>33.59380848275632</v>
+        <v>33.25504038936718</v>
       </c>
       <c r="E83">
-        <v>31.236</v>
+        <v>32.492</v>
       </c>
       <c r="F83">
-        <v>101.736</v>
+        <v>102.992</v>
       </c>
       <c r="G83">
         <v>0.446</v>
@@ -8081,37 +8081,37 @@
         <v>9.77</v>
       </c>
       <c r="M83">
-        <v>23.9893488</v>
+        <v>24.2855136</v>
       </c>
       <c r="N83">
-        <v>-14.2193488</v>
+        <v>-14.5155136</v>
       </c>
       <c r="O83">
-        <v>-4.265804640000001</v>
+        <v>-4.35465408</v>
       </c>
       <c r="P83">
-        <v>-9.953544160000002</v>
+        <v>-10.16085952</v>
       </c>
       <c r="Q83">
-        <v>-2.223544160000001</v>
+        <v>-2.430859520000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2430469105831696</v>
+        <v>0.2540050722822346</v>
       </c>
       <c r="T83">
-        <v>4.555355902613617</v>
+        <v>4.808431230536595</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1221792231392292</v>
+        <v>0.120689232613141</v>
       </c>
       <c r="W83">
-        <v>0.2069901391837698</v>
+        <v>0.2073414789498214</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.407264077130764</v>
+        <v>0.4022974420438034</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2157409257496558</v>
+        <v>0.2176409257496557</v>
       </c>
       <c r="C84">
-        <v>-69.29095961063283</v>
+        <v>-70.87896347727127</v>
       </c>
       <c r="D84">
-        <v>33.25504038936718</v>
+        <v>32.92303652272873</v>
       </c>
       <c r="E84">
-        <v>32.492</v>
+        <v>33.748</v>
       </c>
       <c r="F84">
-        <v>102.992</v>
+        <v>104.248</v>
       </c>
       <c r="G84">
         <v>0.446</v>
@@ -8163,37 +8163,37 @@
         <v>9.77</v>
       </c>
       <c r="M84">
-        <v>24.2855136</v>
+        <v>24.5816784</v>
       </c>
       <c r="N84">
-        <v>-14.5155136</v>
+        <v>-14.8116784</v>
       </c>
       <c r="O84">
-        <v>-4.35465408</v>
+        <v>-4.44350352</v>
       </c>
       <c r="P84">
-        <v>-10.16085952</v>
+        <v>-10.36817488</v>
       </c>
       <c r="Q84">
-        <v>-2.430859520000002</v>
+        <v>-2.638174880000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2540050722822346</v>
+        <v>0.2662524294753072</v>
       </c>
       <c r="T84">
-        <v>4.808431230536595</v>
+        <v>5.091280126450513</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.120689232613141</v>
+        <v>0.1192351454732237</v>
       </c>
       <c r="W84">
-        <v>0.2073414789498214</v>
+        <v>0.2076843526974139</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4022974420438034</v>
+        <v>0.3974504849107455</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2176409257496557</v>
+        <v>0.2195409257496558</v>
       </c>
       <c r="C85">
-        <v>-70.87896347727127</v>
+        <v>-72.46040370784678</v>
       </c>
       <c r="D85">
-        <v>32.92303652272873</v>
+        <v>32.59759629215323</v>
       </c>
       <c r="E85">
-        <v>33.748</v>
+        <v>35.004</v>
       </c>
       <c r="F85">
-        <v>104.248</v>
+        <v>105.504</v>
       </c>
       <c r="G85">
         <v>0.446</v>
@@ -8245,37 +8245,37 @@
         <v>9.77</v>
       </c>
       <c r="M85">
-        <v>24.5816784</v>
+        <v>24.8778432</v>
       </c>
       <c r="N85">
-        <v>-14.8116784</v>
+        <v>-15.1078432</v>
       </c>
       <c r="O85">
-        <v>-4.44350352</v>
+        <v>-4.53235296</v>
       </c>
       <c r="P85">
-        <v>-10.36817488</v>
+        <v>-10.57549024</v>
       </c>
       <c r="Q85">
-        <v>-2.638174880000001</v>
+        <v>-2.84549024</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2662524294753072</v>
+        <v>0.280030706317514</v>
       </c>
       <c r="T85">
-        <v>5.091280126450513</v>
+        <v>5.409485134353671</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1192351454732237</v>
+        <v>0.1178156794556853</v>
       </c>
       <c r="W85">
-        <v>0.2076843526974139</v>
+        <v>0.2080190627843494</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3974504849107455</v>
+        <v>0.392718931518951</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2195409257496557</v>
+        <v>0.2214409257496557</v>
       </c>
       <c r="C86">
-        <v>-72.46040370784675</v>
+        <v>-74.03547303942059</v>
       </c>
       <c r="D86">
-        <v>32.59759629215325</v>
+        <v>32.27852696057941</v>
       </c>
       <c r="E86">
-        <v>35.00399999999999</v>
+        <v>36.25999999999999</v>
       </c>
       <c r="F86">
-        <v>105.504</v>
+        <v>106.76</v>
       </c>
       <c r="G86">
         <v>0.446</v>
@@ -8327,37 +8327,37 @@
         <v>9.77</v>
       </c>
       <c r="M86">
-        <v>24.8778432</v>
+        <v>25.174008</v>
       </c>
       <c r="N86">
-        <v>-15.1078432</v>
+        <v>-15.404008</v>
       </c>
       <c r="O86">
-        <v>-4.532352959999999</v>
+        <v>-4.6212024</v>
       </c>
       <c r="P86">
-        <v>-10.57549024</v>
+        <v>-10.7828056</v>
       </c>
       <c r="Q86">
-        <v>-2.845490239999998</v>
+        <v>-3.052805599999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2800307063175138</v>
+        <v>0.2956460867386814</v>
       </c>
       <c r="T86">
-        <v>5.409485134353667</v>
+        <v>5.770117476643913</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1178156794556853</v>
+        <v>0.1164296126385596</v>
       </c>
       <c r="W86">
-        <v>0.2080190627843494</v>
+        <v>0.2083458973398277</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.392718931518951</v>
+        <v>0.3880987087951986</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2214409257496557</v>
+        <v>0.2233409257496557</v>
       </c>
       <c r="C87">
-        <v>-74.03547303942059</v>
+        <v>-75.60435673606321</v>
       </c>
       <c r="D87">
-        <v>32.27852696057941</v>
+        <v>31.96564326393678</v>
       </c>
       <c r="E87">
-        <v>36.25999999999999</v>
+        <v>37.51599999999999</v>
       </c>
       <c r="F87">
-        <v>106.76</v>
+        <v>108.016</v>
       </c>
       <c r="G87">
         <v>0.446</v>
@@ -8409,37 +8409,37 @@
         <v>9.77</v>
       </c>
       <c r="M87">
-        <v>25.174008</v>
+        <v>25.4701728</v>
       </c>
       <c r="N87">
-        <v>-15.404008</v>
+        <v>-15.7001728</v>
       </c>
       <c r="O87">
-        <v>-4.6212024</v>
+        <v>-4.71005184</v>
       </c>
       <c r="P87">
-        <v>-10.7828056</v>
+        <v>-10.99012096</v>
       </c>
       <c r="Q87">
-        <v>-3.052805599999999</v>
+        <v>-3.26012096</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2956460867386814</v>
+        <v>0.3134922357914444</v>
       </c>
       <c r="T87">
-        <v>5.770117476643913</v>
+        <v>6.182268724975621</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1164296126385596</v>
+        <v>0.11507577993346</v>
       </c>
       <c r="W87">
-        <v>0.2083458973398277</v>
+        <v>0.2086651310916901</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3880987087951986</v>
+        <v>0.3835859331115334</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2233409257496557</v>
+        <v>0.2252409257496557</v>
       </c>
       <c r="C88">
-        <v>-75.60435673606321</v>
+        <v>-77.16723294756474</v>
       </c>
       <c r="D88">
-        <v>31.96564326393678</v>
+        <v>31.65876705243524</v>
       </c>
       <c r="E88">
-        <v>37.51599999999999</v>
+        <v>38.77199999999999</v>
       </c>
       <c r="F88">
-        <v>108.016</v>
+        <v>109.272</v>
       </c>
       <c r="G88">
         <v>0.446</v>
@@ -8491,37 +8491,37 @@
         <v>9.77</v>
       </c>
       <c r="M88">
-        <v>25.4701728</v>
+        <v>25.7663376</v>
       </c>
       <c r="N88">
-        <v>-15.7001728</v>
+        <v>-15.9963376</v>
       </c>
       <c r="O88">
-        <v>-4.71005184</v>
+        <v>-4.79890128</v>
       </c>
       <c r="P88">
-        <v>-10.99012096</v>
+        <v>-11.19743632</v>
       </c>
       <c r="Q88">
-        <v>-3.26012096</v>
+        <v>-3.467436320000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3134922357914444</v>
+        <v>0.3340839462369401</v>
       </c>
       <c r="T88">
-        <v>6.182268724975621</v>
+        <v>6.657827857666053</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.11507577993346</v>
+        <v>0.1137530698192823</v>
       </c>
       <c r="W88">
-        <v>0.2086651310916901</v>
+        <v>0.2089770261366132</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3835859331115334</v>
+        <v>0.3791768993976078</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2252409257496557</v>
+        <v>0.2271409257496557</v>
       </c>
       <c r="C89">
-        <v>-77.16723294756474</v>
+        <v>-78.72427304768013</v>
       </c>
       <c r="D89">
-        <v>31.65876705243524</v>
+        <v>31.35772695231987</v>
       </c>
       <c r="E89">
-        <v>38.77199999999999</v>
+        <v>40.02799999999999</v>
       </c>
       <c r="F89">
-        <v>109.272</v>
+        <v>110.528</v>
       </c>
       <c r="G89">
         <v>0.446</v>
@@ -8573,37 +8573,37 @@
         <v>9.77</v>
       </c>
       <c r="M89">
-        <v>25.7663376</v>
+        <v>26.0625024</v>
       </c>
       <c r="N89">
-        <v>-15.9963376</v>
+        <v>-16.2925024</v>
       </c>
       <c r="O89">
-        <v>-4.79890128</v>
+        <v>-4.88775072</v>
       </c>
       <c r="P89">
-        <v>-11.19743632</v>
+        <v>-11.40475168</v>
       </c>
       <c r="Q89">
-        <v>-3.467436320000001</v>
+        <v>-3.67475168</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3340839462369401</v>
+        <v>0.3581076084233518</v>
       </c>
       <c r="T89">
-        <v>6.657827857666053</v>
+        <v>7.212646845804891</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1137530698192823</v>
+        <v>0.1124604212986087</v>
       </c>
       <c r="W89">
-        <v>0.2089770261366132</v>
+        <v>0.2092818326577881</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3791768993976078</v>
+        <v>0.3748680709953622</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2271409257496557</v>
+        <v>0.2290409257496557</v>
       </c>
       <c r="C90">
-        <v>-78.72427304768013</v>
+        <v>-80.27564195325765</v>
       </c>
       <c r="D90">
-        <v>31.35772695231987</v>
+        <v>31.06235804674234</v>
       </c>
       <c r="E90">
-        <v>40.02799999999999</v>
+        <v>41.28399999999999</v>
       </c>
       <c r="F90">
-        <v>110.528</v>
+        <v>111.784</v>
       </c>
       <c r="G90">
         <v>0.446</v>
@@ -8655,37 +8655,37 @@
         <v>9.77</v>
       </c>
       <c r="M90">
-        <v>26.0625024</v>
+        <v>26.3586672</v>
       </c>
       <c r="N90">
-        <v>-16.2925024</v>
+        <v>-16.5886672</v>
       </c>
       <c r="O90">
-        <v>-4.88775072</v>
+        <v>-4.976600159999999</v>
       </c>
       <c r="P90">
-        <v>-11.40475168</v>
+        <v>-11.61206704</v>
       </c>
       <c r="Q90">
-        <v>-3.67475168</v>
+        <v>-3.882067039999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3581076084233518</v>
+        <v>0.3864992091891111</v>
       </c>
       <c r="T90">
-        <v>7.212646845804891</v>
+        <v>7.868342013605337</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1124604212986087</v>
+        <v>0.1111968210592985</v>
       </c>
       <c r="W90">
-        <v>0.2092818326577881</v>
+        <v>0.2095797895942174</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3748680709953622</v>
+        <v>0.3706560701976616</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2290409257496557</v>
+        <v>0.2309409257496557</v>
       </c>
       <c r="C91">
-        <v>-80.27564195325765</v>
+        <v>-81.8214984255001</v>
       </c>
       <c r="D91">
-        <v>31.06235804674234</v>
+        <v>30.77250157449989</v>
       </c>
       <c r="E91">
-        <v>41.28399999999999</v>
+        <v>42.53999999999999</v>
       </c>
       <c r="F91">
-        <v>111.784</v>
+        <v>113.04</v>
       </c>
       <c r="G91">
         <v>0.446</v>
@@ -8737,37 +8737,37 @@
         <v>9.77</v>
       </c>
       <c r="M91">
-        <v>26.3586672</v>
+        <v>26.654832</v>
       </c>
       <c r="N91">
-        <v>-16.5886672</v>
+        <v>-16.884832</v>
       </c>
       <c r="O91">
-        <v>-4.976600159999999</v>
+        <v>-5.0654496</v>
       </c>
       <c r="P91">
-        <v>-11.61206704</v>
+        <v>-11.8193824</v>
       </c>
       <c r="Q91">
-        <v>-3.882067039999999</v>
+        <v>-4.089382399999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3864992091891111</v>
+        <v>0.4205691301080222</v>
       </c>
       <c r="T91">
-        <v>7.868342013605337</v>
+        <v>8.65517621496587</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1111968210592985</v>
+        <v>0.1099613008253063</v>
       </c>
       <c r="W91">
-        <v>0.2095797895942174</v>
+        <v>0.2098711252653928</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3706560701976616</v>
+        <v>0.3665376694176876</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2309409257496557</v>
+        <v>0.2328409257496557</v>
       </c>
       <c r="C92">
-        <v>-81.8214984255001</v>
+        <v>-83.36199535451479</v>
       </c>
       <c r="D92">
-        <v>30.77250157449989</v>
+        <v>30.48800464548521</v>
       </c>
       <c r="E92">
-        <v>42.53999999999999</v>
+        <v>43.79599999999999</v>
       </c>
       <c r="F92">
-        <v>113.04</v>
+        <v>114.296</v>
       </c>
       <c r="G92">
         <v>0.446</v>
@@ -8819,37 +8819,37 @@
         <v>9.77</v>
       </c>
       <c r="M92">
-        <v>26.654832</v>
+        <v>26.9509968</v>
       </c>
       <c r="N92">
-        <v>-16.884832</v>
+        <v>-17.1809968</v>
       </c>
       <c r="O92">
-        <v>-5.0654496</v>
+        <v>-5.15429904</v>
       </c>
       <c r="P92">
-        <v>-11.8193824</v>
+        <v>-12.02669776</v>
       </c>
       <c r="Q92">
-        <v>-4.089382399999998</v>
+        <v>-4.296697759999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4205691301080222</v>
+        <v>0.4622101445644691</v>
       </c>
       <c r="T92">
-        <v>8.65517621496587</v>
+        <v>9.61686246107319</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1099613008253063</v>
+        <v>0.108752934882171</v>
       </c>
       <c r="W92">
-        <v>0.2098711252653928</v>
+        <v>0.2101560579547841</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3665376694176876</v>
+        <v>0.3625097829405701</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2328409257496557</v>
+        <v>0.2347409257496558</v>
       </c>
       <c r="C93">
-        <v>-83.36199535451479</v>
+        <v>-84.89728002822351</v>
       </c>
       <c r="D93">
-        <v>30.48800464548521</v>
+        <v>30.2087199717765</v>
       </c>
       <c r="E93">
-        <v>43.79599999999999</v>
+        <v>45.05200000000001</v>
       </c>
       <c r="F93">
-        <v>114.296</v>
+        <v>115.552</v>
       </c>
       <c r="G93">
         <v>0.446</v>
@@ -8901,37 +8901,37 @@
         <v>9.77</v>
       </c>
       <c r="M93">
-        <v>26.9509968</v>
+        <v>27.2471616</v>
       </c>
       <c r="N93">
-        <v>-17.1809968</v>
+        <v>-17.4771616</v>
       </c>
       <c r="O93">
-        <v>-5.15429904</v>
+        <v>-5.24314848</v>
       </c>
       <c r="P93">
-        <v>-12.02669776</v>
+        <v>-12.23401312</v>
       </c>
       <c r="Q93">
-        <v>-4.296697759999999</v>
+        <v>-4.504013120000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4622101445644691</v>
+        <v>0.5142614126350279</v>
       </c>
       <c r="T93">
-        <v>9.61686246107319</v>
+        <v>10.81897026870734</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.108752934882171</v>
+        <v>0.1075708377638866</v>
       </c>
       <c r="W93">
-        <v>0.2101560579547841</v>
+        <v>0.2104347964552756</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3625097829405701</v>
+        <v>0.3585694592129552</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2347409257496558</v>
+        <v>0.2366409257496558</v>
       </c>
       <c r="C94">
-        <v>-84.89728002822351</v>
+        <v>-86.42749438662693</v>
       </c>
       <c r="D94">
-        <v>30.2087199717765</v>
+        <v>29.93450561337307</v>
       </c>
       <c r="E94">
-        <v>45.05200000000001</v>
+        <v>46.30800000000001</v>
       </c>
       <c r="F94">
-        <v>115.552</v>
+        <v>116.808</v>
       </c>
       <c r="G94">
         <v>0.446</v>
@@ -8983,37 +8983,37 @@
         <v>9.77</v>
       </c>
       <c r="M94">
-        <v>27.2471616</v>
+        <v>27.5433264</v>
       </c>
       <c r="N94">
-        <v>-17.4771616</v>
+        <v>-17.7733264</v>
       </c>
       <c r="O94">
-        <v>-5.24314848</v>
+        <v>-5.33199792</v>
       </c>
       <c r="P94">
-        <v>-12.23401312</v>
+        <v>-12.44132848</v>
       </c>
       <c r="Q94">
-        <v>-4.504013120000002</v>
+        <v>-4.711328480000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5142614126350279</v>
+        <v>0.5811844715828891</v>
       </c>
       <c r="T94">
-        <v>10.81897026870734</v>
+        <v>12.36453744995125</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1075708377638866</v>
+        <v>0.1064141620890061</v>
       </c>
       <c r="W94">
-        <v>0.2104347964552756</v>
+        <v>0.2107075405794124</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3585694592129552</v>
+        <v>0.3547138736300202</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2366409257496558</v>
+        <v>0.2385409257496557</v>
       </c>
       <c r="C95">
-        <v>-86.42749438662693</v>
+        <v>-87.95277526234523</v>
       </c>
       <c r="D95">
-        <v>29.93450561337307</v>
+        <v>29.66522473765478</v>
       </c>
       <c r="E95">
-        <v>46.30800000000001</v>
+        <v>47.56400000000001</v>
       </c>
       <c r="F95">
-        <v>116.808</v>
+        <v>118.064</v>
       </c>
       <c r="G95">
         <v>0.446</v>
@@ -9065,37 +9065,37 @@
         <v>9.77</v>
       </c>
       <c r="M95">
-        <v>27.5433264</v>
+        <v>27.8394912</v>
       </c>
       <c r="N95">
-        <v>-17.7733264</v>
+        <v>-18.0694912</v>
       </c>
       <c r="O95">
-        <v>-5.33199792</v>
+        <v>-5.420847360000001</v>
       </c>
       <c r="P95">
-        <v>-12.44132848</v>
+        <v>-12.64864384</v>
       </c>
       <c r="Q95">
-        <v>-4.711328480000002</v>
+        <v>-4.918643840000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5811844715828891</v>
+        <v>0.6704152168467041</v>
       </c>
       <c r="T95">
-        <v>12.36453744995125</v>
+        <v>14.4252936916098</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1064141620890061</v>
+        <v>0.1052820965348677</v>
       </c>
       <c r="W95">
-        <v>0.2107075405794124</v>
+        <v>0.2109744816370782</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3547138736300202</v>
+        <v>0.3509403217828924</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2385409257496557</v>
+        <v>0.2404409257496557</v>
       </c>
       <c r="C96">
-        <v>-87.95277526234523</v>
+        <v>-89.47325460829154</v>
       </c>
       <c r="D96">
-        <v>29.66522473765478</v>
+        <v>29.40074539170847</v>
       </c>
       <c r="E96">
-        <v>47.56400000000001</v>
+        <v>48.82000000000001</v>
       </c>
       <c r="F96">
-        <v>118.064</v>
+        <v>119.32</v>
       </c>
       <c r="G96">
         <v>0.446</v>
@@ -9147,37 +9147,37 @@
         <v>9.77</v>
       </c>
       <c r="M96">
-        <v>27.8394912</v>
+        <v>28.135656</v>
       </c>
       <c r="N96">
-        <v>-18.0694912</v>
+        <v>-18.365656</v>
       </c>
       <c r="O96">
-        <v>-5.420847360000001</v>
+        <v>-5.509696800000001</v>
       </c>
       <c r="P96">
-        <v>-12.64864384</v>
+        <v>-12.8559592</v>
       </c>
       <c r="Q96">
-        <v>-4.918643840000001</v>
+        <v>-5.125959200000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6704152168467041</v>
+        <v>0.7953382602160454</v>
       </c>
       <c r="T96">
-        <v>14.4252936916098</v>
+        <v>17.31035242993176</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1052820965348677</v>
+        <v>0.1041738639397638</v>
       </c>
       <c r="W96">
-        <v>0.2109744816370782</v>
+        <v>0.2112358028830037</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3509403217828924</v>
+        <v>0.347246213132546</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2404409257496557</v>
+        <v>0.2423409257496558</v>
       </c>
       <c r="C97">
-        <v>-89.47325460829154</v>
+        <v>-90.98905971327393</v>
       </c>
       <c r="D97">
-        <v>29.40074539170847</v>
+        <v>29.14094028672607</v>
       </c>
       <c r="E97">
-        <v>48.82000000000001</v>
+        <v>50.07600000000001</v>
       </c>
       <c r="F97">
-        <v>119.32</v>
+        <v>120.576</v>
       </c>
       <c r="G97">
         <v>0.446</v>
@@ -9229,37 +9229,37 @@
         <v>9.77</v>
       </c>
       <c r="M97">
-        <v>28.135656</v>
+        <v>28.4318208</v>
       </c>
       <c r="N97">
-        <v>-18.365656</v>
+        <v>-18.6618208</v>
       </c>
       <c r="O97">
-        <v>-5.509696800000001</v>
+        <v>-5.598546240000001</v>
       </c>
       <c r="P97">
-        <v>-12.8559592</v>
+        <v>-13.06327456</v>
       </c>
       <c r="Q97">
-        <v>-5.125959200000004</v>
+        <v>-5.333274560000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7953382602160454</v>
+        <v>0.9827228252700571</v>
       </c>
       <c r="T97">
-        <v>17.31035242993176</v>
+        <v>21.63794053741471</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1041738639397638</v>
+        <v>0.1030887195237246</v>
       </c>
       <c r="W97">
-        <v>0.2112358028830037</v>
+        <v>0.2114916799363058</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.347246213132546</v>
+        <v>0.3436290650790821</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2423409257496557</v>
+        <v>0.2442409257496558</v>
       </c>
       <c r="C98">
-        <v>-90.9890597132739</v>
+        <v>-92.5003134062667</v>
       </c>
       <c r="D98">
-        <v>29.14094028672609</v>
+        <v>28.8856865937333</v>
       </c>
       <c r="E98">
-        <v>50.07599999999999</v>
+        <v>51.33199999999999</v>
       </c>
       <c r="F98">
-        <v>120.576</v>
+        <v>121.832</v>
       </c>
       <c r="G98">
         <v>0.446</v>
@@ -9311,37 +9311,37 @@
         <v>9.77</v>
       </c>
       <c r="M98">
-        <v>28.4318208</v>
+        <v>28.7279856</v>
       </c>
       <c r="N98">
-        <v>-18.6618208</v>
+        <v>-18.9579856</v>
       </c>
       <c r="O98">
-        <v>-5.59854624</v>
+        <v>-5.68739568</v>
       </c>
       <c r="P98">
-        <v>-13.06327456</v>
+        <v>-13.27058992</v>
       </c>
       <c r="Q98">
-        <v>-5.33327456</v>
+        <v>-5.54058992</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9827228252700544</v>
+        <v>1.295030433693406</v>
       </c>
       <c r="T98">
-        <v>21.63794053741465</v>
+        <v>28.85058738321954</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1030887195237246</v>
+        <v>0.1020259492193563</v>
       </c>
       <c r="W98">
-        <v>0.2114916799363057</v>
+        <v>0.2117422811740758</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3436290650790821</v>
+        <v>0.3400864973978545</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2442409257496558</v>
+        <v>0.2461409257496557</v>
       </c>
       <c r="C99">
-        <v>-92.5003134062667</v>
+        <v>-94.00713425003882</v>
       </c>
       <c r="D99">
-        <v>28.8856865937333</v>
+        <v>28.63486574996118</v>
       </c>
       <c r="E99">
-        <v>51.33199999999999</v>
+        <v>52.58799999999999</v>
       </c>
       <c r="F99">
-        <v>121.832</v>
+        <v>123.088</v>
       </c>
       <c r="G99">
         <v>0.446</v>
@@ -9393,37 +9393,37 @@
         <v>9.77</v>
       </c>
       <c r="M99">
-        <v>28.7279856</v>
+        <v>29.0241504</v>
       </c>
       <c r="N99">
-        <v>-18.9579856</v>
+        <v>-19.2541504</v>
       </c>
       <c r="O99">
-        <v>-5.68739568</v>
+        <v>-5.77624512</v>
       </c>
       <c r="P99">
-        <v>-13.27058992</v>
+        <v>-13.47790528</v>
       </c>
       <c r="Q99">
-        <v>-5.54058992</v>
+        <v>-5.747905280000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.295030433693406</v>
+        <v>1.919645650540109</v>
       </c>
       <c r="T99">
-        <v>28.85058738321954</v>
+        <v>43.27588107482931</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1020259492193563</v>
+        <v>0.1009848681048731</v>
       </c>
       <c r="W99">
-        <v>0.2117422811740758</v>
+        <v>0.2119877681008709</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3400864973978545</v>
+        <v>0.3366162270162437</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2461409257496557</v>
+        <v>0.2480409257496557</v>
       </c>
       <c r="C100">
-        <v>-94.00713425003882</v>
+        <v>-95.50963672478159</v>
       </c>
       <c r="D100">
-        <v>28.63486574996118</v>
+        <v>28.3883632752184</v>
       </c>
       <c r="E100">
-        <v>52.58799999999999</v>
+        <v>53.84399999999999</v>
       </c>
       <c r="F100">
-        <v>123.088</v>
+        <v>124.344</v>
       </c>
       <c r="G100">
         <v>0.446</v>
@@ -9475,37 +9475,37 @@
         <v>9.77</v>
       </c>
       <c r="M100">
-        <v>29.0241504</v>
+        <v>29.3203152</v>
       </c>
       <c r="N100">
-        <v>-19.2541504</v>
+        <v>-19.5503152</v>
       </c>
       <c r="O100">
-        <v>-5.77624512</v>
+        <v>-5.86509456</v>
       </c>
       <c r="P100">
-        <v>-13.47790528</v>
+        <v>-13.68522064</v>
       </c>
       <c r="Q100">
-        <v>-5.747905280000001</v>
+        <v>-5.95522064</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.919645650540109</v>
+        <v>3.793491301080218</v>
       </c>
       <c r="T100">
-        <v>43.27588107482931</v>
+        <v>86.55176214965861</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1009848681048731</v>
+        <v>0.09996481893209661</v>
       </c>
       <c r="W100">
-        <v>0.2119877681008709</v>
+        <v>0.2122282956958116</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3366162270162437</v>
+        <v>0.3332160631069887</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2480409257496557</v>
-      </c>
-      <c r="C101">
-        <v>-95.50963672478159</v>
-      </c>
-      <c r="D101">
-        <v>28.3883632752184</v>
-      </c>
-      <c r="E101">
-        <v>53.84399999999999</v>
-      </c>
-      <c r="F101">
-        <v>124.344</v>
-      </c>
-      <c r="G101">
-        <v>0.446</v>
-      </c>
-      <c r="H101">
-        <v>55.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.5</v>
-      </c>
-      <c r="K101">
-        <v>7.73</v>
-      </c>
-      <c r="L101">
-        <v>9.77</v>
-      </c>
-      <c r="M101">
-        <v>29.3203152</v>
-      </c>
-      <c r="N101">
-        <v>-19.5503152</v>
-      </c>
-      <c r="O101">
-        <v>-5.86509456</v>
-      </c>
-      <c r="P101">
-        <v>-13.68522064</v>
-      </c>
-      <c r="Q101">
-        <v>-5.95522064</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.793491301080218</v>
-      </c>
-      <c r="T101">
-        <v>86.55176214965861</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09996481893209661</v>
-      </c>
-      <c r="W101">
-        <v>0.2122282956958116</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3332160631069887</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
